--- a/pools-example-medium-seeded.xlsx
+++ b/pools-example-medium-seeded.xlsx
@@ -1049,11 +1049,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="15"/>
-    <col customWidth="true" max="26" min="2" width="30"/>
+    <col customWidth="true" max="1" min="1" width="9"/>
+    <col customWidth="true" max="3" min="2" width="20"/>
+    <col customWidth="true" max="26" min="4" width="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1418,7 +1422,8 @@
       </c>
     </row>
   </sheetData>
-  <pageSetup orientation="landscape"/>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -3715,7 +3720,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>
@@ -3921,7 +3926,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>

--- a/pools-example-medium-seeded.xlsx
+++ b/pools-example-medium-seeded.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -12,15 +12,17 @@
     <sheet name="Pool Draw" sheetId="3" r:id="rId5"/>
     <sheet name="Pool Matches" sheetId="4" r:id="rId6"/>
     <sheet name="Elimination Matches" sheetId="5" r:id="rId7"/>
-    <sheet name="Names to Print" sheetId="6" r:id="rId8"/>
     <sheet name="Tree 1" sheetId="8" r:id="rId11"/>
     <sheet name="Tree 2" sheetId="9" r:id="rId12"/>
-    <sheet name="Tags" sheetId="10" r:id="rId13"/>
+    <sheet name="Names to Print A" sheetId="10" r:id="rId13"/>
+    <sheet name="Names to Print B" sheetId="11" r:id="rId14"/>
+    <sheet name="Tags" sheetId="12" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$23</definedName>
     <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$41</definedName>
-    <definedName localSheetId="5" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$24</definedName>
+    <definedName localSheetId="7" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$12</definedName>
+    <definedName localSheetId="8" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$12</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -450,7 +452,7 @@
     <t>Round 3 - Match 14</t>
   </si>
   <si>
-    <t>Round 4 - Match 0</t>
+    <t>Round 4 - Match 15</t>
   </si>
   <si>
     <t>Tournament Summary</t>
@@ -1431,6 +1433,240 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="27" t="str">
+        <f>data!D3</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="27" t="str">
+        <f>data!D4</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="27" t="str">
+        <f>data!D5</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="27" t="str">
+        <f>data!D6</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="27" t="str">
+        <f>data!D7</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="27" t="str">
+        <f>data!D8</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="27" t="str">
+        <f>data!D9</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="27" t="str">
+        <f>data!D10</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="27" t="str">
+        <f>data!D11</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="27" t="str">
+        <f>data!D12</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="27" t="str">
+        <f>data!D13</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="27" t="str">
+        <f>data!D14</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="4" manualBreakCount="4">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="27" t="str">
+        <f>data!D15</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="27" t="str">
+        <f>data!D16</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="27" t="str">
+        <f>data!D17</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="27" t="str">
+        <f>data!D18</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="27" t="str">
+        <f>data!D19</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="27" t="str">
+        <f>data!D20</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="27" t="str">
+        <f>data!D21</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="27" t="str">
+        <f>data!D22</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="27" t="str">
+        <f>data!D23</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="27" t="str">
+        <f>data!D24</f>
+      </c>
+    </row>
+    <row r="11" ht="270" customHeight="true">
+      <c r="A11" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" s="27" t="str">
+        <f>data!D25</f>
+      </c>
+    </row>
+    <row r="12" ht="270" customHeight="true">
+      <c r="A12" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="27" t="str">
+        <f>data!D26</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="4" manualBreakCount="4">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+    <brk id="12" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="90"/>
   </cols>
   <sheetData>
@@ -3499,223 +3735,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" style="9" width="30"/>
-    <col customWidth="true" max="2" min="2" style="10" width="160"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="27" t="str">
-        <f>data!D3</f>
-      </c>
-    </row>
-    <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" s="27" t="str">
-        <f>data!D4</f>
-      </c>
-    </row>
-    <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="27" t="str">
-        <f>data!D5</f>
-      </c>
-    </row>
-    <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="27" t="str">
-        <f>data!D6</f>
-      </c>
-    </row>
-    <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="27" t="str">
-        <f>data!D7</f>
-      </c>
-    </row>
-    <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" s="27" t="str">
-        <f>data!D8</f>
-      </c>
-    </row>
-    <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="27" t="str">
-        <f>data!D9</f>
-      </c>
-    </row>
-    <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="27" t="str">
-        <f>data!D10</f>
-      </c>
-    </row>
-    <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" s="27" t="str">
-        <f>data!D11</f>
-      </c>
-    </row>
-    <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" s="27" t="str">
-        <f>data!D12</f>
-      </c>
-    </row>
-    <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="B11" s="27" t="str">
-        <f>data!D13</f>
-      </c>
-    </row>
-    <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="B12" s="27" t="str">
-        <f>data!D14</f>
-      </c>
-    </row>
-    <row r="13" ht="270" customHeight="true">
-      <c r="A13" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="B13" s="27" t="str">
-        <f>data!D15</f>
-      </c>
-    </row>
-    <row r="14" ht="270" customHeight="true">
-      <c r="A14" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="B14" s="27" t="str">
-        <f>data!D16</f>
-      </c>
-    </row>
-    <row r="15" ht="270" customHeight="true">
-      <c r="A15" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="B15" s="27" t="str">
-        <f>data!D17</f>
-      </c>
-    </row>
-    <row r="16" ht="270" customHeight="true">
-      <c r="A16" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="B16" s="27" t="str">
-        <f>data!D18</f>
-      </c>
-    </row>
-    <row r="17" ht="270" customHeight="true">
-      <c r="A17" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="B17" s="27" t="str">
-        <f>data!D19</f>
-      </c>
-    </row>
-    <row r="18" ht="270" customHeight="true">
-      <c r="A18" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="B18" s="27" t="str">
-        <f>data!D20</f>
-      </c>
-    </row>
-    <row r="19" ht="270" customHeight="true">
-      <c r="A19" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="B19" s="27" t="str">
-        <f>data!D21</f>
-      </c>
-    </row>
-    <row r="20" ht="270" customHeight="true">
-      <c r="A20" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="B20" s="27" t="str">
-        <f>data!D22</f>
-      </c>
-    </row>
-    <row r="21" ht="270" customHeight="true">
-      <c r="A21" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="B21" s="27" t="str">
-        <f>data!D23</f>
-      </c>
-    </row>
-    <row r="22" ht="270" customHeight="true">
-      <c r="A22" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="B22" s="27" t="str">
-        <f>data!D24</f>
-      </c>
-    </row>
-    <row r="23" ht="270" customHeight="true">
-      <c r="A23" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="B23" s="27" t="str">
-        <f>data!D25</f>
-      </c>
-    </row>
-    <row r="24" ht="270" customHeight="true">
-      <c r="A24" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="B24" s="27" t="str">
-        <f>data!D26</f>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="8"/>
-  <rowBreaks count="8" manualBreakCount="8">
-    <brk id="3" max="16383" man="true"/>
-    <brk id="6" max="16383" man="true"/>
-    <brk id="9" max="16383" man="true"/>
-    <brk id="12" max="16383" man="true"/>
-    <brk id="15" max="16383" man="true"/>
-    <brk id="18" max="16383" man="true"/>
-    <brk id="21" max="16383" man="true"/>
-    <brk id="24" max="16383" man="true"/>
-  </rowBreaks>
-  <colBreaks/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>

--- a/pools-example-medium-seeded.xlsx
+++ b/pools-example-medium-seeded.xlsx
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$23</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$41</definedName>
+    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$65</definedName>
     <definedName localSheetId="7" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$12</definedName>
     <definedName localSheetId="8" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$12</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$85</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
   <si>
     <t>Number of pools</t>
   </si>
@@ -321,6 +321,24 @@
   </si>
   <si>
     <t>Red</t>
+  </si>
+  <si>
+    <t>Results</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>PW</t>
+  </si>
+  <si>
+    <t>PL</t>
   </si>
   <si>
     <t xml:space="preserve">1. </t>
@@ -576,7 +594,7 @@
       <sz val="150"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -586,6 +604,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFEFEF"/>
       </patternFill>
     </fill>
     <fill>
@@ -692,7 +715,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -733,17 +756,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center"/>
+      <protection hidden="false" locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment/>
+      <protection hidden="false" locked="false"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
@@ -754,10 +785,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false">
@@ -779,6 +810,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -1438,102 +1472,103 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1" s="27" t="str">
+      <c r="A1" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="29" t="str">
         <f>data!D3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" s="27" t="str">
+      <c r="A2" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="29" t="str">
         <f>data!D4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="27" t="str">
+      <c r="A3" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="29" t="str">
         <f>data!D5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="27" t="str">
+      <c r="A4" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="29" t="str">
         <f>data!D6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="27" t="str">
+      <c r="A5" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" s="29" t="str">
         <f>data!D7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" s="27" t="str">
+      <c r="A6" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="29" t="str">
         <f>data!D8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="27" t="str">
+      <c r="A7" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="29" t="str">
         <f>data!D9</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="27" t="str">
+      <c r="A8" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="29" t="str">
         <f>data!D10</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" s="27" t="str">
+      <c r="A9" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" s="29" t="str">
         <f>data!D11</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" s="27" t="str">
+      <c r="A10" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="29" t="str">
         <f>data!D12</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="B11" s="27" t="str">
+      <c r="A11" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" s="29" t="str">
         <f>data!D13</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="B12" s="27" t="str">
+      <c r="A12" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" s="29" t="str">
         <f>data!D14</f>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8"/>
   <rowBreaks count="4" manualBreakCount="4">
@@ -1555,102 +1590,103 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="B1" s="27" t="str">
+      <c r="A1" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="29" t="str">
         <f>data!D15</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="B2" s="27" t="str">
+      <c r="A2" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="29" t="str">
         <f>data!D16</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="26" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" s="27" t="str">
+      <c r="A3" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="29" t="str">
         <f>data!D17</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="B4" s="27" t="str">
+      <c r="A4" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="29" t="str">
         <f>data!D18</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="B5" s="27" t="str">
+      <c r="A5" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="29" t="str">
         <f>data!D19</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="B6" s="27" t="str">
+      <c r="A6" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="29" t="str">
         <f>data!D20</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="B7" s="27" t="str">
+      <c r="A7" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="29" t="str">
         <f>data!D21</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" s="27" t="str">
+      <c r="A8" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="29" t="str">
         <f>data!D22</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="B9" s="27" t="str">
+      <c r="A9" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="29" t="str">
         <f>data!D23</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="B10" s="27" t="str">
+      <c r="A10" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="29" t="str">
         <f>data!D24</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="B11" s="27" t="str">
+      <c r="A11" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="29" t="str">
         <f>data!D25</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="B12" s="27" t="str">
+      <c r="A12" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="29" t="str">
         <f>data!D26</f>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8"/>
   <rowBreaks count="4" manualBreakCount="4">
@@ -1671,246 +1707,247 @@
   </cols>
   <sheetData>
     <row r="1" ht="390" customHeight="true">
-      <c r="A1" s="28" t="s">
-        <v>100</v>
+      <c r="A1" s="30" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="2" ht="390" customHeight="true">
-      <c r="A2" s="28" t="s">
-        <v>100</v>
+      <c r="A2" s="30" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="3" ht="390" customHeight="true">
-      <c r="A3" s="28" t="s">
-        <v>101</v>
+      <c r="A3" s="30" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="4" ht="390" customHeight="true">
-      <c r="A4" s="28" t="s">
-        <v>101</v>
+      <c r="A4" s="30" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="5" ht="390" customHeight="true">
-      <c r="A5" s="28" t="s">
-        <v>102</v>
+      <c r="A5" s="30" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="6" ht="390" customHeight="true">
-      <c r="A6" s="28" t="s">
-        <v>102</v>
+      <c r="A6" s="30" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="7" ht="390" customHeight="true">
-      <c r="A7" s="28" t="s">
-        <v>103</v>
+      <c r="A7" s="30" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="8" ht="390" customHeight="true">
-      <c r="A8" s="28" t="s">
-        <v>103</v>
+      <c r="A8" s="30" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="9" ht="390" customHeight="true">
-      <c r="A9" s="28" t="s">
-        <v>104</v>
+      <c r="A9" s="30" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="10" ht="390" customHeight="true">
-      <c r="A10" s="28" t="s">
-        <v>104</v>
+      <c r="A10" s="30" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="11" ht="390" customHeight="true">
-      <c r="A11" s="28" t="s">
-        <v>105</v>
+      <c r="A11" s="30" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="12" ht="390" customHeight="true">
-      <c r="A12" s="28" t="s">
-        <v>105</v>
+      <c r="A12" s="30" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="13" ht="390" customHeight="true">
-      <c r="A13" s="28" t="s">
-        <v>106</v>
+      <c r="A13" s="30" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="14" ht="390" customHeight="true">
-      <c r="A14" s="28" t="s">
-        <v>106</v>
+      <c r="A14" s="30" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="15" ht="390" customHeight="true">
-      <c r="A15" s="28" t="s">
-        <v>107</v>
+      <c r="A15" s="30" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="16" ht="390" customHeight="true">
-      <c r="A16" s="28" t="s">
-        <v>107</v>
+      <c r="A16" s="30" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="17" ht="390" customHeight="true">
-      <c r="A17" s="28" t="s">
-        <v>108</v>
+      <c r="A17" s="30" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="18" ht="390" customHeight="true">
-      <c r="A18" s="28" t="s">
-        <v>108</v>
+      <c r="A18" s="30" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="19" ht="390" customHeight="true">
-      <c r="A19" s="28" t="s">
-        <v>109</v>
+      <c r="A19" s="30" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="20" ht="390" customHeight="true">
-      <c r="A20" s="28" t="s">
-        <v>109</v>
+      <c r="A20" s="30" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="21" ht="390" customHeight="true">
-      <c r="A21" s="28" t="s">
-        <v>110</v>
+      <c r="A21" s="30" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="22" ht="390" customHeight="true">
-      <c r="A22" s="28" t="s">
-        <v>110</v>
+      <c r="A22" s="30" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="23" ht="390" customHeight="true">
-      <c r="A23" s="28" t="s">
-        <v>111</v>
+      <c r="A23" s="30" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="24" ht="390" customHeight="true">
-      <c r="A24" s="28" t="s">
-        <v>111</v>
+      <c r="A24" s="30" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="25" ht="390" customHeight="true">
-      <c r="A25" s="28" t="s">
-        <v>112</v>
+      <c r="A25" s="30" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="26" ht="390" customHeight="true">
-      <c r="A26" s="28" t="s">
-        <v>112</v>
+      <c r="A26" s="30" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="27" ht="390" customHeight="true">
-      <c r="A27" s="28" t="s">
-        <v>113</v>
+      <c r="A27" s="30" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="28" ht="390" customHeight="true">
-      <c r="A28" s="28" t="s">
-        <v>113</v>
+      <c r="A28" s="30" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="29" ht="390" customHeight="true">
-      <c r="A29" s="28" t="s">
-        <v>114</v>
+      <c r="A29" s="30" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="30" ht="390" customHeight="true">
-      <c r="A30" s="28" t="s">
-        <v>114</v>
+      <c r="A30" s="30" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="31" ht="390" customHeight="true">
-      <c r="A31" s="28" t="s">
-        <v>115</v>
+      <c r="A31" s="30" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="32" ht="390" customHeight="true">
-      <c r="A32" s="28" t="s">
-        <v>115</v>
+      <c r="A32" s="30" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="33" ht="390" customHeight="true">
-      <c r="A33" s="28" t="s">
-        <v>116</v>
+      <c r="A33" s="30" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="34" ht="390" customHeight="true">
-      <c r="A34" s="28" t="s">
-        <v>116</v>
+      <c r="A34" s="30" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="35" ht="390" customHeight="true">
-      <c r="A35" s="28" t="s">
-        <v>117</v>
+      <c r="A35" s="30" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="36" ht="390" customHeight="true">
-      <c r="A36" s="28" t="s">
-        <v>117</v>
+      <c r="A36" s="30" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="37" ht="390" customHeight="true">
-      <c r="A37" s="28" t="s">
-        <v>118</v>
+      <c r="A37" s="30" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="38" ht="390" customHeight="true">
-      <c r="A38" s="28" t="s">
-        <v>118</v>
+      <c r="A38" s="30" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="39" ht="390" customHeight="true">
-      <c r="A39" s="28" t="s">
-        <v>119</v>
+      <c r="A39" s="30" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="40" ht="390" customHeight="true">
-      <c r="A40" s="28" t="s">
-        <v>119</v>
+      <c r="A40" s="30" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="41" ht="390" customHeight="true">
-      <c r="A41" s="28" t="s">
-        <v>120</v>
+      <c r="A41" s="30" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="42" ht="390" customHeight="true">
-      <c r="A42" s="28" t="s">
-        <v>120</v>
+      <c r="A42" s="30" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="43" ht="390" customHeight="true">
-      <c r="A43" s="28" t="s">
-        <v>121</v>
+      <c r="A43" s="30" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="44" ht="390" customHeight="true">
-      <c r="A44" s="28" t="s">
-        <v>121</v>
+      <c r="A44" s="30" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="45" ht="390" customHeight="true">
-      <c r="A45" s="28" t="s">
-        <v>122</v>
+      <c r="A45" s="30" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="46" ht="390" customHeight="true">
-      <c r="A46" s="28" t="s">
-        <v>122</v>
+      <c r="A46" s="30" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="47" ht="390" customHeight="true">
-      <c r="A47" s="28" t="s">
-        <v>123</v>
+      <c r="A47" s="30" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="48" ht="390" customHeight="true">
-      <c r="A48" s="28" t="s">
-        <v>123</v>
+      <c r="A48" s="30" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9"/>
   <rowBreaks count="24" manualBreakCount="24">
@@ -2003,7 +2040,7 @@
       <c r="G2" s="3">
         <v>0.020833333333333332</v>
       </c>
-      <c r="H2" s="29" t="str">
+      <c r="H2" s="31" t="str">
         <f>C2*I2+J2</f>
       </c>
     </row>
@@ -2107,7 +2144,7 @@
       <c r="G8" s="3">
         <v>0.020833333333333332</v>
       </c>
-      <c r="H8" s="29" t="str">
+      <c r="H8" s="31" t="str">
         <f>E8+(A8*F8)+G8</f>
       </c>
     </row>
@@ -2143,7 +2180,7 @@
     </row>
     <row r="13">
       <c r="E13" s="13" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
@@ -2153,62 +2190,62 @@
       <c r="A14">
         <v>2</v>
       </c>
-      <c r="E14" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="29" t="str">
+      <c r="E14" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="31" t="str">
         <f>H2</f>
       </c>
     </row>
     <row r="15">
-      <c r="E15" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="29" t="str">
+      <c r="E15" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="31" t="str">
         <f>H8</f>
       </c>
     </row>
     <row r="16">
-      <c r="E16" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="29" t="str">
+      <c r="E16" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="31" t="str">
         <f>H14+H15</f>
       </c>
     </row>
     <row r="17">
-      <c r="E17" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="29" t="str">
+      <c r="E17" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="31" t="str">
         <f>H16/A14</f>
       </c>
     </row>
     <row r="18">
       <c r="E18" s="13" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
-      <c r="H18" s="30">
+      <c r="H18" s="33">
         <v>0.375</v>
       </c>
     </row>
     <row r="19">
       <c r="E19" s="13" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
-      <c r="H19" s="30" t="str">
+      <c r="H19" s="33" t="str">
         <f>H18+H17</f>
       </c>
     </row>
@@ -2406,14 +2443,15 @@
     <col customWidth="true" max="4" min="4" width="3"/>
     <col customWidth="true" max="6" min="5" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
-    <col customWidth="true" max="8" min="8" width="2"/>
+    <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
     <col customWidth="true" max="11" min="10" width="5"/>
     <col customWidth="true" max="12" min="12" width="3"/>
     <col customWidth="true" max="14" min="13" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="16" min="16" width="2"/>
-    <col customWidth="true" max="20" min="17" width="10.83"/>
+    <col customWidth="true" max="18" min="16" width="5"/>
+    <col customWidth="true" max="19" min="19" width="30"/>
+    <col customWidth="true" max="20" min="20" width="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2480,22 +2518,22 @@
       <c r="A4" s="14" t="str">
         <f>data!$B$4</f>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
         <f>data!$B$3</f>
       </c>
       <c r="I4" s="14" t="str">
         <f>data!$B$16</f>
       </c>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
         <f>data!$B$15</f>
       </c>
@@ -2504,22 +2542,22 @@
       <c r="A5" s="14" t="str">
         <f>data!$B$5</f>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
       <c r="G5" s="14" t="str">
         <f>data!$B$3</f>
       </c>
       <c r="I5" s="14" t="str">
         <f>data!$B$17</f>
       </c>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
       <c r="O5" s="14" t="str">
         <f>data!$B$15</f>
       </c>
@@ -2528,498 +2566,1109 @@
       <c r="A6" s="14" t="str">
         <f>data!$B$5</f>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
       <c r="G6" s="14" t="str">
         <f>data!$B$4</f>
       </c>
       <c r="I6" s="14" t="str">
         <f>data!$B$17</f>
       </c>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
       <c r="O6" s="14" t="str">
         <f>data!$B$16</f>
       </c>
     </row>
     <row r="8">
-      <c r="F8" t="s">
+      <c r="A8" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="G8" s="15"/>
-      <c r="N8" t="s">
+      <c r="B8" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I8" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="O8" s="15"/>
+      <c r="J8" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="M8" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="9">
-      <c r="F9" t="s">
+      <c r="A9" s="14" t="str">
+        <f>data!$B$3</f>
+      </c>
+      <c r="B9" s="14" t="str">
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C9" s="14" t="str">
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D9" s="14" t="str">
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),1,0),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),1,0),0)</f>
+      </c>
+      <c r="E9" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F9" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I9" s="14" t="str">
+        <f>data!$B$15</f>
+      </c>
+      <c r="J9" s="14" t="str">
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K9" s="14" t="str">
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L9" s="14" t="str">
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),1,0),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),1,0),0)</f>
+      </c>
+      <c r="M9" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N9" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="str">
+        <f>data!$B$4</f>
+      </c>
+      <c r="B10" s="14" t="str">
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C10" s="14" t="str">
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D10" s="14" t="str">
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),1,0),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),1,0),0)</f>
+      </c>
+      <c r="E10" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F10" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I10" s="14" t="str">
+        <f>data!$B$16</f>
+      </c>
+      <c r="J10" s="14" t="str">
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K10" s="14" t="str">
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L10" s="14" t="str">
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),1,0),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),1,0),0)</f>
+      </c>
+      <c r="M10" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N10" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="str">
+        <f>data!$B$5</f>
+      </c>
+      <c r="B11" s="14" t="str">
+        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C11" s="14" t="str">
+        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D11" s="14" t="str">
+        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),1,0),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),1,0),0)</f>
+      </c>
+      <c r="E11" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F11" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I11" s="14" t="str">
+        <f>data!$B$17</f>
+      </c>
+      <c r="J11" s="14" t="str">
+        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K11" s="14" t="str">
+        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L11" s="14" t="str">
+        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),1,0),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),1,0),0)</f>
+      </c>
+      <c r="M11" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N11" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="13">
+      <c r="F13" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="19"/>
+      <c r="N13" t="s">
+        <v>103</v>
+      </c>
+      <c r="O13" s="19"/>
+    </row>
+    <row r="14">
+      <c r="F14" t="s">
+        <v>104</v>
+      </c>
+      <c r="G14" s="19"/>
+      <c r="N14" t="s">
+        <v>104</v>
+      </c>
+      <c r="O14" s="19"/>
+    </row>
+    <row r="15">
+      <c r="F15" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" s="19"/>
+      <c r="N15" t="s">
+        <v>105</v>
+      </c>
+      <c r="O15" s="19"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="str">
+        <f>data!$A$8</f>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="I18" s="13" t="str">
+        <f>data!$A$20</f>
+      </c>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="O19" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="str">
+        <f>data!$B$7</f>
+      </c>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="14" t="str">
+        <f>data!$B$6</f>
+      </c>
+      <c r="I20" s="14" t="str">
+        <f>data!$B$19</f>
+      </c>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="14" t="str">
+        <f>data!$B$18</f>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="str">
+        <f>data!$B$8</f>
+      </c>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="14" t="str">
+        <f>data!$B$6</f>
+      </c>
+      <c r="I21" s="14" t="str">
+        <f>data!$B$20</f>
+      </c>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="14" t="str">
+        <f>data!$B$18</f>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="str">
+        <f>data!$B$8</f>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="14" t="str">
+        <f>data!$B$7</f>
+      </c>
+      <c r="I22" s="14" t="str">
+        <f>data!$B$20</f>
+      </c>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="14" t="str">
+        <f>data!$B$19</f>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="G9" s="15"/>
-      <c r="N9" t="s">
+      <c r="C24" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="J24" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="O9" s="15"/>
-    </row>
-    <row r="10">
-      <c r="F10" t="s">
+      <c r="K24" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="G10" s="15"/>
-      <c r="N10" t="s">
-        <v>99</v>
-      </c>
-      <c r="O10" s="15"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="str">
-        <f>data!$A$8</f>
-      </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="I12" s="13" t="str">
-        <f>data!$A$20</f>
-      </c>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="L13" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="O13" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="str">
-        <f>data!$B$7</f>
-      </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14" t="str">
-        <f>data!$B$6</f>
-      </c>
-      <c r="I14" s="14" t="str">
-        <f>data!$B$19</f>
-      </c>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14" t="str">
-        <f>data!$B$18</f>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="str">
-        <f>data!$B$8</f>
-      </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14" t="str">
-        <f>data!$B$6</f>
-      </c>
-      <c r="I15" s="14" t="str">
-        <f>data!$B$20</f>
-      </c>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14" t="str">
-        <f>data!$B$18</f>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="str">
-        <f>data!$B$8</f>
-      </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14" t="str">
-        <f>data!$B$7</f>
-      </c>
-      <c r="I16" s="14" t="str">
-        <f>data!$B$20</f>
-      </c>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14" t="str">
-        <f>data!$B$19</f>
-      </c>
-    </row>
-    <row r="18">
-      <c r="F18" t="s">
-        <v>97</v>
-      </c>
-      <c r="G18" s="15"/>
-      <c r="N18" t="s">
-        <v>97</v>
-      </c>
-      <c r="O18" s="15"/>
-    </row>
-    <row r="19">
-      <c r="F19" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="15"/>
-      <c r="N19" t="s">
-        <v>98</v>
-      </c>
-      <c r="O19" s="15"/>
-    </row>
-    <row r="20">
-      <c r="F20" t="s">
-        <v>99</v>
-      </c>
-      <c r="G20" s="15"/>
-      <c r="N20" t="s">
-        <v>99</v>
-      </c>
-      <c r="O20" s="15"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="str">
-        <f>data!$A$11</f>
-      </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="I22" s="13" t="str">
-        <f>data!$A$23</f>
-      </c>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="13"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="G23" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="I23" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="L23" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="O23" s="16" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="str">
-        <f>data!$B$10</f>
-      </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14" t="str">
-        <f>data!$B$9</f>
-      </c>
-      <c r="I24" s="14" t="str">
-        <f>data!$B$22</f>
-      </c>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14" t="str">
-        <f>data!$B$21</f>
+      <c r="L24" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="M24" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="N24" s="13" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="str">
-        <f>data!$B$11</f>
-      </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14" t="str">
-        <f>data!$B$9</f>
+        <f>data!$B$6</f>
+      </c>
+      <c r="B25" s="14" t="str">
+        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C25" s="14" t="str">
+        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D25" s="14" t="str">
+        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),1,0),0)+IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),1,0),0)</f>
+      </c>
+      <c r="E25" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F25" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))</f>
       </c>
       <c r="I25" s="14" t="str">
-        <f>data!$B$23</f>
-      </c>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14" t="str">
-        <f>data!$B$21</f>
+        <f>data!$B$18</f>
+      </c>
+      <c r="J25" s="14" t="str">
+        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K25" s="14" t="str">
+        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L25" s="14" t="str">
+        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),1,0),0)+IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),1,0),0)</f>
+      </c>
+      <c r="M25" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N25" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))</f>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="str">
-        <f>data!$B$11</f>
-      </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14" t="str">
-        <f>data!$B$10</f>
+        <f>data!$B$7</f>
+      </c>
+      <c r="B26" s="14" t="str">
+        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C26" s="14" t="str">
+        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D26" s="14" t="str">
+        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),1,0),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),1,0),0)</f>
+      </c>
+      <c r="E26" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F26" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))</f>
       </c>
       <c r="I26" s="14" t="str">
-        <f>data!$B$23</f>
-      </c>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14" t="str">
-        <f>data!$B$22</f>
-      </c>
-    </row>
-    <row r="28">
-      <c r="F28" t="s">
-        <v>97</v>
-      </c>
-      <c r="G28" s="15"/>
-      <c r="N28" t="s">
-        <v>97</v>
-      </c>
-      <c r="O28" s="15"/>
+        <f>data!$B$19</f>
+      </c>
+      <c r="J26" s="14" t="str">
+        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K26" s="14" t="str">
+        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L26" s="14" t="str">
+        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),1,0),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),1,0),0)</f>
+      </c>
+      <c r="M26" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N26" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="str">
+        <f>data!$B$8</f>
+      </c>
+      <c r="B27" s="14" t="str">
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C27" s="14" t="str">
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D27" s="14" t="str">
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),1,0),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),1,0),0)</f>
+      </c>
+      <c r="E27" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F27" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I27" s="14" t="str">
+        <f>data!$B$20</f>
+      </c>
+      <c r="J27" s="14" t="str">
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K27" s="14" t="str">
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L27" s="14" t="str">
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),1,0),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),1,0),0)</f>
+      </c>
+      <c r="M27" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N27" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))</f>
+      </c>
     </row>
     <row r="29">
       <c r="F29" t="s">
-        <v>98</v>
-      </c>
-      <c r="G29" s="15"/>
+        <v>103</v>
+      </c>
+      <c r="G29" s="19"/>
       <c r="N29" t="s">
-        <v>98</v>
-      </c>
-      <c r="O29" s="15"/>
+        <v>103</v>
+      </c>
+      <c r="O29" s="19"/>
     </row>
     <row r="30">
       <c r="F30" t="s">
-        <v>99</v>
-      </c>
-      <c r="G30" s="15"/>
+        <v>104</v>
+      </c>
+      <c r="G30" s="19"/>
       <c r="N30" t="s">
-        <v>99</v>
-      </c>
-      <c r="O30" s="15"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="str">
-        <f>data!$A$14</f>
-      </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="I32" s="13" t="str">
-        <f>data!$A$26</f>
-      </c>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="13"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="O30" s="19"/>
+    </row>
+    <row r="31">
+      <c r="F31" t="s">
+        <v>105</v>
+      </c>
+      <c r="G31" s="19"/>
+      <c r="N31" t="s">
+        <v>105</v>
+      </c>
+      <c r="O31" s="19"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="str">
+        <f>data!$A$11</f>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="I34" s="13" t="str">
+        <f>data!$A$23</f>
+      </c>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D35" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G33" s="16" t="s">
+      <c r="G35" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="I33" s="17" t="s">
+      <c r="I35" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="L33" s="14" t="s">
+      <c r="L35" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="O33" s="16" t="s">
+      <c r="O35" s="16" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="str">
-        <f>data!$B$13</f>
-      </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="I34" s="14" t="str">
-        <f>data!$B$25</f>
-      </c>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14" t="str">
-        <f>data!$B$24</f>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="str">
-        <f>data!$B$14</f>
-      </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="I35" s="14" t="str">
-        <f>data!$B$26</f>
-      </c>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="14" t="str">
-        <f>data!$B$24</f>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="str">
+        <f>data!$B$10</f>
+      </c>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="14" t="str">
+        <f>data!$B$9</f>
+      </c>
+      <c r="I36" s="14" t="str">
+        <f>data!$B$22</f>
+      </c>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="14" t="str">
+        <f>data!$B$21</f>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="str">
+        <f>data!$B$11</f>
+      </c>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="14" t="str">
+        <f>data!$B$9</f>
+      </c>
+      <c r="I37" s="14" t="str">
+        <f>data!$B$23</f>
+      </c>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="14" t="str">
+        <f>data!$B$21</f>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="str">
+        <f>data!$B$11</f>
+      </c>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="14" t="str">
+        <f>data!$B$10</f>
+      </c>
+      <c r="I38" s="14" t="str">
+        <f>data!$B$23</f>
+      </c>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="14" t="str">
+        <f>data!$B$22</f>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="J40" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="K40" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="L40" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="M40" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="N40" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="str">
+        <f>data!$B$9</f>
+      </c>
+      <c r="B41" s="14" t="str">
+        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C41" s="14" t="str">
+        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D41" s="14" t="str">
+        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),1,0),0)+IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),1,0),0)</f>
+      </c>
+      <c r="E41" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F41" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I41" s="14" t="str">
+        <f>data!$B$21</f>
+      </c>
+      <c r="J41" s="14" t="str">
+        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K41" s="14" t="str">
+        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L41" s="14" t="str">
+        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),1,0),0)+IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),1,0),0)</f>
+      </c>
+      <c r="M41" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N41" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="str">
+        <f>data!$B$10</f>
+      </c>
+      <c r="B42" s="14" t="str">
+        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C42" s="14" t="str">
+        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D42" s="14" t="str">
+        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),1,0),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),1,0),0)</f>
+      </c>
+      <c r="E42" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F42" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I42" s="14" t="str">
+        <f>data!$B$22</f>
+      </c>
+      <c r="J42" s="14" t="str">
+        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K42" s="14" t="str">
+        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L42" s="14" t="str">
+        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),1,0),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),1,0),0)</f>
+      </c>
+      <c r="M42" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N42" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="str">
+        <f>data!$B$11</f>
+      </c>
+      <c r="B43" s="14" t="str">
+        <f>IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C43" s="14" t="str">
+        <f>IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D43" s="14" t="str">
+        <f>IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),1,0),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),1,0),0)</f>
+      </c>
+      <c r="E43" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F43" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I43" s="14" t="str">
+        <f>data!$B$23</f>
+      </c>
+      <c r="J43" s="14" t="str">
+        <f>IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K43" s="14" t="str">
+        <f>IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L43" s="14" t="str">
+        <f>IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),1,0),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),1,0),0)</f>
+      </c>
+      <c r="M43" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N43" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="45">
+      <c r="F45" t="s">
+        <v>103</v>
+      </c>
+      <c r="G45" s="19"/>
+      <c r="N45" t="s">
+        <v>103</v>
+      </c>
+      <c r="O45" s="19"/>
+    </row>
+    <row r="46">
+      <c r="F46" t="s">
+        <v>104</v>
+      </c>
+      <c r="G46" s="19"/>
+      <c r="N46" t="s">
+        <v>104</v>
+      </c>
+      <c r="O46" s="19"/>
+    </row>
+    <row r="47">
+      <c r="F47" t="s">
+        <v>105</v>
+      </c>
+      <c r="G47" s="19"/>
+      <c r="N47" t="s">
+        <v>105</v>
+      </c>
+      <c r="O47" s="19"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="str">
+        <f>data!$A$14</f>
+      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="I50" s="13" t="str">
+        <f>data!$A$26</f>
+      </c>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="13"/>
+      <c r="M50" s="13"/>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="I51" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="L51" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="O51" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="str">
+        <f>data!$B$13</f>
+      </c>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="14" t="str">
+        <f>data!$B$12</f>
+      </c>
+      <c r="I52" s="14" t="str">
+        <f>data!$B$25</f>
+      </c>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
+      <c r="L52" s="18"/>
+      <c r="M52" s="18"/>
+      <c r="N52" s="18"/>
+      <c r="O52" s="14" t="str">
+        <f>data!$B$24</f>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="str">
         <f>data!$B$14</f>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14" t="str">
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="14" t="str">
+        <f>data!$B$12</f>
+      </c>
+      <c r="I53" s="14" t="str">
+        <f>data!$B$26</f>
+      </c>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="18"/>
+      <c r="M53" s="18"/>
+      <c r="N53" s="18"/>
+      <c r="O53" s="14" t="str">
+        <f>data!$B$24</f>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="str">
+        <f>data!$B$14</f>
+      </c>
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="14" t="str">
         <f>data!$B$13</f>
       </c>
-      <c r="I36" s="14" t="str">
+      <c r="I54" s="14" t="str">
         <f>data!$B$26</f>
       </c>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14" t="str">
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="18"/>
+      <c r="M54" s="18"/>
+      <c r="N54" s="18"/>
+      <c r="O54" s="14" t="str">
         <f>data!$B$25</f>
       </c>
     </row>
-    <row r="38">
-      <c r="F38" t="s">
+    <row r="56">
+      <c r="A56" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="G38" s="15"/>
-      <c r="N38" t="s">
+      <c r="B56" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F56" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I56" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="O38" s="15"/>
-    </row>
-    <row r="39">
-      <c r="F39" t="s">
+      <c r="J56" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="G39" s="15"/>
-      <c r="N39" t="s">
-        <v>98</v>
-      </c>
-      <c r="O39" s="15"/>
-    </row>
-    <row r="40">
-      <c r="F40" t="s">
+      <c r="K56" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="G40" s="15"/>
-      <c r="N40" t="s">
-        <v>99</v>
-      </c>
-      <c r="O40" s="15"/>
+      <c r="L56" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="M56" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="N56" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="str">
+        <f>data!$B$12</f>
+      </c>
+      <c r="B57" s="14" t="str">
+        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C57" s="14" t="str">
+        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D57" s="14" t="str">
+        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),1,0),0)+IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),1,0),0)</f>
+      </c>
+      <c r="E57" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F57" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I57" s="14" t="str">
+        <f>data!$B$24</f>
+      </c>
+      <c r="J57" s="14" t="str">
+        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K57" s="14" t="str">
+        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L57" s="14" t="str">
+        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),1,0),0)+IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),1,0),0)</f>
+      </c>
+      <c r="M57" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N57" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="str">
+        <f>data!$B$13</f>
+      </c>
+      <c r="B58" s="14" t="str">
+        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C58" s="14" t="str">
+        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D58" s="14" t="str">
+        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),1,0),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),1,0),0)</f>
+      </c>
+      <c r="E58" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F58" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I58" s="14" t="str">
+        <f>data!$B$25</f>
+      </c>
+      <c r="J58" s="14" t="str">
+        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K58" s="14" t="str">
+        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L58" s="14" t="str">
+        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),1,0),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),1,0),0)</f>
+      </c>
+      <c r="M58" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N58" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="str">
+        <f>data!$B$14</f>
+      </c>
+      <c r="B59" s="14" t="str">
+        <f>IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C59" s="14" t="str">
+        <f>IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D59" s="14" t="str">
+        <f>IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),1,0),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),1,0),0)</f>
+      </c>
+      <c r="E59" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F59" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="I59" s="14" t="str">
+        <f>data!$B$26</f>
+      </c>
+      <c r="J59" s="14" t="str">
+        <f>IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K59" s="14" t="str">
+        <f>IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L59" s="14" t="str">
+        <f>IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),1,0),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),1,0),0)</f>
+      </c>
+      <c r="M59" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N59" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))</f>
+      </c>
+    </row>
+    <row r="61">
+      <c r="F61" t="s">
+        <v>103</v>
+      </c>
+      <c r="G61" s="19"/>
+      <c r="N61" t="s">
+        <v>103</v>
+      </c>
+      <c r="O61" s="19"/>
+    </row>
+    <row r="62">
+      <c r="F62" t="s">
+        <v>104</v>
+      </c>
+      <c r="G62" s="19"/>
+      <c r="N62" t="s">
+        <v>104</v>
+      </c>
+      <c r="O62" s="19"/>
+    </row>
+    <row r="63">
+      <c r="F63" t="s">
+        <v>105</v>
+      </c>
+      <c r="G63" s="19"/>
+      <c r="N63" t="s">
+        <v>105</v>
+      </c>
+      <c r="O63" s="19"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="I2:O2"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="I12:O12"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="I22:O22"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="I32:O32"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="I18:O18"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="I34:O34"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="I50:O50"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageSetup fitToHeight="0" fitToWidth="2" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
-  <rowBreaks/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="33" max="16383" man="true"/>
+  </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="1048575" man="true"/>
   </colBreaks>
@@ -3039,14 +3688,15 @@
     <col customWidth="true" max="4" min="4" width="3"/>
     <col customWidth="true" max="6" min="5" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
-    <col customWidth="true" max="8" min="8" width="2"/>
+    <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
     <col customWidth="true" max="11" min="10" width="5"/>
     <col customWidth="true" max="12" min="12" width="3"/>
     <col customWidth="true" max="14" min="13" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="16" min="16" width="2"/>
-    <col customWidth="true" max="20" min="17" width="10.83"/>
+    <col customWidth="true" max="18" min="16" width="5"/>
+    <col customWidth="true" max="19" min="19" width="30"/>
+    <col customWidth="true" max="20" min="20" width="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3071,7 +3721,7 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -3080,7 +3730,7 @@
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
       <c r="I2" s="13" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
@@ -3111,51 +3761,51 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G19)</f>
-      </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G30)</f>
+      </c>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G8)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G13)</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G9)</f>
-      </c>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G14)</f>
+      </c>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G18)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G29)</f>
       </c>
     </row>
     <row r="6">
       <c r="F6" t="s">
-        <v>125</v>
-      </c>
-      <c r="G6" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="G6" s="19"/>
       <c r="N6" t="s">
-        <v>125</v>
-      </c>
-      <c r="O6" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="O6" s="19"/>
     </row>
     <row r="7">
       <c r="F7" t="s">
-        <v>126</v>
-      </c>
-      <c r="G7" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="G7" s="19"/>
       <c r="N7" t="s">
-        <v>126</v>
-      </c>
-      <c r="O7" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="O7" s="19"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3164,7 +3814,7 @@
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="I10" s="13" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
@@ -3195,51 +3845,51 @@
     </row>
     <row r="12">
       <c r="A12" s="14" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G39)</f>
-      </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G62)</f>
+      </c>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G28)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G45)</f>
       </c>
       <c r="I12" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G29)</f>
-      </c>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G46)</f>
+      </c>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
       <c r="O12" s="14" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G38)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G61)</f>
       </c>
     </row>
     <row r="14">
       <c r="F14" t="s">
-        <v>125</v>
-      </c>
-      <c r="G14" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="G14" s="19"/>
       <c r="N14" t="s">
-        <v>125</v>
-      </c>
-      <c r="O14" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="O14" s="19"/>
     </row>
     <row r="15">
       <c r="F15" t="s">
-        <v>126</v>
-      </c>
-      <c r="G15" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="G15" s="19"/>
       <c r="N15" t="s">
-        <v>126</v>
-      </c>
-      <c r="O15" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="O15" s="19"/>
     </row>
     <row r="18">
       <c r="A18" s="13" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -3248,7 +3898,7 @@
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
       <c r="I18" s="13" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
@@ -3279,51 +3929,51 @@
     </row>
     <row r="20">
       <c r="A20" s="14" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O19)</f>
-      </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O30)</f>
+      </c>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
       <c r="G20" s="14" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O8)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O13)</f>
       </c>
       <c r="I20" s="14" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O9)</f>
-      </c>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O14)</f>
+      </c>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
       <c r="O20" s="14" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O18)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O29)</f>
       </c>
     </row>
     <row r="22">
       <c r="F22" t="s">
-        <v>125</v>
-      </c>
-      <c r="G22" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="G22" s="19"/>
       <c r="N22" t="s">
-        <v>125</v>
-      </c>
-      <c r="O22" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="O22" s="19"/>
     </row>
     <row r="23">
       <c r="F23" t="s">
-        <v>126</v>
-      </c>
-      <c r="G23" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="G23" s="19"/>
       <c r="N23" t="s">
-        <v>126</v>
-      </c>
-      <c r="O23" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="O23" s="19"/>
     </row>
     <row r="26">
       <c r="A26" s="13" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
@@ -3332,7 +3982,7 @@
       <c r="F26" s="13"/>
       <c r="G26" s="13"/>
       <c r="I26" s="13" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
@@ -3363,51 +4013,51 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O39)</f>
-      </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O62)</f>
+      </c>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="14" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O28)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O45)</f>
       </c>
       <c r="I28" s="14" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O29)</f>
-      </c>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="14"/>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O46)</f>
+      </c>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
       <c r="O28" s="14" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O38)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O61)</f>
       </c>
     </row>
     <row r="30">
       <c r="F30" t="s">
-        <v>125</v>
-      </c>
-      <c r="G30" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="G30" s="19"/>
       <c r="N30" t="s">
-        <v>125</v>
-      </c>
-      <c r="O30" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="O30" s="19"/>
     </row>
     <row r="31">
       <c r="F31" t="s">
-        <v>126</v>
-      </c>
-      <c r="G31" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="G31" s="19"/>
       <c r="N31" t="s">
-        <v>126</v>
-      </c>
-      <c r="O31" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="O31" s="19"/>
     </row>
     <row r="39">
       <c r="A39" s="13" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
@@ -3416,7 +4066,7 @@
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
       <c r="I39" s="13" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J39" s="13"/>
       <c r="K39" s="13"/>
@@ -3449,49 +4099,49 @@
       <c r="A41" s="14" t="str">
         <f>CONCATENATE("M 2 ",G14)</f>
       </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
       <c r="G41" s="14" t="str">
         <f>CONCATENATE("M 1 ",G6)</f>
       </c>
       <c r="I41" s="14" t="str">
         <f>CONCATENATE("M 6 ",O14)</f>
       </c>
-      <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
+      <c r="N41" s="18"/>
       <c r="O41" s="14" t="str">
         <f>CONCATENATE("M 5 ",O6)</f>
       </c>
     </row>
     <row r="43">
       <c r="F43" t="s">
-        <v>125</v>
-      </c>
-      <c r="G43" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="G43" s="19"/>
       <c r="N43" t="s">
-        <v>125</v>
-      </c>
-      <c r="O43" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="O43" s="19"/>
     </row>
     <row r="44">
       <c r="F44" t="s">
-        <v>126</v>
-      </c>
-      <c r="G44" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="G44" s="19"/>
       <c r="N44" t="s">
-        <v>126</v>
-      </c>
-      <c r="O44" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="O44" s="19"/>
     </row>
     <row r="47">
       <c r="A47" s="13" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
@@ -3500,7 +4150,7 @@
       <c r="F47" s="13"/>
       <c r="G47" s="13"/>
       <c r="I47" s="13" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="J47" s="13"/>
       <c r="K47" s="13"/>
@@ -3533,49 +4183,49 @@
       <c r="A49" s="14" t="str">
         <f>CONCATENATE("M 4 ",G30)</f>
       </c>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
       <c r="G49" s="14" t="str">
         <f>CONCATENATE("M 3 ",G22)</f>
       </c>
       <c r="I49" s="14" t="str">
         <f>CONCATENATE("M 8 ",O30)</f>
       </c>
-      <c r="J49" s="14"/>
-      <c r="K49" s="14"/>
-      <c r="L49" s="14"/>
-      <c r="M49" s="14"/>
-      <c r="N49" s="14"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="18"/>
+      <c r="N49" s="18"/>
       <c r="O49" s="14" t="str">
         <f>CONCATENATE("M 7 ",O22)</f>
       </c>
     </row>
     <row r="51">
       <c r="F51" t="s">
-        <v>125</v>
-      </c>
-      <c r="G51" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="G51" s="19"/>
       <c r="N51" t="s">
-        <v>125</v>
-      </c>
-      <c r="O51" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="O51" s="19"/>
     </row>
     <row r="52">
       <c r="F52" t="s">
-        <v>126</v>
-      </c>
-      <c r="G52" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="G52" s="19"/>
       <c r="N52" t="s">
-        <v>126</v>
-      </c>
-      <c r="O52" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="O52" s="19"/>
     </row>
     <row r="60">
       <c r="A60" s="13" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B60" s="13"/>
       <c r="C60" s="13"/>
@@ -3584,7 +4234,7 @@
       <c r="F60" s="13"/>
       <c r="G60" s="13"/>
       <c r="I60" s="13" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J60" s="13"/>
       <c r="K60" s="13"/>
@@ -3617,49 +4267,49 @@
       <c r="A62" s="14" t="str">
         <f>CONCATENATE("M 10 ",G51)</f>
       </c>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
       <c r="G62" s="14" t="str">
         <f>CONCATENATE("M 9 ",G43)</f>
       </c>
       <c r="I62" s="14" t="str">
         <f>CONCATENATE("M 12 ",O51)</f>
       </c>
-      <c r="J62" s="14"/>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14"/>
-      <c r="M62" s="14"/>
-      <c r="N62" s="14"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="18"/>
+      <c r="L62" s="18"/>
+      <c r="M62" s="18"/>
+      <c r="N62" s="18"/>
       <c r="O62" s="14" t="str">
         <f>CONCATENATE("M 11 ",O43)</f>
       </c>
     </row>
     <row r="64">
       <c r="F64" t="s">
-        <v>125</v>
-      </c>
-      <c r="G64" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="G64" s="19"/>
       <c r="N64" t="s">
-        <v>125</v>
-      </c>
-      <c r="O64" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="O64" s="19"/>
     </row>
     <row r="65">
       <c r="F65" t="s">
-        <v>126</v>
-      </c>
-      <c r="G65" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="G65" s="19"/>
       <c r="N65" t="s">
-        <v>126</v>
-      </c>
-      <c r="O65" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="O65" s="19"/>
     </row>
     <row r="73">
       <c r="A73" s="13" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B73" s="13"/>
       <c r="C73" s="13"/>
@@ -3683,28 +4333,29 @@
       <c r="A75" s="14" t="str">
         <f>CONCATENATE("M 14 ",O64)</f>
       </c>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
       <c r="G75" s="14" t="str">
         <f>CONCATENATE("M 13 ",G64)</f>
       </c>
     </row>
     <row r="77">
       <c r="F77" t="s">
-        <v>125</v>
-      </c>
-      <c r="G77" s="15"/>
+        <v>131</v>
+      </c>
+      <c r="G77" s="19"/>
     </row>
     <row r="78">
       <c r="F78" t="s">
-        <v>126</v>
-      </c>
-      <c r="G78" s="15"/>
+        <v>132</v>
+      </c>
+      <c r="G78" s="19"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="17">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:O1"/>
@@ -3765,174 +4416,175 @@
       <c r="P1" s="13"/>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="str">
+      <c r="A4" s="24" t="str">
         <f>data!$A$5</f>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="str">
+      <c r="A5" s="25" t="str">
         <f>"1. " &amp; data!$B$3</f>
       </c>
-      <c r="C5" s="21" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G8)</f>
+      <c r="C5" s="23" t="str">
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G13)</f>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="str">
+      <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$4</f>
       </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="19">
+      <c r="D6" s="22"/>
+      <c r="E6" s="21">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="str">
+      <c r="A7" s="27" t="str">
         <f>"3. " &amp; data!$B$5</f>
       </c>
-      <c r="C7" s="21" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G19)</f>
+      <c r="C7" s="23" t="str">
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G30)</f>
       </c>
       <c r="D7" s="15"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="18"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8">
-      <c r="A8" s="20"/>
-      <c r="G8" s="19">
+      <c r="A8" s="22"/>
+      <c r="G8" s="21">
         <v>9</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="str">
+      <c r="A9" s="24" t="str">
         <f>data!$A$8</f>
       </c>
-      <c r="C9" s="21" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G28)</f>
-      </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="18"/>
+      <c r="C9" s="23" t="str">
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G45)</f>
+      </c>
+      <c r="G9" s="20"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="20"/>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="str">
+      <c r="A10" s="25" t="str">
         <f>"1. " &amp; data!$B$6</f>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="19">
+      <c r="D10" s="22"/>
+      <c r="E10" s="21">
         <v>2</v>
       </c>
       <c r="F10" s="15"/>
-      <c r="G10" s="18"/>
-      <c r="I10" s="18"/>
+      <c r="G10" s="20"/>
+      <c r="I10" s="20"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="str">
+      <c r="A11" s="26" t="str">
         <f>"2. " &amp; data!$B$7</f>
       </c>
-      <c r="C11" s="21" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G39)</f>
+      <c r="C11" s="23" t="str">
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G62)</f>
       </c>
       <c r="D11" s="15"/>
-      <c r="E11" s="18"/>
-      <c r="I11" s="18"/>
+      <c r="E11" s="20"/>
+      <c r="I11" s="20"/>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="str">
+      <c r="A12" s="27" t="str">
         <f>"3. " &amp; data!$B$8</f>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="21">
         <v>13</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20"/>
-      <c r="C13" s="21" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O8)</f>
-      </c>
-      <c r="I13" s="18"/>
+      <c r="A13" s="22"/>
+      <c r="C13" s="23" t="str">
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O13)</f>
+      </c>
+      <c r="I13" s="20"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="str">
+      <c r="A14" s="24" t="str">
         <f>data!$A$11</f>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="19">
+      <c r="D14" s="22"/>
+      <c r="E14" s="21">
         <v>3</v>
       </c>
-      <c r="I14" s="18"/>
+      <c r="I14" s="20"/>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="str">
+      <c r="A15" s="25" t="str">
         <f>"1. " &amp; data!$B$9</f>
       </c>
-      <c r="C15" s="21" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O19)</f>
+      <c r="C15" s="23" t="str">
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O30)</f>
       </c>
       <c r="D15" s="15"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="18"/>
-      <c r="I15" s="18"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="20"/>
+      <c r="I15" s="20"/>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="str">
+      <c r="A16" s="26" t="str">
         <f>"2. " &amp; data!$B$10</f>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="21">
         <v>10</v>
       </c>
       <c r="H16" s="15"/>
-      <c r="I16" s="18"/>
+      <c r="I16" s="20"/>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="str">
+      <c r="A17" s="27" t="str">
         <f>"3. " &amp; data!$B$11</f>
       </c>
-      <c r="C17" s="21" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O28)</f>
-      </c>
-      <c r="G17" s="18"/>
+      <c r="C17" s="23" t="str">
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O45)</f>
+      </c>
+      <c r="G17" s="20"/>
     </row>
     <row r="18">
-      <c r="A18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="19">
+      <c r="A18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="21">
         <v>4</v>
       </c>
       <c r="F18" s="15"/>
-      <c r="G18" s="18"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="str">
+      <c r="A19" s="24" t="str">
         <f>data!$A$14</f>
       </c>
-      <c r="C19" s="21" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O39)</f>
+      <c r="C19" s="23" t="str">
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O62)</f>
       </c>
       <c r="D19" s="15"/>
-      <c r="E19" s="18"/>
+      <c r="E19" s="20"/>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="str">
+      <c r="A20" s="25" t="str">
         <f>"1. " &amp; data!$B$12</f>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="str">
+      <c r="A21" s="26" t="str">
         <f>"2. " &amp; data!$B$13</f>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="str">
+      <c r="A22" s="27" t="str">
         <f>"3. " &amp; data!$B$14</f>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20"/>
+      <c r="A23" s="22"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -3971,174 +4623,175 @@
       <c r="P1" s="13"/>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="str">
+      <c r="A4" s="24" t="str">
         <f>data!$A$17</f>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="str">
+      <c r="A5" s="25" t="str">
         <f>"1. " &amp; data!$B$15</f>
       </c>
-      <c r="C5" s="21" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G18)</f>
+      <c r="C5" s="23" t="str">
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G29)</f>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="str">
+      <c r="A6" s="26" t="str">
         <f>"2. " &amp; data!$B$16</f>
       </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="19">
+      <c r="D6" s="22"/>
+      <c r="E6" s="21">
         <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="str">
+      <c r="A7" s="27" t="str">
         <f>"3. " &amp; data!$B$17</f>
       </c>
-      <c r="C7" s="21" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G9)</f>
+      <c r="C7" s="23" t="str">
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G14)</f>
       </c>
       <c r="D7" s="15"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="18"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8">
-      <c r="A8" s="20"/>
-      <c r="G8" s="19">
+      <c r="A8" s="22"/>
+      <c r="G8" s="21">
         <v>11</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="str">
+      <c r="A9" s="24" t="str">
         <f>data!$A$20</f>
       </c>
-      <c r="C9" s="21" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G38)</f>
-      </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="18"/>
+      <c r="C9" s="23" t="str">
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G61)</f>
+      </c>
+      <c r="G9" s="20"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="20"/>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="str">
+      <c r="A10" s="25" t="str">
         <f>"1. " &amp; data!$B$18</f>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="19">
+      <c r="D10" s="22"/>
+      <c r="E10" s="21">
         <v>6</v>
       </c>
       <c r="F10" s="15"/>
-      <c r="G10" s="18"/>
-      <c r="I10" s="18"/>
+      <c r="G10" s="20"/>
+      <c r="I10" s="20"/>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="str">
+      <c r="A11" s="26" t="str">
         <f>"2. " &amp; data!$B$19</f>
       </c>
-      <c r="C11" s="21" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G29)</f>
+      <c r="C11" s="23" t="str">
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G46)</f>
       </c>
       <c r="D11" s="15"/>
-      <c r="E11" s="18"/>
-      <c r="I11" s="18"/>
+      <c r="E11" s="20"/>
+      <c r="I11" s="20"/>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="str">
+      <c r="A12" s="27" t="str">
         <f>"3. " &amp; data!$B$20</f>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="21">
         <v>14</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20"/>
-      <c r="C13" s="21" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O18)</f>
-      </c>
-      <c r="I13" s="18"/>
+      <c r="A13" s="22"/>
+      <c r="C13" s="23" t="str">
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O29)</f>
+      </c>
+      <c r="I13" s="20"/>
     </row>
     <row r="14">
-      <c r="A14" s="22" t="str">
+      <c r="A14" s="24" t="str">
         <f>data!$A$23</f>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="19">
+      <c r="D14" s="22"/>
+      <c r="E14" s="21">
         <v>7</v>
       </c>
-      <c r="I14" s="18"/>
+      <c r="I14" s="20"/>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="str">
+      <c r="A15" s="25" t="str">
         <f>"1. " &amp; data!$B$21</f>
       </c>
-      <c r="C15" s="21" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O9)</f>
+      <c r="C15" s="23" t="str">
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O14)</f>
       </c>
       <c r="D15" s="15"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="18"/>
-      <c r="I15" s="18"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="20"/>
+      <c r="I15" s="20"/>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="str">
+      <c r="A16" s="26" t="str">
         <f>"2. " &amp; data!$B$22</f>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="21">
         <v>12</v>
       </c>
       <c r="H16" s="15"/>
-      <c r="I16" s="18"/>
+      <c r="I16" s="20"/>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="str">
+      <c r="A17" s="27" t="str">
         <f>"3. " &amp; data!$B$23</f>
       </c>
-      <c r="C17" s="21" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O38)</f>
-      </c>
-      <c r="G17" s="18"/>
+      <c r="C17" s="23" t="str">
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O61)</f>
+      </c>
+      <c r="G17" s="20"/>
     </row>
     <row r="18">
-      <c r="A18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="19">
+      <c r="A18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="21">
         <v>8</v>
       </c>
       <c r="F18" s="15"/>
-      <c r="G18" s="18"/>
+      <c r="G18" s="20"/>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="str">
+      <c r="A19" s="24" t="str">
         <f>data!$A$26</f>
       </c>
-      <c r="C19" s="21" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O29)</f>
+      <c r="C19" s="23" t="str">
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O46)</f>
       </c>
       <c r="D19" s="15"/>
-      <c r="E19" s="18"/>
+      <c r="E19" s="20"/>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="str">
+      <c r="A20" s="25" t="str">
         <f>"1. " &amp; data!$B$24</f>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="str">
+      <c r="A21" s="26" t="str">
         <f>"2. " &amp; data!$B$25</f>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="str">
+      <c r="A22" s="27" t="str">
         <f>"3. " &amp; data!$B$26</f>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20"/>
+      <c r="A23" s="22"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>

--- a/pools-example-medium-seeded.xlsx
+++ b/pools-example-medium-seeded.xlsx
@@ -20,10 +20,10 @@
   </sheets>
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$23</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$O$65</definedName>
+    <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$P$69</definedName>
     <definedName localSheetId="7" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$12</definedName>
     <definedName localSheetId="8" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$12</definedName>
-    <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$O$85</definedName>
+    <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$85</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
@@ -341,13 +341,19 @@
     <t>PL</t>
   </si>
   <si>
-    <t xml:space="preserve">1. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. </t>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Ranking</t>
+  </si>
+  <si>
+    <t>1.</t>
+  </si>
+  <si>
+    <t>2.</t>
+  </si>
+  <si>
+    <t>3.</t>
   </si>
   <si>
     <t>A1</t>
@@ -423,12 +429,6 @@
   </si>
   <si>
     <t>Round 1 - Match 1</t>
-  </si>
-  <si>
-    <t>1.</t>
-  </si>
-  <si>
-    <t>2.</t>
   </si>
   <si>
     <t>Round 1 - Match 5</t>
@@ -1473,98 +1473,98 @@
   <sheetData>
     <row r="1" ht="270" customHeight="true">
       <c r="A1" s="28" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B1" s="29" t="str">
-        <f>data!D3</f>
+        <f>'data'!D3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
       <c r="A2" s="28" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B2" s="29" t="str">
-        <f>data!D4</f>
+        <f>'data'!D4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="28" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B3" s="29" t="str">
-        <f>data!D5</f>
+        <f>'data'!D5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
       <c r="A4" s="28" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B4" s="29" t="str">
-        <f>data!D6</f>
+        <f>'data'!D6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
       <c r="A5" s="28" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B5" s="29" t="str">
-        <f>data!D7</f>
+        <f>'data'!D7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B6" s="29" t="str">
-        <f>data!D8</f>
+        <f>'data'!D8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B7" s="29" t="str">
-        <f>data!D9</f>
+        <f>'data'!D9</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
       <c r="A8" s="28" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B8" s="29" t="str">
-        <f>data!D10</f>
+        <f>'data'!D10</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
       <c r="A9" s="28" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B9" s="29" t="str">
-        <f>data!D11</f>
+        <f>'data'!D11</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
       <c r="A10" s="28" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B10" s="29" t="str">
-        <f>data!D12</f>
+        <f>'data'!D12</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
       <c r="A11" s="28" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B11" s="29" t="str">
-        <f>data!D13</f>
+        <f>'data'!D13</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
       <c r="A12" s="28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B12" s="29" t="str">
-        <f>data!D14</f>
+        <f>'data'!D14</f>
       </c>
     </row>
   </sheetData>
@@ -1591,98 +1591,98 @@
   <sheetData>
     <row r="1" ht="270" customHeight="true">
       <c r="A1" s="28" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B1" s="29" t="str">
-        <f>data!D15</f>
+        <f>'data'!D15</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
       <c r="A2" s="28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B2" s="29" t="str">
-        <f>data!D16</f>
+        <f>'data'!D16</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
       <c r="A3" s="28" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B3" s="29" t="str">
-        <f>data!D17</f>
+        <f>'data'!D17</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
       <c r="A4" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B4" s="29" t="str">
-        <f>data!D18</f>
+        <f>'data'!D18</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
       <c r="A5" s="28" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B5" s="29" t="str">
-        <f>data!D19</f>
+        <f>'data'!D19</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
       <c r="A6" s="28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B6" s="29" t="str">
-        <f>data!D20</f>
+        <f>'data'!D20</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
       <c r="A7" s="28" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B7" s="29" t="str">
-        <f>data!D21</f>
+        <f>'data'!D21</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
       <c r="A8" s="28" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B8" s="29" t="str">
-        <f>data!D22</f>
+        <f>'data'!D22</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
       <c r="A9" s="28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B9" s="29" t="str">
-        <f>data!D23</f>
+        <f>'data'!D23</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
       <c r="A10" s="28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B10" s="29" t="str">
-        <f>data!D24</f>
+        <f>'data'!D24</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
       <c r="A11" s="28" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B11" s="29" t="str">
-        <f>data!D25</f>
+        <f>'data'!D25</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
       <c r="A12" s="28" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B12" s="29" t="str">
-        <f>data!D26</f>
+        <f>'data'!D26</f>
       </c>
     </row>
   </sheetData>
@@ -1708,242 +1708,242 @@
   <sheetData>
     <row r="1" ht="390" customHeight="true">
       <c r="A1" s="30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" ht="390" customHeight="true">
       <c r="A2" s="30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" ht="390" customHeight="true">
       <c r="A3" s="30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" ht="390" customHeight="true">
       <c r="A4" s="30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" ht="390" customHeight="true">
       <c r="A5" s="30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" ht="390" customHeight="true">
       <c r="A6" s="30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" ht="390" customHeight="true">
       <c r="A7" s="30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" ht="390" customHeight="true">
       <c r="A8" s="30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" ht="390" customHeight="true">
       <c r="A9" s="30" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" ht="390" customHeight="true">
       <c r="A10" s="30" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" ht="390" customHeight="true">
       <c r="A11" s="30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" ht="390" customHeight="true">
       <c r="A12" s="30" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" ht="390" customHeight="true">
       <c r="A13" s="30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" ht="390" customHeight="true">
       <c r="A14" s="30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" ht="390" customHeight="true">
       <c r="A15" s="30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" ht="390" customHeight="true">
       <c r="A16" s="30" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" ht="390" customHeight="true">
       <c r="A17" s="30" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" ht="390" customHeight="true">
       <c r="A18" s="30" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" ht="390" customHeight="true">
       <c r="A19" s="30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" ht="390" customHeight="true">
       <c r="A20" s="30" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" ht="390" customHeight="true">
       <c r="A21" s="30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" ht="390" customHeight="true">
       <c r="A22" s="30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" ht="390" customHeight="true">
       <c r="A23" s="30" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" ht="390" customHeight="true">
       <c r="A24" s="30" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="25" ht="390" customHeight="true">
       <c r="A25" s="30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" ht="390" customHeight="true">
       <c r="A26" s="30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" ht="390" customHeight="true">
       <c r="A27" s="30" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" ht="390" customHeight="true">
       <c r="A28" s="30" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" ht="390" customHeight="true">
       <c r="A29" s="30" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" ht="390" customHeight="true">
       <c r="A30" s="30" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" ht="390" customHeight="true">
       <c r="A31" s="30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" ht="390" customHeight="true">
       <c r="A32" s="30" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" ht="390" customHeight="true">
       <c r="A33" s="30" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" ht="390" customHeight="true">
       <c r="A34" s="30" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" ht="390" customHeight="true">
       <c r="A35" s="30" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" ht="390" customHeight="true">
       <c r="A36" s="30" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" ht="390" customHeight="true">
       <c r="A37" s="30" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" ht="390" customHeight="true">
       <c r="A38" s="30" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" ht="390" customHeight="true">
       <c r="A39" s="30" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40" ht="390" customHeight="true">
       <c r="A40" s="30" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" ht="390" customHeight="true">
       <c r="A41" s="30" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" ht="390" customHeight="true">
       <c r="A42" s="30" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" ht="390" customHeight="true">
       <c r="A43" s="30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="44" ht="390" customHeight="true">
       <c r="A44" s="30" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" ht="390" customHeight="true">
       <c r="A45" s="30" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="46" ht="390" customHeight="true">
       <c r="A46" s="30" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="47" ht="390" customHeight="true">
       <c r="A47" s="30" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="48" ht="390" customHeight="true">
       <c r="A48" s="30" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2303,13 +2303,13 @@
     </row>
     <row r="5" ht="17" customHeight="true">
       <c r="B5" s="11" t="str">
-        <f>data!$A$5</f>
+        <f>'data'!$A$5</f>
       </c>
       <c r="D5" s="11" t="str">
-        <f>data!$A$14</f>
+        <f>'data'!$A$14</f>
       </c>
       <c r="F5" s="11" t="str">
-        <f>data!$A$23</f>
+        <f>'data'!$A$23</f>
       </c>
     </row>
     <row r="6" ht="17" customHeight="true">
@@ -2347,13 +2347,13 @@
     </row>
     <row r="11">
       <c r="B11" s="11" t="str">
-        <f>data!$A$8</f>
+        <f>'data'!$A$8</f>
       </c>
       <c r="D11" s="11" t="str">
-        <f>data!$A$17</f>
+        <f>'data'!$A$17</f>
       </c>
       <c r="F11" s="11" t="str">
-        <f>data!$A$26</f>
+        <f>'data'!$A$26</f>
       </c>
     </row>
     <row r="12">
@@ -2391,10 +2391,10 @@
     </row>
     <row r="17">
       <c r="B17" s="11" t="str">
-        <f>data!$A$11</f>
+        <f>'data'!$A$11</f>
       </c>
       <c r="D17" s="11" t="str">
-        <f>data!$A$20</f>
+        <f>'data'!$A$20</f>
       </c>
     </row>
     <row r="18">
@@ -2439,19 +2439,16 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="3" min="2" width="5"/>
-    <col customWidth="true" max="4" min="4" width="3"/>
-    <col customWidth="true" max="6" min="5" width="5"/>
+    <col customWidth="true" max="6" min="2" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
     <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
-    <col customWidth="true" max="11" min="10" width="5"/>
-    <col customWidth="true" max="12" min="12" width="3"/>
-    <col customWidth="true" max="14" min="13" width="5"/>
+    <col customWidth="true" max="14" min="10" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="18" min="16" width="5"/>
-    <col customWidth="true" max="19" min="19" width="30"/>
-    <col customWidth="true" max="20" min="20" width="2"/>
+    <col customWidth="true" max="16" min="16" width="5"/>
+    <col customWidth="true" max="20" min="17" width="10.83"/>
+    <col customWidth="true" hidden="true" max="21" min="21" width="9.140625"/>
+    <col customWidth="true" hidden="true" max="29" min="29" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2476,7 +2473,7 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="str">
-        <f>data!$A$5</f>
+        <f>'data'!$A$5</f>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -2485,7 +2482,7 @@
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
       <c r="I2" s="13" t="str">
-        <f>data!$A$17</f>
+        <f>'data'!$A$17</f>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
@@ -2516,7 +2513,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>data!$B$4</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -2524,10 +2521,10 @@
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>data!$B$3</f>
+        <f>'data'!$B$3</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>data!$B$16</f>
+        <f>'data'!$B$16</f>
       </c>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
@@ -2535,12 +2532,12 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>data!$B$15</f>
+        <f>'data'!$B$15</f>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="str">
-        <f>data!$B$5</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -2548,10 +2545,10 @@
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
       <c r="G5" s="14" t="str">
-        <f>data!$B$3</f>
+        <f>'data'!$B$3</f>
       </c>
       <c r="I5" s="14" t="str">
-        <f>data!$B$17</f>
+        <f>'data'!$B$17</f>
       </c>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
@@ -2559,12 +2556,12 @@
       <c r="M5" s="18"/>
       <c r="N5" s="18"/>
       <c r="O5" s="14" t="str">
-        <f>data!$B$15</f>
+        <f>'data'!$B$15</f>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="str">
-        <f>data!$B$5</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -2572,10 +2569,10 @@
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="G6" s="14" t="str">
-        <f>data!$B$4</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="I6" s="14" t="str">
-        <f>data!$B$17</f>
+        <f>'data'!$B$17</f>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
@@ -2583,7 +2580,7 @@
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
       <c r="O6" s="14" t="str">
-        <f>data!$B$16</f>
+        <f>'data'!$B$16</f>
       </c>
     </row>
     <row r="8">
@@ -2605,6 +2602,9 @@
       <c r="F8" s="13" t="s">
         <v>102</v>
       </c>
+      <c r="G8" s="13" t="s">
+        <v>103</v>
+      </c>
       <c r="I8" s="13" t="s">
         <v>97</v>
       </c>
@@ -2623,19 +2623,22 @@
       <c r="N8" s="13" t="s">
         <v>102</v>
       </c>
+      <c r="O8" s="13" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="str">
-        <f>data!$B$3</f>
+        <f>'data'!$B$3</f>
       </c>
       <c r="B9" s="14" t="str">
-        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="C9" s="14" t="str">
-        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="D9" s="14" t="str">
-        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),1,0),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="E9" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))</f>
@@ -2643,17 +2646,20 @@
       <c r="F9" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))</f>
       </c>
+      <c r="G9" s="18" t="str">
+        <f>RANK(U9,$U$9:$U$11)+COUNTIF($U$8:U8,U9)</f>
+      </c>
       <c r="I9" s="14" t="str">
-        <f>data!$B$15</f>
+        <f>'data'!$B$15</f>
       </c>
       <c r="J9" s="14" t="str">
-        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="K9" s="14" t="str">
-        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="L9" s="14" t="str">
-        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),1,0),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="M9" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))</f>
@@ -2661,19 +2667,28 @@
       <c r="N9" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))</f>
       </c>
+      <c r="O9" s="18" t="str">
+        <f>RANK(AC9,$AC$9:$AC$11)+COUNTIF($AC$8:AC8,AC9)</f>
+      </c>
+      <c r="U9" t="str">
+        <f>=(B9*1000000)-(C9*10000)+(D9*100)+(E9*1)-(F9*0.01)</f>
+      </c>
+      <c r="AC9" t="str">
+        <f>=(J9*1000000)-(K9*10000)+(L9*100)+(M9*1)-(N9*0.01)</f>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="str">
-        <f>data!$B$4</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="B10" s="14" t="str">
-        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="C10" s="14" t="str">
-        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="D10" s="14" t="str">
-        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x"),1,0),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="E10" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))</f>
@@ -2681,17 +2696,20 @@
       <c r="F10" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))</f>
       </c>
+      <c r="G10" s="18" t="str">
+        <f>RANK(U10,$U$9:$U$11)+COUNTIF($U$8:U9,U10)</f>
+      </c>
       <c r="I10" s="14" t="str">
-        <f>data!$B$16</f>
+        <f>'data'!$B$16</f>
       </c>
       <c r="J10" s="14" t="str">
-        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="K10" s="14" t="str">
-        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="L10" s="14" t="str">
-        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x"),1,0),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="M10" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))</f>
@@ -2699,19 +2717,28 @@
       <c r="N10" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))</f>
       </c>
+      <c r="O10" s="18" t="str">
+        <f>RANK(AC10,$AC$9:$AC$11)+COUNTIF($AC$8:AC9,AC10)</f>
+      </c>
+      <c r="U10" t="str">
+        <f>=(B10*1000000)-(C10*10000)+(D10*100)+(E10*1)-(F10*0.01)</f>
+      </c>
+      <c r="AC10" t="str">
+        <f>=(J10*1000000)-(K10*10000)+(L10*100)+(M10*1)-(N10*0.01)</f>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="str">
-        <f>data!$B$5</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="B11" s="14" t="str">
-        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="C11" s="14" t="str">
-        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="D11" s="14" t="str">
-        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x"),1,0),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="E11" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))</f>
@@ -2719,17 +2746,20 @@
       <c r="F11" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))</f>
       </c>
+      <c r="G11" s="18" t="str">
+        <f>RANK(U11,$U$9:$U$11)+COUNTIF($U$8:U10,U11)</f>
+      </c>
       <c r="I11" s="14" t="str">
-        <f>data!$B$17</f>
+        <f>'data'!$B$17</f>
       </c>
       <c r="J11" s="14" t="str">
-        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="K11" s="14" t="str">
-        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="L11" s="14" t="str">
-        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x"),1,0),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="M11" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))</f>
@@ -2737,104 +2767,111 @@
       <c r="N11" s="14" t="str">
         <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))</f>
       </c>
-    </row>
-    <row r="13">
-      <c r="F13" t="s">
-        <v>103</v>
-      </c>
-      <c r="G13" s="19"/>
-      <c r="N13" t="s">
-        <v>103</v>
-      </c>
-      <c r="O13" s="19"/>
+      <c r="O11" s="18" t="str">
+        <f>RANK(AC11,$AC$9:$AC$11)+COUNTIF($AC$8:AC10,AC11)</f>
+      </c>
+      <c r="U11" t="str">
+        <f>=(B11*1000000)-(C11*10000)+(D11*100)+(E11*1)-(F11*0.01)</f>
+      </c>
+      <c r="AC11" t="str">
+        <f>=(J11*1000000)-(K11*10000)+(L11*100)+(M11*1)-(N11*0.01)</f>
+      </c>
     </row>
     <row r="14">
-      <c r="F14" t="s">
+      <c r="F14" s="13"/>
+      <c r="G14" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="G14" s="19"/>
-      <c r="N14" t="s">
+      <c r="N14" s="13"/>
+      <c r="O14" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="O14" s="19"/>
     </row>
     <row r="15">
       <c r="F15" t="s">
         <v>105</v>
       </c>
-      <c r="G15" s="19"/>
+      <c r="G15" s="19" t="str">
+        <f>IFERROR(INDEX($A$9:$A$11, MATCH(1, $G$9:$G$11, 0)), "-")</f>
+      </c>
       <c r="N15" t="s">
         <v>105</v>
       </c>
-      <c r="O15" s="19"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="str">
-        <f>data!$A$8</f>
-      </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="I18" s="13" t="str">
-        <f>data!$A$20</f>
-      </c>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
+      <c r="O15" s="19" t="str">
+        <f>IFERROR(INDEX($I$9:$I$11, MATCH(1, $O$9:$O$11, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="16">
+      <c r="F16" t="s">
+        <v>106</v>
+      </c>
+      <c r="G16" s="19" t="str">
+        <f>IFERROR(INDEX($A$9:$A$11, MATCH(2, $G$9:$G$11, 0)), "-")</f>
+      </c>
+      <c r="N16" t="s">
+        <v>106</v>
+      </c>
+      <c r="O16" s="19" t="str">
+        <f>IFERROR(INDEX($I$9:$I$11, MATCH(2, $O$9:$O$11, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="17">
+      <c r="F17" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" s="19" t="str">
+        <f>IFERROR(INDEX($A$9:$A$11, MATCH(3, $G$9:$G$11, 0)), "-")</f>
+      </c>
+      <c r="N17" t="s">
+        <v>107</v>
+      </c>
+      <c r="O17" s="19" t="str">
+        <f>IFERROR(INDEX($I$9:$I$11, MATCH(3, $O$9:$O$11, 0)), "-")</f>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="13" t="str">
+        <f>'data'!$A$8</f>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="I19" s="13" t="str">
+        <f>'data'!$A$20</f>
+      </c>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="13"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D20" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="G20" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="I19" s="17" t="s">
+      <c r="I20" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="L19" s="14" t="s">
+      <c r="L20" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="O19" s="16" t="s">
+      <c r="O20" s="16" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="str">
-        <f>data!$B$7</f>
-      </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="14" t="str">
-        <f>data!$B$6</f>
-      </c>
-      <c r="I20" s="14" t="str">
-        <f>data!$B$19</f>
-      </c>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="14" t="str">
-        <f>data!$B$18</f>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="str">
-        <f>data!$B$8</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -2842,10 +2879,10 @@
       <c r="E21" s="18"/>
       <c r="F21" s="18"/>
       <c r="G21" s="14" t="str">
-        <f>data!$B$6</f>
+        <f>'data'!$B$6</f>
       </c>
       <c r="I21" s="14" t="str">
-        <f>data!$B$20</f>
+        <f>'data'!$B$19</f>
       </c>
       <c r="J21" s="18"/>
       <c r="K21" s="18"/>
@@ -2853,12 +2890,12 @@
       <c r="M21" s="18"/>
       <c r="N21" s="18"/>
       <c r="O21" s="14" t="str">
-        <f>data!$B$18</f>
+        <f>'data'!$B$18</f>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="str">
-        <f>data!$B$8</f>
+        <f>'data'!$B$8</f>
       </c>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -2866,10 +2903,10 @@
       <c r="E22" s="18"/>
       <c r="F22" s="18"/>
       <c r="G22" s="14" t="str">
-        <f>data!$B$7</f>
+        <f>'data'!$B$6</f>
       </c>
       <c r="I22" s="14" t="str">
-        <f>data!$B$20</f>
+        <f>'data'!$B$20</f>
       </c>
       <c r="J22" s="18"/>
       <c r="K22" s="18"/>
@@ -2877,282 +2914,322 @@
       <c r="M22" s="18"/>
       <c r="N22" s="18"/>
       <c r="O22" s="14" t="str">
-        <f>data!$B$19</f>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="s">
+        <f>'data'!$B$18</f>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="str">
+        <f>'data'!$B$8</f>
+      </c>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="14" t="str">
+        <f>'data'!$B$7</f>
+      </c>
+      <c r="I23" s="14" t="str">
+        <f>'data'!$B$20</f>
+      </c>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="14" t="str">
+        <f>'data'!$B$19</f>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B25" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C25" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D25" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E25" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="F24" s="13" t="s">
+      <c r="F25" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="I24" s="13" t="s">
+      <c r="G25" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="I25" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="J24" s="13" t="s">
+      <c r="J25" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="K24" s="13" t="s">
+      <c r="K25" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L24" s="13" t="s">
+      <c r="L25" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="M24" s="13" t="s">
+      <c r="M25" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="N24" s="13" t="s">
+      <c r="N25" s="13" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="str">
-        <f>data!$B$6</f>
-      </c>
-      <c r="B25" s="14" t="str">
-        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="C25" s="14" t="str">
-        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="D25" s="14" t="str">
-        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),1,0),0)+IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),1,0),0)</f>
-      </c>
-      <c r="E25" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F25" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="I25" s="14" t="str">
-        <f>data!$B$18</f>
-      </c>
-      <c r="J25" s="14" t="str">
-        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="K25" s="14" t="str">
-        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="L25" s="14" t="str">
-        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),1,0),0)+IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),1,0),0)</f>
-      </c>
-      <c r="M25" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="N25" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))</f>
+      <c r="O25" s="13" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="str">
-        <f>data!$B$7</f>
+        <f>'data'!$B$6</f>
       </c>
       <c r="B26" s="14" t="str">
-        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x",AND(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x",AND(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="C26" s="14" t="str">
-        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x",AND(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x",AND(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="D26" s="14" t="str">
-        <f>IF(OR(COUNTA(B20,C20,E20,F20)&gt;0,OR(D20="X",D20="x")),IF(OR(D20="X",D20="x"),1,0),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x",AND(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x",AND(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="E26" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F26" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G26" s="18" t="str">
+        <f>RANK(U26,$U$26:$U$28)+COUNTIF($U$25:U25,U26)</f>
       </c>
       <c r="I26" s="14" t="str">
-        <f>data!$B$19</f>
+        <f>'data'!$B$18</f>
       </c>
       <c r="J26" s="14" t="str">
-        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x",AND(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x",AND(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="K26" s="14" t="str">
-        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x",AND(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x",AND(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="L26" s="14" t="str">
-        <f>IF(OR(COUNTA(J20,K20,M20,N20)&gt;0,OR(L20="X",L20="x")),IF(OR(L20="X",L20="x"),1,0),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x",AND(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x",AND(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="M26" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N26" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N20," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O26" s="18" t="str">
+        <f>RANK(AC26,$AC$26:$AC$28)+COUNTIF($AC$25:AC25,AC26)</f>
+      </c>
+      <c r="U26" t="str">
+        <f>=(B26*1000000)-(C26*10000)+(D26*100)+(E26*1)-(F26*0.01)</f>
+      </c>
+      <c r="AC26" t="str">
+        <f>=(J26*1000000)-(K26*10000)+(L26*100)+(M26*1)-(N26*0.01)</f>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="str">
-        <f>data!$B$8</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="B27" s="14" t="str">
-        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x",AND(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),IF(OR(D23="X",D23="x",AND(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="C27" s="14" t="str">
-        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x",AND(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),IF(OR(D23="X",D23="x",AND(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="D27" s="14" t="str">
-        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x"),1,0),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x",AND(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),IF(OR(D23="X",D23="x",AND(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="E27" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F27" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G27" s="18" t="str">
+        <f>RANK(U27,$U$26:$U$28)+COUNTIF($U$25:U26,U27)</f>
       </c>
       <c r="I27" s="14" t="str">
-        <f>data!$B$20</f>
+        <f>'data'!$B$19</f>
       </c>
       <c r="J27" s="14" t="str">
-        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x",AND(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),IF(OR(L23="X",L23="x",AND(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="K27" s="14" t="str">
-        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x",AND(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),IF(OR(L23="X",L23="x",AND(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="L27" s="14" t="str">
-        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x"),1,0),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x",AND(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),IF(OR(L23="X",L23="x",AND(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="M27" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N27" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))</f>
-      </c>
-    </row>
-    <row r="29">
-      <c r="F29" t="s">
-        <v>103</v>
-      </c>
-      <c r="G29" s="19"/>
-      <c r="N29" t="s">
-        <v>103</v>
-      </c>
-      <c r="O29" s="19"/>
-    </row>
-    <row r="30">
-      <c r="F30" t="s">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O27" s="18" t="str">
+        <f>RANK(AC27,$AC$26:$AC$28)+COUNTIF($AC$25:AC26,AC27)</f>
+      </c>
+      <c r="U27" t="str">
+        <f>=(B27*1000000)-(C27*10000)+(D27*100)+(E27*1)-(F27*0.01)</f>
+      </c>
+      <c r="AC27" t="str">
+        <f>=(J27*1000000)-(K27*10000)+(L27*100)+(M27*1)-(N27*0.01)</f>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="str">
+        <f>'data'!$B$8</f>
+      </c>
+      <c r="B28" s="14" t="str">
+        <f>IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x",AND(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),IF(OR(D23="X",D23="x",AND(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C28" s="14" t="str">
+        <f>IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x",AND(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),IF(OR(D23="X",D23="x",AND(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D28" s="14" t="str">
+        <f>IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x",AND(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),IF(OR(D23="X",D23="x",AND(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="E28" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F28" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G28" s="18" t="str">
+        <f>RANK(U28,$U$26:$U$28)+COUNTIF($U$25:U27,U28)</f>
+      </c>
+      <c r="I28" s="14" t="str">
+        <f>'data'!$B$20</f>
+      </c>
+      <c r="J28" s="14" t="str">
+        <f>IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x",AND(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),IF(OR(L23="X",L23="x",AND(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K28" s="14" t="str">
+        <f>IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x",AND(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),IF(OR(L23="X",L23="x",AND(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L28" s="14" t="str">
+        <f>IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x",AND(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),IF(OR(L23="X",L23="x",AND(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="M28" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N28" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O28" s="18" t="str">
+        <f>RANK(AC28,$AC$26:$AC$28)+COUNTIF($AC$25:AC27,AC28)</f>
+      </c>
+      <c r="U28" t="str">
+        <f>=(B28*1000000)-(C28*10000)+(D28*100)+(E28*1)-(F28*0.01)</f>
+      </c>
+      <c r="AC28" t="str">
+        <f>=(J28*1000000)-(K28*10000)+(L28*100)+(M28*1)-(N28*0.01)</f>
+      </c>
+    </row>
+    <row r="31">
+      <c r="F31" s="13"/>
+      <c r="G31" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="G30" s="19"/>
-      <c r="N30" t="s">
+      <c r="N31" s="13"/>
+      <c r="O31" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="O30" s="19"/>
-    </row>
-    <row r="31">
-      <c r="F31" t="s">
+    </row>
+    <row r="32">
+      <c r="F32" t="s">
         <v>105</v>
       </c>
-      <c r="G31" s="19"/>
-      <c r="N31" t="s">
+      <c r="G32" s="19" t="str">
+        <f>IFERROR(INDEX($A$26:$A$28, MATCH(1, $G$26:$G$28, 0)), "-")</f>
+      </c>
+      <c r="N32" t="s">
         <v>105</v>
       </c>
-      <c r="O31" s="19"/>
+      <c r="O32" s="19" t="str">
+        <f>IFERROR(INDEX($I$26:$I$28, MATCH(1, $O$26:$O$28, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="33">
+      <c r="F33" t="s">
+        <v>106</v>
+      </c>
+      <c r="G33" s="19" t="str">
+        <f>IFERROR(INDEX($A$26:$A$28, MATCH(2, $G$26:$G$28, 0)), "-")</f>
+      </c>
+      <c r="N33" t="s">
+        <v>106</v>
+      </c>
+      <c r="O33" s="19" t="str">
+        <f>IFERROR(INDEX($I$26:$I$28, MATCH(2, $O$26:$O$28, 0)), "-")</f>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="str">
-        <f>data!$A$11</f>
-      </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="I34" s="13" t="str">
-        <f>data!$A$23</f>
-      </c>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="17" t="s">
+      <c r="F34" t="s">
+        <v>107</v>
+      </c>
+      <c r="G34" s="19" t="str">
+        <f>IFERROR(INDEX($A$26:$A$28, MATCH(3, $G$26:$G$28, 0)), "-")</f>
+      </c>
+      <c r="N34" t="s">
+        <v>107</v>
+      </c>
+      <c r="O34" s="19" t="str">
+        <f>IFERROR(INDEX($I$26:$I$28, MATCH(3, $O$26:$O$28, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="str">
+        <f>'data'!$A$11</f>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="I36" s="13" t="str">
+        <f>'data'!$A$23</f>
+      </c>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D37" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="16" t="s">
+      <c r="G37" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="I35" s="17" t="s">
+      <c r="I37" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="L35" s="14" t="s">
+      <c r="L37" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="O35" s="16" t="s">
+      <c r="O37" s="16" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="str">
-        <f>data!$B$10</f>
-      </c>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="14" t="str">
-        <f>data!$B$9</f>
-      </c>
-      <c r="I36" s="14" t="str">
-        <f>data!$B$22</f>
-      </c>
-      <c r="J36" s="18"/>
-      <c r="K36" s="18"/>
-      <c r="L36" s="18"/>
-      <c r="M36" s="18"/>
-      <c r="N36" s="18"/>
-      <c r="O36" s="14" t="str">
-        <f>data!$B$21</f>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="str">
-        <f>data!$B$11</f>
-      </c>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="14" t="str">
-        <f>data!$B$9</f>
-      </c>
-      <c r="I37" s="14" t="str">
-        <f>data!$B$23</f>
-      </c>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
-      <c r="M37" s="18"/>
-      <c r="N37" s="18"/>
-      <c r="O37" s="14" t="str">
-        <f>data!$B$21</f>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="str">
-        <f>data!$B$11</f>
+        <f>'data'!$B$10</f>
       </c>
       <c r="B38" s="18"/>
       <c r="C38" s="18"/>
@@ -3160,10 +3237,10 @@
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
       <c r="G38" s="14" t="str">
-        <f>data!$B$10</f>
+        <f>'data'!$B$9</f>
       </c>
       <c r="I38" s="14" t="str">
-        <f>data!$B$23</f>
+        <f>'data'!$B$22</f>
       </c>
       <c r="J38" s="18"/>
       <c r="K38" s="18"/>
@@ -3171,484 +3248,660 @@
       <c r="M38" s="18"/>
       <c r="N38" s="18"/>
       <c r="O38" s="14" t="str">
-        <f>data!$B$22</f>
+        <f>'data'!$B$21</f>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="str">
+        <f>'data'!$B$11</f>
+      </c>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="14" t="str">
+        <f>'data'!$B$9</f>
+      </c>
+      <c r="I39" s="14" t="str">
+        <f>'data'!$B$23</f>
+      </c>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="14" t="str">
+        <f>'data'!$B$21</f>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="14" t="str">
+        <f>'data'!$B$11</f>
+      </c>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="14" t="str">
+        <f>'data'!$B$10</f>
+      </c>
+      <c r="I40" s="14" t="str">
+        <f>'data'!$B$23</f>
+      </c>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="14" t="str">
+        <f>'data'!$B$22</f>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B42" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C42" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D42" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="E42" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="F40" s="13" t="s">
+      <c r="F42" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="I40" s="13" t="s">
+      <c r="G42" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="I42" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="J40" s="13" t="s">
+      <c r="J42" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="K40" s="13" t="s">
+      <c r="K42" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L40" s="13" t="s">
+      <c r="L42" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="M40" s="13" t="s">
+      <c r="M42" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="N40" s="13" t="s">
+      <c r="N42" s="13" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="14" t="str">
-        <f>data!$B$9</f>
-      </c>
-      <c r="B41" s="14" t="str">
-        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="C41" s="14" t="str">
-        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="D41" s="14" t="str">
-        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),1,0),0)+IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),1,0),0)</f>
-      </c>
-      <c r="E41" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F41" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="I41" s="14" t="str">
-        <f>data!$B$21</f>
-      </c>
-      <c r="J41" s="14" t="str">
-        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="K41" s="14" t="str">
-        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="L41" s="14" t="str">
-        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),1,0),0)+IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),1,0),0)</f>
-      </c>
-      <c r="M41" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="N41" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))</f>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="14" t="str">
-        <f>data!$B$10</f>
-      </c>
-      <c r="B42" s="14" t="str">
-        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="C42" s="14" t="str">
-        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="D42" s="14" t="str">
-        <f>IF(OR(COUNTA(B36,C36,E36,F36)&gt;0,OR(D36="X",D36="x")),IF(OR(D36="X",D36="x"),1,0),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),1,0),0)</f>
-      </c>
-      <c r="E42" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F42" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="I42" s="14" t="str">
-        <f>data!$B$22</f>
-      </c>
-      <c r="J42" s="14" t="str">
-        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="K42" s="14" t="str">
-        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="L42" s="14" t="str">
-        <f>IF(OR(COUNTA(J36,K36,M36,N36)&gt;0,OR(L36="X",L36="x")),IF(OR(L36="X",L36="x"),1,0),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),1,0),0)</f>
-      </c>
-      <c r="M42" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="N42" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N36," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))</f>
+      <c r="O42" s="13" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="str">
-        <f>data!$B$11</f>
+        <f>'data'!$B$9</f>
       </c>
       <c r="B43" s="14" t="str">
-        <f>IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x",AND(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),IF(OR(D39="X",D39="x",AND(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="C43" s="14" t="str">
-        <f>IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x",AND(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),IF(OR(D39="X",D39="x",AND(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="D43" s="14" t="str">
-        <f>IF(OR(COUNTA(B37,C37,E37,F37)&gt;0,OR(D37="X",D37="x")),IF(OR(D37="X",D37="x"),1,0),0)+IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x",AND(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),IF(OR(D39="X",D39="x",AND(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="E43" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F43" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G43" s="18" t="str">
+        <f>RANK(U43,$U$43:$U$45)+COUNTIF($U$42:U42,U43)</f>
       </c>
       <c r="I43" s="14" t="str">
-        <f>data!$B$23</f>
+        <f>'data'!$B$21</f>
       </c>
       <c r="J43" s="14" t="str">
-        <f>IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x",AND(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),IF(OR(L39="X",L39="x",AND(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="K43" s="14" t="str">
-        <f>IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")))*1),0)</f>
+        <f>IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x",AND(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),IF(OR(L39="X",L39="x",AND(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))*1),0)</f>
       </c>
       <c r="L43" s="14" t="str">
-        <f>IF(OR(COUNTA(J37,K37,M37,N37)&gt;0,OR(L37="X",L37="x")),IF(OR(L37="X",L37="x"),1,0),0)+IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x"),1,0),0)</f>
+        <f>IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x",AND(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),IF(OR(L39="X",L39="x",AND(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))))),1,0),0)</f>
       </c>
       <c r="M43" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))</f>
       </c>
       <c r="N43" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O43" s="18" t="str">
+        <f>RANK(AC43,$AC$43:$AC$45)+COUNTIF($AC$42:AC42,AC43)</f>
+      </c>
+      <c r="U43" t="str">
+        <f>=(B43*1000000)-(C43*10000)+(D43*100)+(E43*1)-(F43*0.01)</f>
+      </c>
+      <c r="AC43" t="str">
+        <f>=(J43*1000000)-(K43*10000)+(L43*100)+(M43*1)-(N43*0.01)</f>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="str">
+        <f>'data'!$B$10</f>
+      </c>
+      <c r="B44" s="14" t="str">
+        <f>IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x",AND(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),IF(OR(D40="X",D40="x",AND(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C44" s="14" t="str">
+        <f>IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x",AND(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),IF(OR(D40="X",D40="x",AND(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D44" s="14" t="str">
+        <f>IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x",AND(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),IF(OR(D40="X",D40="x",AND(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="E44" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F44" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G44" s="18" t="str">
+        <f>RANK(U44,$U$43:$U$45)+COUNTIF($U$42:U43,U44)</f>
+      </c>
+      <c r="I44" s="14" t="str">
+        <f>'data'!$B$22</f>
+      </c>
+      <c r="J44" s="14" t="str">
+        <f>IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x",AND(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),IF(OR(L40="X",L40="x",AND(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K44" s="14" t="str">
+        <f>IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x",AND(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),IF(OR(L40="X",L40="x",AND(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L44" s="14" t="str">
+        <f>IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x",AND(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),IF(OR(L40="X",L40="x",AND(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="M44" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N44" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O44" s="18" t="str">
+        <f>RANK(AC44,$AC$43:$AC$45)+COUNTIF($AC$42:AC43,AC44)</f>
+      </c>
+      <c r="U44" t="str">
+        <f>=(B44*1000000)-(C44*10000)+(D44*100)+(E44*1)-(F44*0.01)</f>
+      </c>
+      <c r="AC44" t="str">
+        <f>=(J44*1000000)-(K44*10000)+(L44*100)+(M44*1)-(N44*0.01)</f>
       </c>
     </row>
     <row r="45">
-      <c r="F45" t="s">
-        <v>103</v>
-      </c>
-      <c r="G45" s="19"/>
-      <c r="N45" t="s">
-        <v>103</v>
-      </c>
-      <c r="O45" s="19"/>
-    </row>
-    <row r="46">
-      <c r="F46" t="s">
+      <c r="A45" s="14" t="str">
+        <f>'data'!$B$11</f>
+      </c>
+      <c r="B45" s="14" t="str">
+        <f>IF(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),IF(OR(D39="X",D39="x",AND(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),IF(OR(D40="X",D40="x",AND(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C45" s="14" t="str">
+        <f>IF(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),IF(OR(D39="X",D39="x",AND(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),IF(OR(D40="X",D40="x",AND(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D45" s="14" t="str">
+        <f>IF(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),IF(OR(D39="X",D39="x",AND(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),IF(OR(D40="X",D40="x",AND(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="E45" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F45" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G45" s="18" t="str">
+        <f>RANK(U45,$U$43:$U$45)+COUNTIF($U$42:U44,U45)</f>
+      </c>
+      <c r="I45" s="14" t="str">
+        <f>'data'!$B$23</f>
+      </c>
+      <c r="J45" s="14" t="str">
+        <f>IF(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),IF(OR(L39="X",L39="x",AND(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),IF(OR(L40="X",L40="x",AND(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K45" s="14" t="str">
+        <f>IF(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),IF(OR(L39="X",L39="x",AND(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),IF(OR(L40="X",L40="x",AND(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L45" s="14" t="str">
+        <f>IF(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),IF(OR(L39="X",L39="x",AND(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),IF(OR(L40="X",L40="x",AND(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="M45" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N45" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O45" s="18" t="str">
+        <f>RANK(AC45,$AC$43:$AC$45)+COUNTIF($AC$42:AC44,AC45)</f>
+      </c>
+      <c r="U45" t="str">
+        <f>=(B45*1000000)-(C45*10000)+(D45*100)+(E45*1)-(F45*0.01)</f>
+      </c>
+      <c r="AC45" t="str">
+        <f>=(J45*1000000)-(K45*10000)+(L45*100)+(M45*1)-(N45*0.01)</f>
+      </c>
+    </row>
+    <row r="48">
+      <c r="F48" s="13"/>
+      <c r="G48" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="G46" s="19"/>
-      <c r="N46" t="s">
+      <c r="N48" s="13"/>
+      <c r="O48" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="O46" s="19"/>
-    </row>
-    <row r="47">
-      <c r="F47" t="s">
+    </row>
+    <row r="49">
+      <c r="F49" t="s">
         <v>105</v>
       </c>
-      <c r="G47" s="19"/>
-      <c r="N47" t="s">
+      <c r="G49" s="19" t="str">
+        <f>IFERROR(INDEX($A$43:$A$45, MATCH(1, $G$43:$G$45, 0)), "-")</f>
+      </c>
+      <c r="N49" t="s">
         <v>105</v>
       </c>
-      <c r="O47" s="19"/>
+      <c r="O49" s="19" t="str">
+        <f>IFERROR(INDEX($I$43:$I$45, MATCH(1, $O$43:$O$45, 0)), "-")</f>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="13" t="str">
-        <f>data!$A$14</f>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="I50" s="13" t="str">
-        <f>data!$A$26</f>
-      </c>
-      <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
-      <c r="L50" s="13"/>
-      <c r="M50" s="13"/>
-      <c r="N50" s="13"/>
-      <c r="O50" s="13"/>
+      <c r="F50" t="s">
+        <v>106</v>
+      </c>
+      <c r="G50" s="19" t="str">
+        <f>IFERROR(INDEX($A$43:$A$45, MATCH(2, $G$43:$G$45, 0)), "-")</f>
+      </c>
+      <c r="N50" t="s">
+        <v>106</v>
+      </c>
+      <c r="O50" s="19" t="str">
+        <f>IFERROR(INDEX($I$43:$I$45, MATCH(2, $O$43:$O$45, 0)), "-")</f>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="s">
+      <c r="F51" t="s">
+        <v>107</v>
+      </c>
+      <c r="G51" s="19" t="str">
+        <f>IFERROR(INDEX($A$43:$A$45, MATCH(3, $G$43:$G$45, 0)), "-")</f>
+      </c>
+      <c r="N51" t="s">
+        <v>107</v>
+      </c>
+      <c r="O51" s="19" t="str">
+        <f>IFERROR(INDEX($I$43:$I$45, MATCH(3, $O$43:$O$45, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="str">
+        <f>'data'!$A$14</f>
+      </c>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="I53" s="13" t="str">
+        <f>'data'!$A$26</f>
+      </c>
+      <c r="J53" s="13"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="13"/>
+      <c r="N53" s="13"/>
+      <c r="O53" s="13"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D54" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G51" s="16" t="s">
+      <c r="G54" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="I51" s="17" t="s">
+      <c r="I54" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="L51" s="14" t="s">
+      <c r="L54" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="O51" s="16" t="s">
+      <c r="O54" s="16" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="14" t="str">
-        <f>data!$B$13</f>
-      </c>
-      <c r="B52" s="18"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
-      <c r="F52" s="18"/>
-      <c r="G52" s="14" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="I52" s="14" t="str">
-        <f>data!$B$25</f>
-      </c>
-      <c r="J52" s="18"/>
-      <c r="K52" s="18"/>
-      <c r="L52" s="18"/>
-      <c r="M52" s="18"/>
-      <c r="N52" s="18"/>
-      <c r="O52" s="14" t="str">
-        <f>data!$B$24</f>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="14" t="str">
-        <f>data!$B$14</f>
-      </c>
-      <c r="B53" s="18"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
-      <c r="F53" s="18"/>
-      <c r="G53" s="14" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="I53" s="14" t="str">
-        <f>data!$B$26</f>
-      </c>
-      <c r="J53" s="18"/>
-      <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
-      <c r="M53" s="18"/>
-      <c r="N53" s="18"/>
-      <c r="O53" s="14" t="str">
-        <f>data!$B$24</f>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="14" t="str">
-        <f>data!$B$14</f>
-      </c>
-      <c r="B54" s="18"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="14" t="str">
-        <f>data!$B$13</f>
-      </c>
-      <c r="I54" s="14" t="str">
-        <f>data!$B$26</f>
-      </c>
-      <c r="J54" s="18"/>
-      <c r="K54" s="18"/>
-      <c r="L54" s="18"/>
-      <c r="M54" s="18"/>
-      <c r="N54" s="18"/>
-      <c r="O54" s="14" t="str">
-        <f>data!$B$25</f>
+    <row r="55">
+      <c r="A55" s="14" t="str">
+        <f>'data'!$B$13</f>
+      </c>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="14" t="str">
+        <f>'data'!$B$12</f>
+      </c>
+      <c r="I55" s="14" t="str">
+        <f>'data'!$B$25</f>
+      </c>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="18"/>
+      <c r="M55" s="18"/>
+      <c r="N55" s="18"/>
+      <c r="O55" s="14" t="str">
+        <f>'data'!$B$24</f>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="D56" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="E56" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="F56" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="I56" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="J56" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="K56" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="L56" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="M56" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="N56" s="13" t="s">
-        <v>102</v>
+      <c r="A56" s="14" t="str">
+        <f>'data'!$B$14</f>
+      </c>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="14" t="str">
+        <f>'data'!$B$12</f>
+      </c>
+      <c r="I56" s="14" t="str">
+        <f>'data'!$B$26</f>
+      </c>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
+      <c r="L56" s="18"/>
+      <c r="M56" s="18"/>
+      <c r="N56" s="18"/>
+      <c r="O56" s="14" t="str">
+        <f>'data'!$B$24</f>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="str">
-        <f>data!$B$12</f>
-      </c>
-      <c r="B57" s="14" t="str">
-        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="C57" s="14" t="str">
-        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="D57" s="14" t="str">
-        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),1,0),0)+IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),1,0),0)</f>
-      </c>
-      <c r="E57" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F57" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))</f>
+        <f>'data'!$B$14</f>
+      </c>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="14" t="str">
+        <f>'data'!$B$13</f>
       </c>
       <c r="I57" s="14" t="str">
-        <f>data!$B$24</f>
-      </c>
-      <c r="J57" s="14" t="str">
-        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="K57" s="14" t="str">
-        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="L57" s="14" t="str">
-        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),1,0),0)+IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),1,0),0)</f>
-      </c>
-      <c r="M57" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="N57" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))</f>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="14" t="str">
-        <f>data!$B$13</f>
-      </c>
-      <c r="B58" s="14" t="str">
-        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="C58" s="14" t="str">
-        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="D58" s="14" t="str">
-        <f>IF(OR(COUNTA(B52,C52,E52,F52)&gt;0,OR(D52="X",D52="x")),IF(OR(D52="X",D52="x"),1,0),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),1,0),0)</f>
-      </c>
-      <c r="E58" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F58" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="I58" s="14" t="str">
-        <f>data!$B$25</f>
-      </c>
-      <c r="J58" s="14" t="str">
-        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="K58" s="14" t="str">
-        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="L58" s="14" t="str">
-        <f>IF(OR(COUNTA(J52,K52,M52,N52)&gt;0,OR(L52="X",L52="x")),IF(OR(L52="X",L52="x"),1,0),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),1,0),0)</f>
-      </c>
-      <c r="M58" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="N58" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N52," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))</f>
+        <f>'data'!$B$26</f>
+      </c>
+      <c r="J57" s="18"/>
+      <c r="K57" s="18"/>
+      <c r="L57" s="18"/>
+      <c r="M57" s="18"/>
+      <c r="N57" s="18"/>
+      <c r="O57" s="14" t="str">
+        <f>'data'!$B$25</f>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="14" t="str">
-        <f>data!$B$14</f>
-      </c>
-      <c r="B59" s="14" t="str">
-        <f>IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="C59" s="14" t="str">
-        <f>IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="D59" s="14" t="str">
-        <f>IF(OR(COUNTA(B53,C53,E53,F53)&gt;0,OR(D53="X",D53="x")),IF(OR(D53="X",D53="x"),1,0),0)+IF(OR(COUNTA(B54,C54,E54,F54)&gt;0,OR(D54="X",D54="x")),IF(OR(D54="X",D54="x"),1,0),0)</f>
-      </c>
-      <c r="E59" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F59" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="I59" s="14" t="str">
-        <f>data!$B$26</f>
-      </c>
-      <c r="J59" s="14" t="str">
-        <f>IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="K59" s="14" t="str">
-        <f>IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-","")))*1),0)</f>
-      </c>
-      <c r="L59" s="14" t="str">
-        <f>IF(OR(COUNTA(J53,K53,M53,N53)&gt;0,OR(L53="X",L53="x")),IF(OR(L53="X",L53="x"),1,0),0)+IF(OR(COUNTA(J54,K54,M54,N54)&gt;0,OR(L54="X",L54="x")),IF(OR(L54="X",L54="x"),1,0),0)</f>
-      </c>
-      <c r="M59" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K54," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="N59" s="14" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N54," ",""),"0",""),"-",""))</f>
+      <c r="A59" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="G59" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="I59" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="J59" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="K59" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="L59" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="M59" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="N59" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="O59" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="str">
+        <f>'data'!$B$12</f>
+      </c>
+      <c r="B60" s="14" t="str">
+        <f>IF(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),IF(OR(D55="X",D55="x",AND(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),IF(OR(D56="X",D56="x",AND(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C60" s="14" t="str">
+        <f>IF(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),IF(OR(D55="X",D55="x",AND(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),IF(OR(D56="X",D56="x",AND(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D60" s="14" t="str">
+        <f>IF(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),IF(OR(D55="X",D55="x",AND(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),IF(OR(D56="X",D56="x",AND(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="E60" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F60" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G60" s="18" t="str">
+        <f>RANK(U60,$U$60:$U$62)+COUNTIF($U$59:U59,U60)</f>
+      </c>
+      <c r="I60" s="14" t="str">
+        <f>'data'!$B$24</f>
+      </c>
+      <c r="J60" s="14" t="str">
+        <f>IF(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),IF(OR(L55="X",L55="x",AND(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),IF(OR(L56="X",L56="x",AND(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K60" s="14" t="str">
+        <f>IF(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),IF(OR(L55="X",L55="x",AND(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),IF(OR(L56="X",L56="x",AND(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L60" s="14" t="str">
+        <f>IF(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),IF(OR(L55="X",L55="x",AND(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),IF(OR(L56="X",L56="x",AND(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="M60" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N60" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O60" s="18" t="str">
+        <f>RANK(AC60,$AC$60:$AC$62)+COUNTIF($AC$59:AC59,AC60)</f>
+      </c>
+      <c r="U60" t="str">
+        <f>=(B60*1000000)-(C60*10000)+(D60*100)+(E60*1)-(F60*0.01)</f>
+      </c>
+      <c r="AC60" t="str">
+        <f>=(J60*1000000)-(K60*10000)+(L60*100)+(M60*1)-(N60*0.01)</f>
       </c>
     </row>
     <row r="61">
-      <c r="F61" t="s">
-        <v>103</v>
-      </c>
-      <c r="G61" s="19"/>
-      <c r="N61" t="s">
-        <v>103</v>
-      </c>
-      <c r="O61" s="19"/>
+      <c r="A61" s="14" t="str">
+        <f>'data'!$B$13</f>
+      </c>
+      <c r="B61" s="14" t="str">
+        <f>IF(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),IF(OR(D55="X",D55="x",AND(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),IF(OR(D57="X",D57="x",AND(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C61" s="14" t="str">
+        <f>IF(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),IF(OR(D55="X",D55="x",AND(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),IF(OR(D57="X",D57="x",AND(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D61" s="14" t="str">
+        <f>IF(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),IF(OR(D55="X",D55="x",AND(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),IF(OR(D57="X",D57="x",AND(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="E61" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F61" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G61" s="18" t="str">
+        <f>RANK(U61,$U$60:$U$62)+COUNTIF($U$59:U60,U61)</f>
+      </c>
+      <c r="I61" s="14" t="str">
+        <f>'data'!$B$25</f>
+      </c>
+      <c r="J61" s="14" t="str">
+        <f>IF(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),IF(OR(L55="X",L55="x",AND(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),IF(OR(L57="X",L57="x",AND(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K61" s="14" t="str">
+        <f>IF(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),IF(OR(L55="X",L55="x",AND(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),IF(OR(L57="X",L57="x",AND(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L61" s="14" t="str">
+        <f>IF(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),IF(OR(L55="X",L55="x",AND(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),IF(OR(L57="X",L57="x",AND(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="M61" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N61" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O61" s="18" t="str">
+        <f>RANK(AC61,$AC$60:$AC$62)+COUNTIF($AC$59:AC60,AC61)</f>
+      </c>
+      <c r="U61" t="str">
+        <f>=(B61*1000000)-(C61*10000)+(D61*100)+(E61*1)-(F61*0.01)</f>
+      </c>
+      <c r="AC61" t="str">
+        <f>=(J61*1000000)-(K61*10000)+(L61*100)+(M61*1)-(N61*0.01)</f>
+      </c>
     </row>
     <row r="62">
-      <c r="F62" t="s">
+      <c r="A62" s="14" t="str">
+        <f>'data'!$B$14</f>
+      </c>
+      <c r="B62" s="14" t="str">
+        <f>IF(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),IF(OR(D56="X",D56="x",AND(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),IF(OR(D57="X",D57="x",AND(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="C62" s="14" t="str">
+        <f>IF(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),IF(OR(D56="X",D56="x",AND(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),IF(OR(D57="X",D57="x",AND(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="D62" s="14" t="str">
+        <f>IF(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),IF(OR(D56="X",D56="x",AND(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),IF(OR(D57="X",D57="x",AND(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="E62" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F62" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="G62" s="18" t="str">
+        <f>RANK(U62,$U$60:$U$62)+COUNTIF($U$59:U61,U62)</f>
+      </c>
+      <c r="I62" s="14" t="str">
+        <f>'data'!$B$26</f>
+      </c>
+      <c r="J62" s="14" t="str">
+        <f>IF(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),IF(OR(L56="X",L56="x",AND(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),IF(OR(L57="X",L57="x",AND(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="K62" s="14" t="str">
+        <f>IF(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),IF(OR(L56="X",L56="x",AND(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),IF(OR(L57="X",L57="x",AND(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-",""))&lt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")))*1),0)</f>
+      </c>
+      <c r="L62" s="14" t="str">
+        <f>IF(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),IF(OR(L56="X",L56="x",AND(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))))),1,0),0)+IF(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),IF(OR(L57="X",L57="x",AND(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))))),1,0),0)</f>
+      </c>
+      <c r="M62" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="N62" s="14" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="O62" s="18" t="str">
+        <f>RANK(AC62,$AC$60:$AC$62)+COUNTIF($AC$59:AC61,AC62)</f>
+      </c>
+      <c r="U62" t="str">
+        <f>=(B62*1000000)-(C62*10000)+(D62*100)+(E62*1)-(F62*0.01)</f>
+      </c>
+      <c r="AC62" t="str">
+        <f>=(J62*1000000)-(K62*10000)+(L62*100)+(M62*1)-(N62*0.01)</f>
+      </c>
+    </row>
+    <row r="65">
+      <c r="F65" s="13"/>
+      <c r="G65" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="G62" s="19"/>
-      <c r="N62" t="s">
+      <c r="N65" s="13"/>
+      <c r="O65" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="O62" s="19"/>
-    </row>
-    <row r="63">
-      <c r="F63" t="s">
+    </row>
+    <row r="66">
+      <c r="F66" t="s">
         <v>105</v>
       </c>
-      <c r="G63" s="19"/>
-      <c r="N63" t="s">
+      <c r="G66" s="19" t="str">
+        <f>IFERROR(INDEX($A$60:$A$62, MATCH(1, $G$60:$G$62, 0)), "-")</f>
+      </c>
+      <c r="N66" t="s">
         <v>105</v>
       </c>
-      <c r="O63" s="19"/>
+      <c r="O66" s="19" t="str">
+        <f>IFERROR(INDEX($I$60:$I$62, MATCH(1, $O$60:$O$62, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="67">
+      <c r="F67" t="s">
+        <v>106</v>
+      </c>
+      <c r="G67" s="19" t="str">
+        <f>IFERROR(INDEX($A$60:$A$62, MATCH(2, $G$60:$G$62, 0)), "-")</f>
+      </c>
+      <c r="N67" t="s">
+        <v>106</v>
+      </c>
+      <c r="O67" s="19" t="str">
+        <f>IFERROR(INDEX($I$60:$I$62, MATCH(2, $O$60:$O$62, 0)), "-")</f>
+      </c>
+    </row>
+    <row r="68">
+      <c r="F68" t="s">
+        <v>107</v>
+      </c>
+      <c r="G68" s="19" t="str">
+        <f>IFERROR(INDEX($A$60:$A$62, MATCH(3, $G$60:$G$62, 0)), "-")</f>
+      </c>
+      <c r="N68" t="s">
+        <v>107</v>
+      </c>
+      <c r="O68" s="19" t="str">
+        <f>IFERROR(INDEX($I$60:$I$62, MATCH(3, $O$60:$O$62, 0)), "-")</f>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
@@ -3657,17 +3910,17 @@
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="I2:O2"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="I18:O18"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="I34:O34"/>
-    <mergeCell ref="A50:G50"/>
-    <mergeCell ref="I50:O50"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="I19:O19"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="I36:O36"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="I53:O53"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageSetup fitToHeight="0" fitToWidth="2" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="33" max="16383" man="true"/>
+    <brk id="35" max="16383" man="true"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="1048575" man="true"/>
@@ -3684,19 +3937,14 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="3" min="2" width="5"/>
-    <col customWidth="true" max="4" min="4" width="3"/>
-    <col customWidth="true" max="6" min="5" width="5"/>
+    <col customWidth="true" max="6" min="2" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
     <col customWidth="true" max="8" min="8" width="5"/>
     <col customWidth="true" max="9" min="9" width="30"/>
-    <col customWidth="true" max="11" min="10" width="5"/>
-    <col customWidth="true" max="12" min="12" width="3"/>
-    <col customWidth="true" max="14" min="13" width="5"/>
+    <col customWidth="true" max="14" min="10" width="5"/>
     <col customWidth="true" max="15" min="15" width="30"/>
-    <col customWidth="true" max="18" min="16" width="5"/>
-    <col customWidth="true" max="19" min="19" width="30"/>
-    <col customWidth="true" max="20" min="20" width="2"/>
+    <col customWidth="true" max="16" min="16" width="5"/>
+    <col customWidth="true" max="20" min="17" width="10.83"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3721,7 +3969,7 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -3761,7 +4009,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G30)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G36)</f>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -3769,10 +4017,10 @@
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G13)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G18)</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G14)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G19)</f>
       </c>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
@@ -3780,26 +4028,26 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G29)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G35)</f>
       </c>
     </row>
     <row r="6">
       <c r="F6" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G6" s="19"/>
       <c r="N6" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="O6" s="19"/>
     </row>
     <row r="7">
       <c r="F7" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="G7" s="19"/>
       <c r="N7" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O7" s="19"/>
     </row>
@@ -3845,7 +4093,7 @@
     </row>
     <row r="12">
       <c r="A12" s="14" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G62)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G70)</f>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -3853,10 +4101,10 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G45)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G52)</f>
       </c>
       <c r="I12" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G46)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G53)</f>
       </c>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
@@ -3864,26 +4112,26 @@
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
       <c r="O12" s="14" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G61)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G69)</f>
       </c>
     </row>
     <row r="14">
       <c r="F14" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G14" s="19"/>
       <c r="N14" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="O14" s="19"/>
     </row>
     <row r="15">
       <c r="F15" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="G15" s="19"/>
       <c r="N15" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O15" s="19"/>
     </row>
@@ -3929,7 +4177,7 @@
     </row>
     <row r="20">
       <c r="A20" s="14" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O30)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O36)</f>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -3937,10 +4185,10 @@
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
       <c r="G20" s="14" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O13)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O18)</f>
       </c>
       <c r="I20" s="14" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O14)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O19)</f>
       </c>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
@@ -3948,26 +4196,26 @@
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
       <c r="O20" s="14" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O29)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O35)</f>
       </c>
     </row>
     <row r="22">
       <c r="F22" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G22" s="19"/>
       <c r="N22" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="O22" s="19"/>
     </row>
     <row r="23">
       <c r="F23" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="G23" s="19"/>
       <c r="N23" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O23" s="19"/>
     </row>
@@ -4013,7 +4261,7 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O62)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O70)</f>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -4021,10 +4269,10 @@
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="14" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O45)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O52)</f>
       </c>
       <c r="I28" s="14" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O46)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O53)</f>
       </c>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
@@ -4032,26 +4280,26 @@
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="14" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O61)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O69)</f>
       </c>
     </row>
     <row r="30">
       <c r="F30" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G30" s="19"/>
       <c r="N30" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="O30" s="19"/>
     </row>
     <row r="31">
       <c r="F31" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="G31" s="19"/>
       <c r="N31" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O31" s="19"/>
     </row>
@@ -4121,21 +4369,21 @@
     </row>
     <row r="43">
       <c r="F43" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G43" s="19"/>
       <c r="N43" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="O43" s="19"/>
     </row>
     <row r="44">
       <c r="F44" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="G44" s="19"/>
       <c r="N44" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O44" s="19"/>
     </row>
@@ -4205,21 +4453,21 @@
     </row>
     <row r="51">
       <c r="F51" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G51" s="19"/>
       <c r="N51" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="O51" s="19"/>
     </row>
     <row r="52">
       <c r="F52" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="G52" s="19"/>
       <c r="N52" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O52" s="19"/>
     </row>
@@ -4289,21 +4537,21 @@
     </row>
     <row r="64">
       <c r="F64" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G64" s="19"/>
       <c r="N64" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="O64" s="19"/>
     </row>
     <row r="65">
       <c r="F65" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="G65" s="19"/>
       <c r="N65" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="O65" s="19"/>
     </row>
@@ -4344,13 +4592,13 @@
     </row>
     <row r="77">
       <c r="F77" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G77" s="19"/>
     </row>
     <row r="78">
       <c r="F78" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="G78" s="19"/>
     </row>
@@ -4417,7 +4665,7 @@
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
-        <f>data!$A$5</f>
+        <f>'data'!$A$5</f>
       </c>
     </row>
     <row r="5">
@@ -4425,7 +4673,7 @@
         <f>"1. " &amp; data!$B$3</f>
       </c>
       <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G13)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G18)</f>
       </c>
     </row>
     <row r="6">
@@ -4442,7 +4690,7 @@
         <f>"3. " &amp; data!$B$5</f>
       </c>
       <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G30)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G36)</f>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="20"/>
@@ -4457,10 +4705,10 @@
     </row>
     <row r="9">
       <c r="A9" s="24" t="str">
-        <f>data!$A$8</f>
+        <f>'data'!$A$8</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G45)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G52)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -4483,7 +4731,7 @@
         <f>"2. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G62)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G70)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -4500,13 +4748,13 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O13)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O18)</f>
       </c>
       <c r="I13" s="20"/>
     </row>
     <row r="14">
       <c r="A14" s="24" t="str">
-        <f>data!$A$11</f>
+        <f>'data'!$A$11</f>
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="21">
@@ -4519,7 +4767,7 @@
         <f>"1. " &amp; data!$B$9</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O30)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O36)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -4542,7 +4790,7 @@
         <f>"3. " &amp; data!$B$11</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O45)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O52)</f>
       </c>
       <c r="G17" s="20"/>
     </row>
@@ -4557,10 +4805,10 @@
     </row>
     <row r="19">
       <c r="A19" s="24" t="str">
-        <f>data!$A$14</f>
+        <f>'data'!$A$14</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O62)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O70)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -4624,7 +4872,7 @@
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
-        <f>data!$A$17</f>
+        <f>'data'!$A$17</f>
       </c>
     </row>
     <row r="5">
@@ -4632,7 +4880,7 @@
         <f>"1. " &amp; data!$B$15</f>
       </c>
       <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G29)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G35)</f>
       </c>
     </row>
     <row r="6">
@@ -4649,7 +4897,7 @@
         <f>"3. " &amp; data!$B$17</f>
       </c>
       <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G14)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G19)</f>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="20"/>
@@ -4664,10 +4912,10 @@
     </row>
     <row r="9">
       <c r="A9" s="24" t="str">
-        <f>data!$A$20</f>
+        <f>'data'!$A$20</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G61)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G69)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -4690,7 +4938,7 @@
         <f>"2. " &amp; data!$B$19</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G46)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G53)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -4707,13 +4955,13 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O29)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O35)</f>
       </c>
       <c r="I13" s="20"/>
     </row>
     <row r="14">
       <c r="A14" s="24" t="str">
-        <f>data!$A$23</f>
+        <f>'data'!$A$23</f>
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="21">
@@ -4726,7 +4974,7 @@
         <f>"1. " &amp; data!$B$21</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O14)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O19)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -4749,7 +4997,7 @@
         <f>"3. " &amp; data!$B$23</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O61)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O69)</f>
       </c>
       <c r="G17" s="20"/>
     </row>
@@ -4764,10 +5012,10 @@
     </row>
     <row r="19">
       <c r="A19" s="24" t="str">
-        <f>data!$A$26</f>
+        <f>'data'!$A$26</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O46)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O53)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>

--- a/pools-example-medium-seeded.xlsx
+++ b/pools-example-medium-seeded.xlsx
@@ -4009,7 +4009,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G36)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -4017,10 +4017,10 @@
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G18)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G15)</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G19)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G16)</f>
       </c>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
@@ -4028,7 +4028,7 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G35)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
       </c>
     </row>
     <row r="6">
@@ -4093,7 +4093,7 @@
     </row>
     <row r="12">
       <c r="A12" s="14" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G70)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -4101,10 +4101,10 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G52)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
       </c>
       <c r="I12" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G53)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
       </c>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
@@ -4112,7 +4112,7 @@
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
       <c r="O12" s="14" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G69)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
       </c>
     </row>
     <row r="14">
@@ -4177,7 +4177,7 @@
     </row>
     <row r="20">
       <c r="A20" s="14" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O36)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O33)</f>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -4185,10 +4185,10 @@
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
       <c r="G20" s="14" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O18)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O15)</f>
       </c>
       <c r="I20" s="14" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O19)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O16)</f>
       </c>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
@@ -4196,7 +4196,7 @@
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
       <c r="O20" s="14" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O35)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O32)</f>
       </c>
     </row>
     <row r="22">
@@ -4261,7 +4261,7 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O70)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O67)</f>
       </c>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
@@ -4269,10 +4269,10 @@
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="14" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O52)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O49)</f>
       </c>
       <c r="I28" s="14" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O53)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O50)</f>
       </c>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
@@ -4280,7 +4280,7 @@
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="14" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O69)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O66)</f>
       </c>
     </row>
     <row r="30">
@@ -4673,7 +4673,7 @@
         <f>"1. " &amp; data!$B$3</f>
       </c>
       <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G18)</f>
+        <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G15)</f>
       </c>
     </row>
     <row r="6">
@@ -4690,7 +4690,7 @@
         <f>"3. " &amp; data!$B$5</f>
       </c>
       <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G36)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="20"/>
@@ -4708,7 +4708,7 @@
         <f>'data'!$A$8</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G52)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -4731,7 +4731,7 @@
         <f>"2. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G70)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -4748,7 +4748,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O18)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O15)</f>
       </c>
       <c r="I13" s="20"/>
     </row>
@@ -4767,7 +4767,7 @@
         <f>"1. " &amp; data!$B$9</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O36)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O33)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -4790,7 +4790,7 @@
         <f>"3. " &amp; data!$B$11</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O52)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O49)</f>
       </c>
       <c r="G17" s="20"/>
     </row>
@@ -4808,7 +4808,7 @@
         <f>'data'!$A$14</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O70)</f>
+        <f>CONCATENATE("Pool H-2nd ",'Pool Matches'!O67)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>
@@ -4880,7 +4880,7 @@
         <f>"1. " &amp; data!$B$15</f>
       </c>
       <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G35)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
       </c>
     </row>
     <row r="6">
@@ -4897,7 +4897,7 @@
         <f>"3. " &amp; data!$B$17</f>
       </c>
       <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G19)</f>
+        <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G16)</f>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="20"/>
@@ -4915,7 +4915,7 @@
         <f>'data'!$A$20</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G69)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -4938,7 +4938,7 @@
         <f>"2. " &amp; data!$B$19</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G53)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -4955,7 +4955,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O35)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O32)</f>
       </c>
       <c r="I13" s="20"/>
     </row>
@@ -4974,7 +4974,7 @@
         <f>"1. " &amp; data!$B$21</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O19)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O16)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -4997,7 +4997,7 @@
         <f>"3. " &amp; data!$B$23</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O69)</f>
+        <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O66)</f>
       </c>
       <c r="G17" s="20"/>
     </row>
@@ -5015,7 +5015,7 @@
         <f>'data'!$A$26</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O53)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O50)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>

--- a/pools-example-medium-seeded.xlsx
+++ b/pools-example-medium-seeded.xlsx
@@ -2671,10 +2671,10 @@
         <f>RANK(AC9,$AC$9:$AC$11)+COUNTIF($AC$8:AC8,AC9)</f>
       </c>
       <c r="U9" t="str">
-        <f>=(B9*1000000)-(C9*10000)+(D9*100)+(E9*1)-(F9*0.01)</f>
+        <f>(B9*1000000)-(C9*10000)+(D9*100)+(E9*1)-(F9*0.01)</f>
       </c>
       <c r="AC9" t="str">
-        <f>=(J9*1000000)-(K9*10000)+(L9*100)+(M9*1)-(N9*0.01)</f>
+        <f>(J9*1000000)-(K9*10000)+(L9*100)+(M9*1)-(N9*0.01)</f>
       </c>
     </row>
     <row r="10">
@@ -2721,10 +2721,10 @@
         <f>RANK(AC10,$AC$9:$AC$11)+COUNTIF($AC$8:AC9,AC10)</f>
       </c>
       <c r="U10" t="str">
-        <f>=(B10*1000000)-(C10*10000)+(D10*100)+(E10*1)-(F10*0.01)</f>
+        <f>(B10*1000000)-(C10*10000)+(D10*100)+(E10*1)-(F10*0.01)</f>
       </c>
       <c r="AC10" t="str">
-        <f>=(J10*1000000)-(K10*10000)+(L10*100)+(M10*1)-(N10*0.01)</f>
+        <f>(J10*1000000)-(K10*10000)+(L10*100)+(M10*1)-(N10*0.01)</f>
       </c>
     </row>
     <row r="11">
@@ -2771,10 +2771,10 @@
         <f>RANK(AC11,$AC$9:$AC$11)+COUNTIF($AC$8:AC10,AC11)</f>
       </c>
       <c r="U11" t="str">
-        <f>=(B11*1000000)-(C11*10000)+(D11*100)+(E11*1)-(F11*0.01)</f>
+        <f>(B11*1000000)-(C11*10000)+(D11*100)+(E11*1)-(F11*0.01)</f>
       </c>
       <c r="AC11" t="str">
-        <f>=(J11*1000000)-(K11*10000)+(L11*100)+(M11*1)-(N11*0.01)</f>
+        <f>(J11*1000000)-(K11*10000)+(L11*100)+(M11*1)-(N11*0.01)</f>
       </c>
     </row>
     <row r="14">
@@ -3029,10 +3029,10 @@
         <f>RANK(AC26,$AC$26:$AC$28)+COUNTIF($AC$25:AC25,AC26)</f>
       </c>
       <c r="U26" t="str">
-        <f>=(B26*1000000)-(C26*10000)+(D26*100)+(E26*1)-(F26*0.01)</f>
+        <f>(B26*1000000)-(C26*10000)+(D26*100)+(E26*1)-(F26*0.01)</f>
       </c>
       <c r="AC26" t="str">
-        <f>=(J26*1000000)-(K26*10000)+(L26*100)+(M26*1)-(N26*0.01)</f>
+        <f>(J26*1000000)-(K26*10000)+(L26*100)+(M26*1)-(N26*0.01)</f>
       </c>
     </row>
     <row r="27">
@@ -3079,10 +3079,10 @@
         <f>RANK(AC27,$AC$26:$AC$28)+COUNTIF($AC$25:AC26,AC27)</f>
       </c>
       <c r="U27" t="str">
-        <f>=(B27*1000000)-(C27*10000)+(D27*100)+(E27*1)-(F27*0.01)</f>
+        <f>(B27*1000000)-(C27*10000)+(D27*100)+(E27*1)-(F27*0.01)</f>
       </c>
       <c r="AC27" t="str">
-        <f>=(J27*1000000)-(K27*10000)+(L27*100)+(M27*1)-(N27*0.01)</f>
+        <f>(J27*1000000)-(K27*10000)+(L27*100)+(M27*1)-(N27*0.01)</f>
       </c>
     </row>
     <row r="28">
@@ -3129,10 +3129,10 @@
         <f>RANK(AC28,$AC$26:$AC$28)+COUNTIF($AC$25:AC27,AC28)</f>
       </c>
       <c r="U28" t="str">
-        <f>=(B28*1000000)-(C28*10000)+(D28*100)+(E28*1)-(F28*0.01)</f>
+        <f>(B28*1000000)-(C28*10000)+(D28*100)+(E28*1)-(F28*0.01)</f>
       </c>
       <c r="AC28" t="str">
-        <f>=(J28*1000000)-(K28*10000)+(L28*100)+(M28*1)-(N28*0.01)</f>
+        <f>(J28*1000000)-(K28*10000)+(L28*100)+(M28*1)-(N28*0.01)</f>
       </c>
     </row>
     <row r="31">
@@ -3387,10 +3387,10 @@
         <f>RANK(AC43,$AC$43:$AC$45)+COUNTIF($AC$42:AC42,AC43)</f>
       </c>
       <c r="U43" t="str">
-        <f>=(B43*1000000)-(C43*10000)+(D43*100)+(E43*1)-(F43*0.01)</f>
+        <f>(B43*1000000)-(C43*10000)+(D43*100)+(E43*1)-(F43*0.01)</f>
       </c>
       <c r="AC43" t="str">
-        <f>=(J43*1000000)-(K43*10000)+(L43*100)+(M43*1)-(N43*0.01)</f>
+        <f>(J43*1000000)-(K43*10000)+(L43*100)+(M43*1)-(N43*0.01)</f>
       </c>
     </row>
     <row r="44">
@@ -3437,10 +3437,10 @@
         <f>RANK(AC44,$AC$43:$AC$45)+COUNTIF($AC$42:AC43,AC44)</f>
       </c>
       <c r="U44" t="str">
-        <f>=(B44*1000000)-(C44*10000)+(D44*100)+(E44*1)-(F44*0.01)</f>
+        <f>(B44*1000000)-(C44*10000)+(D44*100)+(E44*1)-(F44*0.01)</f>
       </c>
       <c r="AC44" t="str">
-        <f>=(J44*1000000)-(K44*10000)+(L44*100)+(M44*1)-(N44*0.01)</f>
+        <f>(J44*1000000)-(K44*10000)+(L44*100)+(M44*1)-(N44*0.01)</f>
       </c>
     </row>
     <row r="45">
@@ -3487,10 +3487,10 @@
         <f>RANK(AC45,$AC$43:$AC$45)+COUNTIF($AC$42:AC44,AC45)</f>
       </c>
       <c r="U45" t="str">
-        <f>=(B45*1000000)-(C45*10000)+(D45*100)+(E45*1)-(F45*0.01)</f>
+        <f>(B45*1000000)-(C45*10000)+(D45*100)+(E45*1)-(F45*0.01)</f>
       </c>
       <c r="AC45" t="str">
-        <f>=(J45*1000000)-(K45*10000)+(L45*100)+(M45*1)-(N45*0.01)</f>
+        <f>(J45*1000000)-(K45*10000)+(L45*100)+(M45*1)-(N45*0.01)</f>
       </c>
     </row>
     <row r="48">
@@ -3745,10 +3745,10 @@
         <f>RANK(AC60,$AC$60:$AC$62)+COUNTIF($AC$59:AC59,AC60)</f>
       </c>
       <c r="U60" t="str">
-        <f>=(B60*1000000)-(C60*10000)+(D60*100)+(E60*1)-(F60*0.01)</f>
+        <f>(B60*1000000)-(C60*10000)+(D60*100)+(E60*1)-(F60*0.01)</f>
       </c>
       <c r="AC60" t="str">
-        <f>=(J60*1000000)-(K60*10000)+(L60*100)+(M60*1)-(N60*0.01)</f>
+        <f>(J60*1000000)-(K60*10000)+(L60*100)+(M60*1)-(N60*0.01)</f>
       </c>
     </row>
     <row r="61">
@@ -3795,10 +3795,10 @@
         <f>RANK(AC61,$AC$60:$AC$62)+COUNTIF($AC$59:AC60,AC61)</f>
       </c>
       <c r="U61" t="str">
-        <f>=(B61*1000000)-(C61*10000)+(D61*100)+(E61*1)-(F61*0.01)</f>
+        <f>(B61*1000000)-(C61*10000)+(D61*100)+(E61*1)-(F61*0.01)</f>
       </c>
       <c r="AC61" t="str">
-        <f>=(J61*1000000)-(K61*10000)+(L61*100)+(M61*1)-(N61*0.01)</f>
+        <f>(J61*1000000)-(K61*10000)+(L61*100)+(M61*1)-(N61*0.01)</f>
       </c>
     </row>
     <row r="62">
@@ -3845,10 +3845,10 @@
         <f>RANK(AC62,$AC$60:$AC$62)+COUNTIF($AC$59:AC61,AC62)</f>
       </c>
       <c r="U62" t="str">
-        <f>=(B62*1000000)-(C62*10000)+(D62*100)+(E62*1)-(F62*0.01)</f>
+        <f>(B62*1000000)-(C62*10000)+(D62*100)+(E62*1)-(F62*0.01)</f>
       </c>
       <c r="AC62" t="str">
-        <f>=(J62*1000000)-(K62*10000)+(L62*100)+(M62*1)-(N62*0.01)</f>
+        <f>(J62*1000000)-(K62*10000)+(L62*100)+(M62*1)-(N62*0.01)</f>
       </c>
     </row>
     <row r="65">

--- a/pools-example-medium-seeded.xlsx
+++ b/pools-example-medium-seeded.xlsx
@@ -591,7 +591,7 @@
       <family val="2"/>
       <b val="1"/>
       <color/>
-      <sz val="150"/>
+      <sz val="200"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1706,242 +1706,242 @@
     <col customWidth="true" max="1" min="1" width="90"/>
   </cols>
   <sheetData>
-    <row r="1" ht="390" customHeight="true">
+    <row r="1" ht="409" customHeight="true">
       <c r="A1" s="30" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="2" ht="390" customHeight="true">
+    <row r="2" ht="409" customHeight="true">
       <c r="A2" s="30" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="3" ht="390" customHeight="true">
+    <row r="3" ht="409" customHeight="true">
       <c r="A3" s="30" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="4" ht="390" customHeight="true">
+    <row r="4" ht="409" customHeight="true">
       <c r="A4" s="30" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="5" ht="390" customHeight="true">
+    <row r="5" ht="409" customHeight="true">
       <c r="A5" s="30" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="6" ht="390" customHeight="true">
+    <row r="6" ht="409" customHeight="true">
       <c r="A6" s="30" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="7" ht="390" customHeight="true">
+    <row r="7" ht="409" customHeight="true">
       <c r="A7" s="30" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="8" ht="390" customHeight="true">
+    <row r="8" ht="409" customHeight="true">
       <c r="A8" s="30" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="9" ht="390" customHeight="true">
+    <row r="9" ht="409" customHeight="true">
       <c r="A9" s="30" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="10" ht="390" customHeight="true">
+    <row r="10" ht="409" customHeight="true">
       <c r="A10" s="30" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="11" ht="390" customHeight="true">
+    <row r="11" ht="409" customHeight="true">
       <c r="A11" s="30" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="12" ht="390" customHeight="true">
+    <row r="12" ht="409" customHeight="true">
       <c r="A12" s="30" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="13" ht="390" customHeight="true">
+    <row r="13" ht="409" customHeight="true">
       <c r="A13" s="30" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" ht="390" customHeight="true">
+    <row r="14" ht="409" customHeight="true">
       <c r="A14" s="30" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="15" ht="390" customHeight="true">
+    <row r="15" ht="409" customHeight="true">
       <c r="A15" s="30" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="16" ht="390" customHeight="true">
+    <row r="16" ht="409" customHeight="true">
       <c r="A16" s="30" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="17" ht="390" customHeight="true">
+    <row r="17" ht="409" customHeight="true">
       <c r="A17" s="30" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="18" ht="390" customHeight="true">
+    <row r="18" ht="409" customHeight="true">
       <c r="A18" s="30" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="19" ht="390" customHeight="true">
+    <row r="19" ht="409" customHeight="true">
       <c r="A19" s="30" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="20" ht="390" customHeight="true">
+    <row r="20" ht="409" customHeight="true">
       <c r="A20" s="30" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="21" ht="390" customHeight="true">
+    <row r="21" ht="409" customHeight="true">
       <c r="A21" s="30" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="22" ht="390" customHeight="true">
+    <row r="22" ht="409" customHeight="true">
       <c r="A22" s="30" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="23" ht="390" customHeight="true">
+    <row r="23" ht="409" customHeight="true">
       <c r="A23" s="30" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="24" ht="390" customHeight="true">
+    <row r="24" ht="409" customHeight="true">
       <c r="A24" s="30" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="25" ht="390" customHeight="true">
+    <row r="25" ht="409" customHeight="true">
       <c r="A25" s="30" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="26" ht="390" customHeight="true">
+    <row r="26" ht="409" customHeight="true">
       <c r="A26" s="30" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="27" ht="390" customHeight="true">
+    <row r="27" ht="409" customHeight="true">
       <c r="A27" s="30" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="28" ht="390" customHeight="true">
+    <row r="28" ht="409" customHeight="true">
       <c r="A28" s="30" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="29" ht="390" customHeight="true">
+    <row r="29" ht="409" customHeight="true">
       <c r="A29" s="30" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="30" ht="390" customHeight="true">
+    <row r="30" ht="409" customHeight="true">
       <c r="A30" s="30" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="31" ht="390" customHeight="true">
+    <row r="31" ht="409" customHeight="true">
       <c r="A31" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="32" ht="390" customHeight="true">
+    <row r="32" ht="409" customHeight="true">
       <c r="A32" s="30" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="33" ht="390" customHeight="true">
+    <row r="33" ht="409" customHeight="true">
       <c r="A33" s="30" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="34" ht="390" customHeight="true">
+    <row r="34" ht="409" customHeight="true">
       <c r="A34" s="30" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="35" ht="390" customHeight="true">
+    <row r="35" ht="409" customHeight="true">
       <c r="A35" s="30" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="36" ht="390" customHeight="true">
+    <row r="36" ht="409" customHeight="true">
       <c r="A36" s="30" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="37" ht="390" customHeight="true">
+    <row r="37" ht="409" customHeight="true">
       <c r="A37" s="30" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="38" ht="390" customHeight="true">
+    <row r="38" ht="409" customHeight="true">
       <c r="A38" s="30" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="39" ht="390" customHeight="true">
+    <row r="39" ht="409" customHeight="true">
       <c r="A39" s="30" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="40" ht="390" customHeight="true">
+    <row r="40" ht="409" customHeight="true">
       <c r="A40" s="30" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="41" ht="390" customHeight="true">
+    <row r="41" ht="409" customHeight="true">
       <c r="A41" s="30" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="42" ht="390" customHeight="true">
+    <row r="42" ht="409" customHeight="true">
       <c r="A42" s="30" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="43" ht="390" customHeight="true">
+    <row r="43" ht="409" customHeight="true">
       <c r="A43" s="30" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="44" ht="390" customHeight="true">
+    <row r="44" ht="409" customHeight="true">
       <c r="A44" s="30" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="45" ht="390" customHeight="true">
+    <row r="45" ht="409" customHeight="true">
       <c r="A45" s="30" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="46" ht="390" customHeight="true">
+    <row r="46" ht="409" customHeight="true">
       <c r="A46" s="30" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="47" ht="390" customHeight="true">
+    <row r="47" ht="409" customHeight="true">
       <c r="A47" s="30" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="48" ht="390" customHeight="true">
+    <row r="48" ht="409" customHeight="true">
       <c r="A48" s="30" t="s">
         <v>131</v>
       </c>

--- a/pools-example-medium-seeded.xlsx
+++ b/pools-example-medium-seeded.xlsx
@@ -591,7 +591,7 @@
       <family val="2"/>
       <b val="1"/>
       <color/>
-      <sz val="200"/>
+      <sz val="250"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1703,7 +1703,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="90"/>
+    <col customWidth="true" max="1" min="1" width="110"/>
   </cols>
   <sheetData>
     <row r="1" ht="409" customHeight="true">

--- a/pools-example-medium-seeded.xlsx
+++ b/pools-example-medium-seeded.xlsx
@@ -21,6 +21,8 @@
   <definedNames>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Pool Draw'!$B$2:$F$23</definedName>
     <definedName localSheetId="3" name="_xlnm.Print_Area">'Pool Matches'!$A$1:$P$69</definedName>
+    <definedName localSheetId="5" name="_xlnm.Print_Area">'Tree 1'!$A$1:$I$23</definedName>
+    <definedName localSheetId="6" name="_xlnm.Print_Area">'Tree 2'!$A$1:$I$23</definedName>
     <definedName localSheetId="7" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$12</definedName>
     <definedName localSheetId="8" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$12</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$85</definedName>
@@ -4635,12 +4637,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4655,13 +4662,6 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
@@ -4834,20 +4834,25 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4862,13 +4867,6 @@
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
       <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="24" t="str">
@@ -5041,9 +5039,9 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/pools-example-medium-seeded.xlsx
+++ b/pools-example-medium-seeded.xlsx
@@ -787,7 +787,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">

--- a/pools-example-medium-seeded.xlsx
+++ b/pools-example-medium-seeded.xlsx
@@ -4011,7 +4011,7 @@
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O16)</f>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -4030,7 +4030,7 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O15)</f>
       </c>
     </row>
     <row r="6">
@@ -4095,7 +4095,7 @@
     </row>
     <row r="12">
       <c r="A12" s="14" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O33)</f>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -4103,10 +4103,10 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="14" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
       </c>
       <c r="I12" s="14" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
       </c>
       <c r="J12" s="18"/>
       <c r="K12" s="18"/>
@@ -4114,7 +4114,7 @@
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
       <c r="O12" s="14" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O32)</f>
       </c>
     </row>
     <row r="14">
@@ -4179,7 +4179,7 @@
     </row>
     <row r="20">
       <c r="A20" s="14" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O33)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O50)</f>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -4187,10 +4187,10 @@
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
       <c r="G20" s="14" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O15)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
       </c>
       <c r="I20" s="14" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O16)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
       </c>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
@@ -4198,7 +4198,7 @@
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
       <c r="O20" s="14" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O32)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O49)</f>
       </c>
     </row>
     <row r="22">
@@ -4271,10 +4271,10 @@
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="14" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O49)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
       </c>
       <c r="I28" s="14" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O50)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
       </c>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
@@ -4690,7 +4690,7 @@
         <f>"3. " &amp; data!$B$5</f>
       </c>
       <c r="C7" s="23" t="str">
-        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
+        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O16)</f>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="20"/>
@@ -4708,7 +4708,7 @@
         <f>'data'!$A$8</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
+        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -4731,7 +4731,7 @@
         <f>"2. " &amp; data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
+        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O33)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -4748,7 +4748,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O15)</f>
+        <f>CONCATENATE("Pool C-1st ",'Pool Matches'!G49)</f>
       </c>
       <c r="I13" s="20"/>
     </row>
@@ -4767,7 +4767,7 @@
         <f>"1. " &amp; data!$B$9</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O33)</f>
+        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O50)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -4790,7 +4790,7 @@
         <f>"3. " &amp; data!$B$11</f>
       </c>
       <c r="C17" s="23" t="str">
-        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O49)</f>
+        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
       </c>
       <c r="G17" s="20"/>
     </row>
@@ -4878,7 +4878,7 @@
         <f>"1. " &amp; data!$B$15</f>
       </c>
       <c r="C5" s="23" t="str">
-        <f>CONCATENATE("Pool B-1st ",'Pool Matches'!G32)</f>
+        <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O15)</f>
       </c>
     </row>
     <row r="6">
@@ -4913,7 +4913,7 @@
         <f>'data'!$A$20</f>
       </c>
       <c r="C9" s="23" t="str">
-        <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
+        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O32)</f>
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
@@ -4936,7 +4936,7 @@
         <f>"2. " &amp; data!$B$19</f>
       </c>
       <c r="C11" s="23" t="str">
-        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
+        <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="20"/>
@@ -4953,7 +4953,7 @@
     <row r="13">
       <c r="A13" s="22"/>
       <c r="C13" s="23" t="str">
-        <f>CONCATENATE("Pool F-1st ",'Pool Matches'!O32)</f>
+        <f>CONCATENATE("Pool G-1st ",'Pool Matches'!O49)</f>
       </c>
       <c r="I13" s="20"/>
     </row>
@@ -4972,7 +4972,7 @@
         <f>"1. " &amp; data!$B$21</f>
       </c>
       <c r="C15" s="23" t="str">
-        <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O16)</f>
+        <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="20"/>
@@ -5013,7 +5013,7 @@
         <f>'data'!$A$26</f>
       </c>
       <c r="C19" s="23" t="str">
-        <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O50)</f>
+        <f>CONCATENATE("Pool D-2nd ",'Pool Matches'!G67)</f>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="20"/>

--- a/pools-example-medium-seeded.xlsx
+++ b/pools-example-medium-seeded.xlsx
@@ -145,6 +145,90 @@
     <t>Pool C</t>
   </si>
   <si>
+    <t>Legolas Greenleaf</t>
+  </si>
+  <si>
+    <t>GREENLEAF</t>
+  </si>
+  <si>
+    <t>Moby Dick</t>
+  </si>
+  <si>
+    <t>Team Nu</t>
+  </si>
+  <si>
+    <t>DICK</t>
+  </si>
+  <si>
+    <t>Samwise Gamgee</t>
+  </si>
+  <si>
+    <t>Team Tau</t>
+  </si>
+  <si>
+    <t>GAMGEE</t>
+  </si>
+  <si>
+    <t>Pool D</t>
+  </si>
+  <si>
+    <t>Eddard Stark</t>
+  </si>
+  <si>
+    <t>Team Epsilon</t>
+  </si>
+  <si>
+    <t>STARK</t>
+  </si>
+  <si>
+    <t>Othello</t>
+  </si>
+  <si>
+    <t>Team Omicron</t>
+  </si>
+  <si>
+    <t>OTHELLO</t>
+  </si>
+  <si>
+    <t>Tyrion Lannister</t>
+  </si>
+  <si>
+    <t>Team Upsilon</t>
+  </si>
+  <si>
+    <t>Pool E</t>
+  </si>
+  <si>
+    <t>Daenerys Targaryen</t>
+  </si>
+  <si>
+    <t>Team Delta</t>
+  </si>
+  <si>
+    <t>TARGARYEN</t>
+  </si>
+  <si>
+    <t>Inigo Montoya</t>
+  </si>
+  <si>
+    <t>Team Iota</t>
+  </si>
+  <si>
+    <t>MONTOYA</t>
+  </si>
+  <si>
+    <t>Willy Wonka</t>
+  </si>
+  <si>
+    <t>Team Psi</t>
+  </si>
+  <si>
+    <t>WONKA</t>
+  </si>
+  <si>
+    <t>Pool F</t>
+  </si>
+  <si>
     <t>Ygritte</t>
   </si>
   <si>
@@ -152,90 +236,6 @@
   </si>
   <si>
     <t>YGRITTE</t>
-  </si>
-  <si>
-    <t>Moby Dick</t>
-  </si>
-  <si>
-    <t>Team Nu</t>
-  </si>
-  <si>
-    <t>DICK</t>
-  </si>
-  <si>
-    <t>Samwise Gamgee</t>
-  </si>
-  <si>
-    <t>Team Tau</t>
-  </si>
-  <si>
-    <t>GAMGEE</t>
-  </si>
-  <si>
-    <t>Pool D</t>
-  </si>
-  <si>
-    <t>Eddard Stark</t>
-  </si>
-  <si>
-    <t>Team Epsilon</t>
-  </si>
-  <si>
-    <t>STARK</t>
-  </si>
-  <si>
-    <t>Othello</t>
-  </si>
-  <si>
-    <t>Team Omicron</t>
-  </si>
-  <si>
-    <t>OTHELLO</t>
-  </si>
-  <si>
-    <t>Tyrion Lannister</t>
-  </si>
-  <si>
-    <t>Team Upsilon</t>
-  </si>
-  <si>
-    <t>Pool E</t>
-  </si>
-  <si>
-    <t>Daenerys Targaryen</t>
-  </si>
-  <si>
-    <t>Team Delta</t>
-  </si>
-  <si>
-    <t>TARGARYEN</t>
-  </si>
-  <si>
-    <t>Inigo Montoya</t>
-  </si>
-  <si>
-    <t>Team Iota</t>
-  </si>
-  <si>
-    <t>MONTOYA</t>
-  </si>
-  <si>
-    <t>Willy Wonka</t>
-  </si>
-  <si>
-    <t>Team Psi</t>
-  </si>
-  <si>
-    <t>WONKA</t>
-  </si>
-  <si>
-    <t>Pool F</t>
-  </si>
-  <si>
-    <t>Legolas Greenleaf</t>
-  </si>
-  <si>
-    <t>GREENLEAF</t>
   </si>
   <si>
     <t>Team Lambda</t>
@@ -1215,10 +1215,10 @@
         <v>37</v>
       </c>
       <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
         <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -1226,13 +1226,13 @@
         <v>36</v>
       </c>
       <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
         <v>40</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>41</v>
-      </c>
-      <c r="D10" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -1240,52 +1240,52 @@
         <v>36</v>
       </c>
       <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
         <v>43</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>44</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
         <v>46</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>47</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>48</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
         <v>50</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>51</v>
-      </c>
-      <c r="D13" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" t="s">
         <v>53</v>
-      </c>
-      <c r="C14" t="s">
-        <v>54</v>
       </c>
       <c r="D14" t="s">
         <v>19</v>
@@ -1293,55 +1293,55 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" t="s">
         <v>55</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>56</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>57</v>
-      </c>
-      <c r="D15" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" t="s">
         <v>59</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>60</v>
-      </c>
-      <c r="D16" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" t="s">
         <v>62</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>63</v>
-      </c>
-      <c r="D17" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" t="s">
         <v>65</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>66</v>
-      </c>
-      <c r="C18" t="s">
-        <v>28</v>
       </c>
       <c r="D18" t="s">
         <v>67</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
@@ -1363,7 +1363,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s">
         <v>69</v>

--- a/pools-example-medium-seeded.xlsx
+++ b/pools-example-medium-seeded.xlsx
@@ -94,6 +94,27 @@
     <t>LANNISTER</t>
   </si>
   <si>
+    <t>Katniss Everdeen</t>
+  </si>
+  <si>
+    <t>Team Lambda</t>
+  </si>
+  <si>
+    <t>EVERDEEN</t>
+  </si>
+  <si>
+    <t>Ron Weasley</t>
+  </si>
+  <si>
+    <t>Team Sigma</t>
+  </si>
+  <si>
+    <t>WEASLEY</t>
+  </si>
+  <si>
+    <t>Pool B</t>
+  </si>
+  <si>
     <t>Gandalf The Grey</t>
   </si>
   <si>
@@ -103,6 +124,63 @@
     <t>GANDALF</t>
   </si>
   <si>
+    <t>Moby Dick</t>
+  </si>
+  <si>
+    <t>Team Nu</t>
+  </si>
+  <si>
+    <t>DICK</t>
+  </si>
+  <si>
+    <t>Tyrion Lannister</t>
+  </si>
+  <si>
+    <t>Team Upsilon</t>
+  </si>
+  <si>
+    <t>Pool C</t>
+  </si>
+  <si>
+    <t>Inigo Montoya</t>
+  </si>
+  <si>
+    <t>Team Iota</t>
+  </si>
+  <si>
+    <t>MONTOYA</t>
+  </si>
+  <si>
+    <t>Legolas Greenleaf</t>
+  </si>
+  <si>
+    <t>Team Mu</t>
+  </si>
+  <si>
+    <t>GREENLEAF</t>
+  </si>
+  <si>
+    <t>Voldemort</t>
+  </si>
+  <si>
+    <t>Team Chi</t>
+  </si>
+  <si>
+    <t>VOLDEMORT</t>
+  </si>
+  <si>
+    <t>Pool D</t>
+  </si>
+  <si>
+    <t>Eddard Stark</t>
+  </si>
+  <si>
+    <t>Team Epsilon</t>
+  </si>
+  <si>
+    <t>STARK</t>
+  </si>
+  <si>
     <t>Petyr Baelish</t>
   </si>
   <si>
@@ -112,16 +190,67 @@
     <t>BAELISH</t>
   </si>
   <si>
-    <t>Pool B</t>
-  </si>
-  <si>
-    <t>Katniss Everdeen</t>
-  </si>
-  <si>
-    <t>Team Mu</t>
-  </si>
-  <si>
-    <t>EVERDEEN</t>
+    <t>Xaro Xhoan Daxos</t>
+  </si>
+  <si>
+    <t>Team Omega</t>
+  </si>
+  <si>
+    <t>DAXOS</t>
+  </si>
+  <si>
+    <t>Pool E</t>
+  </si>
+  <si>
+    <t>Daenerys Targaryen</t>
+  </si>
+  <si>
+    <t>Team Delta</t>
+  </si>
+  <si>
+    <t>TARGARYEN</t>
+  </si>
+  <si>
+    <t>Samwise Gamgee</t>
+  </si>
+  <si>
+    <t>Team Tau</t>
+  </si>
+  <si>
+    <t>GAMGEE</t>
+  </si>
+  <si>
+    <t>Pool F</t>
+  </si>
+  <si>
+    <t>Hermione Granger</t>
+  </si>
+  <si>
+    <t>Team Theta</t>
+  </si>
+  <si>
+    <t>GRANGER</t>
+  </si>
+  <si>
+    <t>Neville Longbottom</t>
+  </si>
+  <si>
+    <t>Team Xi</t>
+  </si>
+  <si>
+    <t>LONGBOTTOM</t>
+  </si>
+  <si>
+    <t>Ulysses</t>
+  </si>
+  <si>
+    <t>Team Phi</t>
+  </si>
+  <si>
+    <t>ULYSSES</t>
+  </si>
+  <si>
+    <t>Pool G</t>
   </si>
   <si>
     <t>Jon Snow</t>
@@ -133,6 +262,36 @@
     <t>SNOW</t>
   </si>
   <si>
+    <t>Othello</t>
+  </si>
+  <si>
+    <t>Team Omicron</t>
+  </si>
+  <si>
+    <t>OTHELLO</t>
+  </si>
+  <si>
+    <t>Willy Wonka</t>
+  </si>
+  <si>
+    <t>Team Psi</t>
+  </si>
+  <si>
+    <t>WONKA</t>
+  </si>
+  <si>
+    <t>Pool H</t>
+  </si>
+  <si>
+    <t>Frodo Baggins</t>
+  </si>
+  <si>
+    <t>Team Zeta</t>
+  </si>
+  <si>
+    <t>BAGGINS</t>
+  </si>
+  <si>
     <t>Quirinus Quirrell</t>
   </si>
   <si>
@@ -142,93 +301,6 @@
     <t>QUIRRELL</t>
   </si>
   <si>
-    <t>Pool C</t>
-  </si>
-  <si>
-    <t>Legolas Greenleaf</t>
-  </si>
-  <si>
-    <t>GREENLEAF</t>
-  </si>
-  <si>
-    <t>Moby Dick</t>
-  </si>
-  <si>
-    <t>Team Nu</t>
-  </si>
-  <si>
-    <t>DICK</t>
-  </si>
-  <si>
-    <t>Samwise Gamgee</t>
-  </si>
-  <si>
-    <t>Team Tau</t>
-  </si>
-  <si>
-    <t>GAMGEE</t>
-  </si>
-  <si>
-    <t>Pool D</t>
-  </si>
-  <si>
-    <t>Eddard Stark</t>
-  </si>
-  <si>
-    <t>Team Epsilon</t>
-  </si>
-  <si>
-    <t>STARK</t>
-  </si>
-  <si>
-    <t>Othello</t>
-  </si>
-  <si>
-    <t>Team Omicron</t>
-  </si>
-  <si>
-    <t>OTHELLO</t>
-  </si>
-  <si>
-    <t>Tyrion Lannister</t>
-  </si>
-  <si>
-    <t>Team Upsilon</t>
-  </si>
-  <si>
-    <t>Pool E</t>
-  </si>
-  <si>
-    <t>Daenerys Targaryen</t>
-  </si>
-  <si>
-    <t>Team Delta</t>
-  </si>
-  <si>
-    <t>TARGARYEN</t>
-  </si>
-  <si>
-    <t>Inigo Montoya</t>
-  </si>
-  <si>
-    <t>Team Iota</t>
-  </si>
-  <si>
-    <t>MONTOYA</t>
-  </si>
-  <si>
-    <t>Willy Wonka</t>
-  </si>
-  <si>
-    <t>Team Psi</t>
-  </si>
-  <si>
-    <t>WONKA</t>
-  </si>
-  <si>
-    <t>Pool F</t>
-  </si>
-  <si>
     <t>Ygritte</t>
   </si>
   <si>
@@ -236,78 +308,6 @@
   </si>
   <si>
     <t>YGRITTE</t>
-  </si>
-  <si>
-    <t>Team Lambda</t>
-  </si>
-  <si>
-    <t>Ron Weasley</t>
-  </si>
-  <si>
-    <t>Team Sigma</t>
-  </si>
-  <si>
-    <t>WEASLEY</t>
-  </si>
-  <si>
-    <t>Pool G</t>
-  </si>
-  <si>
-    <t>Voldemort</t>
-  </si>
-  <si>
-    <t>Team Chi</t>
-  </si>
-  <si>
-    <t>VOLDEMORT</t>
-  </si>
-  <si>
-    <t>Xaro Xhoan Daxos</t>
-  </si>
-  <si>
-    <t>Team Omega</t>
-  </si>
-  <si>
-    <t>DAXOS</t>
-  </si>
-  <si>
-    <t>Hermione Granger</t>
-  </si>
-  <si>
-    <t>Team Theta</t>
-  </si>
-  <si>
-    <t>GRANGER</t>
-  </si>
-  <si>
-    <t>Pool H</t>
-  </si>
-  <si>
-    <t>Frodo Baggins</t>
-  </si>
-  <si>
-    <t>Team Zeta</t>
-  </si>
-  <si>
-    <t>BAGGINS</t>
-  </si>
-  <si>
-    <t>Ulysses</t>
-  </si>
-  <si>
-    <t>Team Phi</t>
-  </si>
-  <si>
-    <t>ULYSSES</t>
-  </si>
-  <si>
-    <t>Neville Longbottom</t>
-  </si>
-  <si>
-    <t>Team Xi</t>
-  </si>
-  <si>
-    <t>LONGBOTTOM</t>
   </si>
   <si>
     <t>Shiaijo A</t>
@@ -1204,18 +1204,18 @@
         <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
         <v>36</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
       </c>
       <c r="D9" t="s">
         <v>38</v>
@@ -1223,7 +1223,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
         <v>39</v>
@@ -1237,7 +1237,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
         <v>42</v>
@@ -1288,82 +1288,82 @@
         <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" t="s">
         <v>61</v>
-      </c>
-      <c r="C17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" t="s">
         <v>64</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" t="s">
         <v>65</v>
-      </c>
-      <c r="C18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" t="s">
         <v>68</v>
-      </c>
-      <c r="D19" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
         <v>69</v>

--- a/pools-example-medium-seeded.xlsx
+++ b/pools-example-medium-seeded.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
   <si>
     <t>Number of pools</t>
   </si>
@@ -79,6 +79,9 @@
     <t>Display Name</t>
   </si>
   <si>
+    <t>Player Number</t>
+  </si>
+  <si>
     <t>Metadata</t>
   </si>
   <si>
@@ -94,6 +97,9 @@
     <t>LANNISTER</t>
   </si>
   <si>
+    <t>K1</t>
+  </si>
+  <si>
     <t>Katniss Everdeen</t>
   </si>
   <si>
@@ -103,6 +109,9 @@
     <t>EVERDEEN</t>
   </si>
   <si>
+    <t>K2</t>
+  </si>
+  <si>
     <t>Ron Weasley</t>
   </si>
   <si>
@@ -112,6 +121,9 @@
     <t>WEASLEY</t>
   </si>
   <si>
+    <t>K3</t>
+  </si>
+  <si>
     <t>Pool B</t>
   </si>
   <si>
@@ -124,6 +136,9 @@
     <t>GANDALF</t>
   </si>
   <si>
+    <t>K4</t>
+  </si>
+  <si>
     <t>Moby Dick</t>
   </si>
   <si>
@@ -133,12 +148,18 @@
     <t>DICK</t>
   </si>
   <si>
+    <t>K5</t>
+  </si>
+  <si>
     <t>Tyrion Lannister</t>
   </si>
   <si>
     <t>Team Upsilon</t>
   </si>
   <si>
+    <t>K6</t>
+  </si>
+  <si>
     <t>Pool C</t>
   </si>
   <si>
@@ -151,6 +172,9 @@
     <t>MONTOYA</t>
   </si>
   <si>
+    <t>K7</t>
+  </si>
+  <si>
     <t>Legolas Greenleaf</t>
   </si>
   <si>
@@ -160,6 +184,9 @@
     <t>GREENLEAF</t>
   </si>
   <si>
+    <t>K8</t>
+  </si>
+  <si>
     <t>Voldemort</t>
   </si>
   <si>
@@ -169,6 +196,9 @@
     <t>VOLDEMORT</t>
   </si>
   <si>
+    <t>K9</t>
+  </si>
+  <si>
     <t>Pool D</t>
   </si>
   <si>
@@ -181,6 +211,9 @@
     <t>STARK</t>
   </si>
   <si>
+    <t>K10</t>
+  </si>
+  <si>
     <t>Petyr Baelish</t>
   </si>
   <si>
@@ -190,6 +223,9 @@
     <t>BAELISH</t>
   </si>
   <si>
+    <t>K11</t>
+  </si>
+  <si>
     <t>Xaro Xhoan Daxos</t>
   </si>
   <si>
@@ -199,6 +235,9 @@
     <t>DAXOS</t>
   </si>
   <si>
+    <t>K12</t>
+  </si>
+  <si>
     <t>Pool E</t>
   </si>
   <si>
@@ -211,6 +250,12 @@
     <t>TARGARYEN</t>
   </si>
   <si>
+    <t>K13</t>
+  </si>
+  <si>
+    <t>K14</t>
+  </si>
+  <si>
     <t>Samwise Gamgee</t>
   </si>
   <si>
@@ -220,6 +265,9 @@
     <t>GAMGEE</t>
   </si>
   <si>
+    <t>K15</t>
+  </si>
+  <si>
     <t>Pool F</t>
   </si>
   <si>
@@ -232,6 +280,9 @@
     <t>GRANGER</t>
   </si>
   <si>
+    <t>K16</t>
+  </si>
+  <si>
     <t>Neville Longbottom</t>
   </si>
   <si>
@@ -241,6 +292,9 @@
     <t>LONGBOTTOM</t>
   </si>
   <si>
+    <t>K17</t>
+  </si>
+  <si>
     <t>Ulysses</t>
   </si>
   <si>
@@ -250,6 +304,9 @@
     <t>ULYSSES</t>
   </si>
   <si>
+    <t>K18</t>
+  </si>
+  <si>
     <t>Pool G</t>
   </si>
   <si>
@@ -262,6 +319,9 @@
     <t>SNOW</t>
   </si>
   <si>
+    <t>K19</t>
+  </si>
+  <si>
     <t>Othello</t>
   </si>
   <si>
@@ -271,6 +331,9 @@
     <t>OTHELLO</t>
   </si>
   <si>
+    <t>K20</t>
+  </si>
+  <si>
     <t>Willy Wonka</t>
   </si>
   <si>
@@ -280,6 +343,9 @@
     <t>WONKA</t>
   </si>
   <si>
+    <t>K21</t>
+  </si>
+  <si>
     <t>Pool H</t>
   </si>
   <si>
@@ -292,6 +358,9 @@
     <t>BAGGINS</t>
   </si>
   <si>
+    <t>K22</t>
+  </si>
+  <si>
     <t>Quirinus Quirrell</t>
   </si>
   <si>
@@ -301,6 +370,9 @@
     <t>QUIRRELL</t>
   </si>
   <si>
+    <t>K23</t>
+  </si>
+  <si>
     <t>Ygritte</t>
   </si>
   <si>
@@ -310,6 +382,9 @@
     <t>YGRITTE</t>
   </si>
   <si>
+    <t>K24</t>
+  </si>
+  <si>
     <t>Shiaijo A</t>
   </si>
   <si>
@@ -356,78 +431,6 @@
   </si>
   <si>
     <t>3.</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
-    <t>D3</t>
-  </si>
-  <si>
-    <t>E1</t>
-  </si>
-  <si>
-    <t>E2</t>
-  </si>
-  <si>
-    <t>E3</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
-    <t>F2</t>
-  </si>
-  <si>
-    <t>F3</t>
-  </si>
-  <si>
-    <t>G1</t>
-  </si>
-  <si>
-    <t>G2</t>
-  </si>
-  <si>
-    <t>G3</t>
-  </si>
-  <si>
-    <t>H1</t>
-  </si>
-  <si>
-    <t>H2</t>
-  </si>
-  <si>
-    <t>H3</t>
   </si>
   <si>
     <t>Round 1 - Match 1</t>
@@ -1122,341 +1125,416 @@
       <c r="E2" t="s">
         <v>15</v>
       </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>45</v>
+      </c>
+      <c r="E9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>49</v>
+      </c>
+      <c r="E10" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>58</v>
+      </c>
+      <c r="E12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>62</v>
+      </c>
+      <c r="E13" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>66</v>
+      </c>
+      <c r="E14" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>71</v>
+      </c>
+      <c r="E15" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>76</v>
+      </c>
+      <c r="E17" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>81</v>
+      </c>
+      <c r="E18" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>85</v>
+      </c>
+      <c r="E19" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>71</v>
+        <v>89</v>
+      </c>
+      <c r="E20" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>94</v>
+      </c>
+      <c r="E21" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>98</v>
+      </c>
+      <c r="E22" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>102</v>
+      </c>
+      <c r="E23" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>107</v>
+      </c>
+      <c r="E24" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>111</v>
+      </c>
+      <c r="E25" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>115</v>
+      </c>
+      <c r="E26" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1474,96 +1552,96 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="28" t="s">
-        <v>108</v>
+      <c r="A1" s="28" t="str">
+        <f>'data'!$E$3</f>
       </c>
       <c r="B1" s="29" t="str">
         <f>'data'!D3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="28" t="s">
-        <v>109</v>
+      <c r="A2" s="28" t="str">
+        <f>'data'!$E$4</f>
       </c>
       <c r="B2" s="29" t="str">
         <f>'data'!D4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="28" t="s">
-        <v>110</v>
+      <c r="A3" s="28" t="str">
+        <f>'data'!$E$5</f>
       </c>
       <c r="B3" s="29" t="str">
         <f>'data'!D5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="28" t="s">
-        <v>111</v>
+      <c r="A4" s="28" t="str">
+        <f>'data'!$E$6</f>
       </c>
       <c r="B4" s="29" t="str">
         <f>'data'!D6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="28" t="s">
-        <v>112</v>
+      <c r="A5" s="28" t="str">
+        <f>'data'!$E$7</f>
       </c>
       <c r="B5" s="29" t="str">
         <f>'data'!D7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="28" t="s">
-        <v>113</v>
+      <c r="A6" s="28" t="str">
+        <f>'data'!$E$8</f>
       </c>
       <c r="B6" s="29" t="str">
         <f>'data'!D8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="28" t="s">
-        <v>114</v>
+      <c r="A7" s="28" t="str">
+        <f>'data'!$E$9</f>
       </c>
       <c r="B7" s="29" t="str">
         <f>'data'!D9</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="28" t="s">
-        <v>115</v>
+      <c r="A8" s="28" t="str">
+        <f>'data'!$E$10</f>
       </c>
       <c r="B8" s="29" t="str">
         <f>'data'!D10</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="28" t="s">
-        <v>116</v>
+      <c r="A9" s="28" t="str">
+        <f>'data'!$E$11</f>
       </c>
       <c r="B9" s="29" t="str">
         <f>'data'!D11</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="28" t="s">
-        <v>117</v>
+      <c r="A10" s="28" t="str">
+        <f>'data'!$E$12</f>
       </c>
       <c r="B10" s="29" t="str">
         <f>'data'!D12</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="28" t="s">
-        <v>118</v>
+      <c r="A11" s="28" t="str">
+        <f>'data'!$E$13</f>
       </c>
       <c r="B11" s="29" t="str">
         <f>'data'!D13</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="28" t="s">
-        <v>119</v>
+      <c r="A12" s="28" t="str">
+        <f>'data'!$E$14</f>
       </c>
       <c r="B12" s="29" t="str">
         <f>'data'!D14</f>
@@ -1592,96 +1670,96 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="28" t="s">
-        <v>120</v>
+      <c r="A1" s="28" t="str">
+        <f>'data'!$E$15</f>
       </c>
       <c r="B1" s="29" t="str">
         <f>'data'!D15</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="28" t="s">
-        <v>121</v>
+      <c r="A2" s="28" t="str">
+        <f>'data'!$E$16</f>
       </c>
       <c r="B2" s="29" t="str">
         <f>'data'!D16</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="28" t="s">
-        <v>122</v>
+      <c r="A3" s="28" t="str">
+        <f>'data'!$E$17</f>
       </c>
       <c r="B3" s="29" t="str">
         <f>'data'!D17</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="28" t="s">
-        <v>123</v>
+      <c r="A4" s="28" t="str">
+        <f>'data'!$E$18</f>
       </c>
       <c r="B4" s="29" t="str">
         <f>'data'!D18</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="28" t="s">
-        <v>124</v>
+      <c r="A5" s="28" t="str">
+        <f>'data'!$E$19</f>
       </c>
       <c r="B5" s="29" t="str">
         <f>'data'!D19</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="28" t="s">
-        <v>125</v>
+      <c r="A6" s="28" t="str">
+        <f>'data'!$E$20</f>
       </c>
       <c r="B6" s="29" t="str">
         <f>'data'!D20</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="28" t="s">
-        <v>126</v>
+      <c r="A7" s="28" t="str">
+        <f>'data'!$E$21</f>
       </c>
       <c r="B7" s="29" t="str">
         <f>'data'!D21</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="28" t="s">
-        <v>127</v>
+      <c r="A8" s="28" t="str">
+        <f>'data'!$E$22</f>
       </c>
       <c r="B8" s="29" t="str">
         <f>'data'!D22</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="28" t="s">
-        <v>128</v>
+      <c r="A9" s="28" t="str">
+        <f>'data'!$E$23</f>
       </c>
       <c r="B9" s="29" t="str">
         <f>'data'!D23</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="28" t="s">
-        <v>129</v>
+      <c r="A10" s="28" t="str">
+        <f>'data'!$E$24</f>
       </c>
       <c r="B10" s="29" t="str">
         <f>'data'!D24</f>
       </c>
     </row>
     <row r="11" ht="270" customHeight="true">
-      <c r="A11" s="28" t="s">
-        <v>130</v>
+      <c r="A11" s="28" t="str">
+        <f>'data'!$E$25</f>
       </c>
       <c r="B11" s="29" t="str">
         <f>'data'!D25</f>
       </c>
     </row>
     <row r="12" ht="270" customHeight="true">
-      <c r="A12" s="28" t="s">
-        <v>131</v>
+      <c r="A12" s="28" t="str">
+        <f>'data'!$E$26</f>
       </c>
       <c r="B12" s="29" t="str">
         <f>'data'!D26</f>
@@ -1710,242 +1788,242 @@
   <sheetData>
     <row r="1" ht="409" customHeight="true">
       <c r="A1" s="30" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" ht="409" customHeight="true">
       <c r="A2" s="30" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" ht="409" customHeight="true">
       <c r="A3" s="30" t="s">
-        <v>109</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" ht="409" customHeight="true">
       <c r="A4" s="30" t="s">
-        <v>109</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" ht="409" customHeight="true">
       <c r="A5" s="30" t="s">
-        <v>110</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="409" customHeight="true">
       <c r="A6" s="30" t="s">
-        <v>110</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" ht="409" customHeight="true">
       <c r="A7" s="30" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" ht="409" customHeight="true">
       <c r="A8" s="30" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="409" customHeight="true">
       <c r="A9" s="30" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" ht="409" customHeight="true">
       <c r="A10" s="30" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" ht="409" customHeight="true">
       <c r="A11" s="30" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" ht="409" customHeight="true">
       <c r="A12" s="30" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" ht="409" customHeight="true">
       <c r="A13" s="30" t="s">
-        <v>114</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" ht="409" customHeight="true">
       <c r="A14" s="30" t="s">
-        <v>114</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" ht="409" customHeight="true">
       <c r="A15" s="30" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" ht="409" customHeight="true">
       <c r="A16" s="30" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" ht="409" customHeight="true">
       <c r="A17" s="30" t="s">
-        <v>116</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" ht="409" customHeight="true">
       <c r="A18" s="30" t="s">
-        <v>116</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" ht="409" customHeight="true">
       <c r="A19" s="30" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" ht="409" customHeight="true">
       <c r="A20" s="30" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" ht="409" customHeight="true">
       <c r="A21" s="30" t="s">
-        <v>118</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" ht="409" customHeight="true">
       <c r="A22" s="30" t="s">
-        <v>118</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" ht="409" customHeight="true">
       <c r="A23" s="30" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" ht="409" customHeight="true">
       <c r="A24" s="30" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" ht="409" customHeight="true">
       <c r="A25" s="30" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" ht="409" customHeight="true">
       <c r="A26" s="30" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" ht="409" customHeight="true">
       <c r="A27" s="30" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" ht="409" customHeight="true">
       <c r="A28" s="30" t="s">
-        <v>121</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" ht="409" customHeight="true">
       <c r="A29" s="30" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" ht="409" customHeight="true">
       <c r="A30" s="30" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" ht="409" customHeight="true">
       <c r="A31" s="30" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" ht="409" customHeight="true">
       <c r="A32" s="30" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" ht="409" customHeight="true">
       <c r="A33" s="30" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" ht="409" customHeight="true">
       <c r="A34" s="30" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" ht="409" customHeight="true">
       <c r="A35" s="30" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" ht="409" customHeight="true">
       <c r="A36" s="30" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" ht="409" customHeight="true">
       <c r="A37" s="30" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" ht="409" customHeight="true">
       <c r="A38" s="30" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" ht="409" customHeight="true">
       <c r="A39" s="30" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" ht="409" customHeight="true">
       <c r="A40" s="30" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" ht="409" customHeight="true">
       <c r="A41" s="30" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" ht="409" customHeight="true">
       <c r="A42" s="30" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" ht="409" customHeight="true">
       <c r="A43" s="30" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" ht="409" customHeight="true">
       <c r="A44" s="30" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" ht="409" customHeight="true">
       <c r="A45" s="30" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" ht="409" customHeight="true">
       <c r="A46" s="30" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" ht="409" customHeight="true">
       <c r="A47" s="30" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" ht="409" customHeight="true">
       <c r="A48" s="30" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2182,7 +2260,7 @@
     </row>
     <row r="13">
       <c r="E13" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
@@ -2193,7 +2271,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="32" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -2203,7 +2281,7 @@
     </row>
     <row r="15">
       <c r="E15" s="32" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F15" s="32"/>
       <c r="G15" s="32"/>
@@ -2213,7 +2291,7 @@
     </row>
     <row r="16">
       <c r="E16" s="32" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F16" s="32"/>
       <c r="G16" s="32"/>
@@ -2223,7 +2301,7 @@
     </row>
     <row r="17">
       <c r="E17" s="32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F17" s="32"/>
       <c r="G17" s="32"/>
@@ -2233,7 +2311,7 @@
     </row>
     <row r="18">
       <c r="E18" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
@@ -2243,7 +2321,7 @@
     </row>
     <row r="19">
       <c r="E19" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
@@ -2316,35 +2394,35 @@
     </row>
     <row r="6" ht="17" customHeight="true">
       <c r="B6" s="12" t="str">
-        <f>"1. " &amp; data!$B$3</f>
+        <f>data!$E$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="D6" s="12" t="str">
-        <f>"1. " &amp; data!$B$12</f>
+        <f>data!$E$12&amp;" "&amp;data!$B$12</f>
       </c>
       <c r="F6" s="12" t="str">
-        <f>"1. " &amp; data!$B$21</f>
+        <f>data!$E$21&amp;" "&amp;data!$B$21</f>
       </c>
     </row>
     <row r="7" ht="17" customHeight="true">
       <c r="B7" s="12" t="str">
-        <f>"2. " &amp; data!$B$4</f>
+        <f>data!$E$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="D7" s="12" t="str">
-        <f>"2. " &amp; data!$B$13</f>
+        <f>data!$E$13&amp;" "&amp;data!$B$13</f>
       </c>
       <c r="F7" s="12" t="str">
-        <f>"2. " &amp; data!$B$22</f>
+        <f>data!$E$22&amp;" "&amp;data!$B$22</f>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="12" t="str">
-        <f>"3. " &amp; data!$B$5</f>
+        <f>data!$E$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="D8" s="12" t="str">
-        <f>"3. " &amp; data!$B$14</f>
+        <f>data!$E$14&amp;" "&amp;data!$B$14</f>
       </c>
       <c r="F8" s="12" t="str">
-        <f>"3. " &amp; data!$B$23</f>
+        <f>data!$E$23&amp;" "&amp;data!$B$23</f>
       </c>
     </row>
     <row r="11">
@@ -2360,35 +2438,35 @@
     </row>
     <row r="12">
       <c r="B12" s="12" t="str">
-        <f>"1. " &amp; data!$B$6</f>
+        <f>data!$E$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="D12" s="12" t="str">
-        <f>"1. " &amp; data!$B$15</f>
+        <f>data!$E$15&amp;" "&amp;data!$B$15</f>
       </c>
       <c r="F12" s="12" t="str">
-        <f>"1. " &amp; data!$B$24</f>
+        <f>data!$E$24&amp;" "&amp;data!$B$24</f>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="12" t="str">
-        <f>"2. " &amp; data!$B$7</f>
+        <f>data!$E$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="D13" s="12" t="str">
-        <f>"2. " &amp; data!$B$16</f>
+        <f>data!$E$16&amp;" "&amp;data!$B$16</f>
       </c>
       <c r="F13" s="12" t="str">
-        <f>"2. " &amp; data!$B$25</f>
+        <f>data!$E$25&amp;" "&amp;data!$B$25</f>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="12" t="str">
-        <f>"3. " &amp; data!$B$8</f>
+        <f>data!$E$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="D14" s="12" t="str">
-        <f>"3. " &amp; data!$B$17</f>
+        <f>data!$E$17&amp;" "&amp;data!$B$17</f>
       </c>
       <c r="F14" s="12" t="str">
-        <f>"3. " &amp; data!$B$26</f>
+        <f>data!$E$26&amp;" "&amp;data!$B$26</f>
       </c>
     </row>
     <row r="17">
@@ -2401,26 +2479,26 @@
     </row>
     <row r="18">
       <c r="B18" s="12" t="str">
-        <f>"1. " &amp; data!$B$9</f>
+        <f>data!$E$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="D18" s="12" t="str">
-        <f>"1. " &amp; data!$B$18</f>
+        <f>data!$E$18&amp;" "&amp;data!$B$18</f>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="12" t="str">
-        <f>"2. " &amp; data!$B$10</f>
+        <f>data!$E$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="D19" s="12" t="str">
-        <f>"2. " &amp; data!$B$19</f>
+        <f>data!$E$19&amp;" "&amp;data!$B$19</f>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="12" t="str">
-        <f>"3. " &amp; data!$B$11</f>
+        <f>data!$E$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="D20" s="12" t="str">
-        <f>"3. " &amp; data!$B$20</f>
+        <f>data!$E$20&amp;" "&amp;data!$B$20</f>
       </c>
     </row>
   </sheetData>
@@ -2455,7 +2533,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -2464,7 +2542,7 @@
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
       <c r="I1" s="13" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
@@ -2495,27 +2573,27 @@
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$E$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -2523,10 +2601,10 @@
       <c r="E4" s="18"/>
       <c r="F4" s="18"/>
       <c r="G4" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$E$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="I4" s="14" t="str">
-        <f>'data'!$B$16</f>
+        <f>data!$E$16&amp;" "&amp;data!$B$16</f>
       </c>
       <c r="J4" s="18"/>
       <c r="K4" s="18"/>
@@ -2534,12 +2612,12 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
       <c r="O4" s="14" t="str">
-        <f>'data'!$B$15</f>
+        <f>data!$E$15&amp;" "&amp;data!$B$15</f>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$E$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -2547,10 +2625,10 @@
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
       <c r="G5" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$E$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="I5" s="14" t="str">
-        <f>'data'!$B$17</f>
+        <f>data!$E$17&amp;" "&amp;data!$B$17</f>
       </c>
       <c r="J5" s="18"/>
       <c r="K5" s="18"/>
@@ -2558,12 +2636,12 @@
       <c r="M5" s="18"/>
       <c r="N5" s="18"/>
       <c r="O5" s="14" t="str">
-        <f>'data'!$B$15</f>
+        <f>data!$E$15&amp;" "&amp;data!$B$15</f>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$E$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -2571,10 +2649,10 @@
       <c r="E6" s="18"/>
       <c r="F6" s="18"/>
       <c r="G6" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$E$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="I6" s="14" t="str">
-        <f>'data'!$B$17</f>
+        <f>data!$E$17&amp;" "&amp;data!$B$17</f>
       </c>
       <c r="J6" s="18"/>
       <c r="K6" s="18"/>
@@ -2582,56 +2660,56 @@
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
       <c r="O6" s="14" t="str">
-        <f>'data'!$B$16</f>
+        <f>data!$E$16&amp;" "&amp;data!$B$16</f>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="str">
-        <f>'data'!$B$3</f>
+        <f>data!$E$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="B9" s="14" t="str">
         <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))*1),0)</f>
@@ -2652,7 +2730,7 @@
         <f>RANK(U9,$U$9:$U$11)+COUNTIF($U$8:U8,U9)</f>
       </c>
       <c r="I9" s="14" t="str">
-        <f>'data'!$B$15</f>
+        <f>data!$E$15&amp;" "&amp;data!$B$15</f>
       </c>
       <c r="J9" s="14" t="str">
         <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))*1),0)</f>
@@ -2681,7 +2759,7 @@
     </row>
     <row r="10">
       <c r="A10" s="14" t="str">
-        <f>'data'!$B$4</f>
+        <f>data!$E$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="B10" s="14" t="str">
         <f>IF(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),IF(OR(D4="X",D4="x",AND(OR(COUNTA(B4,C4,E4,F4)&gt;0,OR(D4="X",D4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))*1),0)</f>
@@ -2702,7 +2780,7 @@
         <f>RANK(U10,$U$9:$U$11)+COUNTIF($U$8:U9,U10)</f>
       </c>
       <c r="I10" s="14" t="str">
-        <f>'data'!$B$16</f>
+        <f>data!$E$16&amp;" "&amp;data!$B$16</f>
       </c>
       <c r="J10" s="14" t="str">
         <f>IF(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),IF(OR(L4="X",L4="x",AND(OR(COUNTA(J4,K4,M4,N4)&gt;0,OR(L4="X",L4="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K4," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M4," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N4," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))*1),0)</f>
@@ -2731,7 +2809,7 @@
     </row>
     <row r="11">
       <c r="A11" s="14" t="str">
-        <f>'data'!$B$5</f>
+        <f>data!$E$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="B11" s="14" t="str">
         <f>IF(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),IF(OR(D5="X",D5="x",AND(OR(COUNTA(B5,C5,E5,F5)&gt;0,OR(D5="X",D5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),IF(OR(D6="X",D6="x",AND(OR(COUNTA(B6,C6,E6,F6)&gt;0,OR(D6="X",D6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))*1),0)</f>
@@ -2752,7 +2830,7 @@
         <f>RANK(U11,$U$9:$U$11)+COUNTIF($U$8:U10,U11)</f>
       </c>
       <c r="I11" s="14" t="str">
-        <f>'data'!$B$17</f>
+        <f>data!$E$17&amp;" "&amp;data!$B$17</f>
       </c>
       <c r="J11" s="14" t="str">
         <f>IF(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),IF(OR(L5="X",L5="x",AND(OR(COUNTA(J5,K5,M5,N5)&gt;0,OR(L5="X",L5="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K5," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N5," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),IF(OR(L6="X",L6="x",AND(OR(COUNTA(J6,K6,M6,N6)&gt;0,OR(L6="X",L6="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K6," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N6," ",""),"0",""),"-","")))*1),0)</f>
@@ -2782,22 +2860,22 @@
     <row r="14">
       <c r="F14" s="13"/>
       <c r="G14" s="13" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="N14" s="13"/>
       <c r="O14" s="13" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15">
       <c r="F15" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G15" s="19" t="str">
         <f>IFERROR(INDEX($A$9:$A$11, MATCH(1, $G$9:$G$11, 0)), "-")</f>
       </c>
       <c r="N15" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O15" s="19" t="str">
         <f>IFERROR(INDEX($I$9:$I$11, MATCH(1, $O$9:$O$11, 0)), "-")</f>
@@ -2805,13 +2883,13 @@
     </row>
     <row r="16">
       <c r="F16" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G16" s="19" t="str">
         <f>IFERROR(INDEX($A$9:$A$11, MATCH(2, $G$9:$G$11, 0)), "-")</f>
       </c>
       <c r="N16" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O16" s="19" t="str">
         <f>IFERROR(INDEX($I$9:$I$11, MATCH(2, $O$9:$O$11, 0)), "-")</f>
@@ -2819,13 +2897,13 @@
     </row>
     <row r="17">
       <c r="F17" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="G17" s="19" t="str">
         <f>IFERROR(INDEX($A$9:$A$11, MATCH(3, $G$9:$G$11, 0)), "-")</f>
       </c>
       <c r="N17" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="O17" s="19" t="str">
         <f>IFERROR(INDEX($I$9:$I$11, MATCH(3, $O$9:$O$11, 0)), "-")</f>
@@ -2853,27 +2931,27 @@
     </row>
     <row r="20">
       <c r="A20" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O20" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$E$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -2881,10 +2959,10 @@
       <c r="E21" s="18"/>
       <c r="F21" s="18"/>
       <c r="G21" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$E$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="I21" s="14" t="str">
-        <f>'data'!$B$19</f>
+        <f>data!$E$19&amp;" "&amp;data!$B$19</f>
       </c>
       <c r="J21" s="18"/>
       <c r="K21" s="18"/>
@@ -2892,12 +2970,12 @@
       <c r="M21" s="18"/>
       <c r="N21" s="18"/>
       <c r="O21" s="14" t="str">
-        <f>'data'!$B$18</f>
+        <f>data!$E$18&amp;" "&amp;data!$B$18</f>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$E$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -2905,10 +2983,10 @@
       <c r="E22" s="18"/>
       <c r="F22" s="18"/>
       <c r="G22" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$E$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="I22" s="14" t="str">
-        <f>'data'!$B$20</f>
+        <f>data!$E$20&amp;" "&amp;data!$B$20</f>
       </c>
       <c r="J22" s="18"/>
       <c r="K22" s="18"/>
@@ -2916,12 +2994,12 @@
       <c r="M22" s="18"/>
       <c r="N22" s="18"/>
       <c r="O22" s="14" t="str">
-        <f>'data'!$B$18</f>
+        <f>data!$E$18&amp;" "&amp;data!$B$18</f>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$E$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -2929,10 +3007,10 @@
       <c r="E23" s="18"/>
       <c r="F23" s="18"/>
       <c r="G23" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$E$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="I23" s="14" t="str">
-        <f>'data'!$B$20</f>
+        <f>data!$E$20&amp;" "&amp;data!$B$20</f>
       </c>
       <c r="J23" s="18"/>
       <c r="K23" s="18"/>
@@ -2940,56 +3018,56 @@
       <c r="M23" s="18"/>
       <c r="N23" s="18"/>
       <c r="O23" s="14" t="str">
-        <f>'data'!$B$19</f>
+        <f>data!$E$19&amp;" "&amp;data!$B$19</f>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="L25" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="O25" s="13" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="str">
-        <f>'data'!$B$6</f>
+        <f>data!$E$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="B26" s="14" t="str">
         <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x",AND(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x",AND(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))*1),0)</f>
@@ -3010,7 +3088,7 @@
         <f>RANK(U26,$U$26:$U$28)+COUNTIF($U$25:U25,U26)</f>
       </c>
       <c r="I26" s="14" t="str">
-        <f>'data'!$B$18</f>
+        <f>data!$E$18&amp;" "&amp;data!$B$18</f>
       </c>
       <c r="J26" s="14" t="str">
         <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x",AND(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x",AND(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))*1),0)</f>
@@ -3039,7 +3117,7 @@
     </row>
     <row r="27">
       <c r="A27" s="14" t="str">
-        <f>'data'!$B$7</f>
+        <f>data!$E$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="B27" s="14" t="str">
         <f>IF(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),IF(OR(D21="X",D21="x",AND(OR(COUNTA(B21,C21,E21,F21)&gt;0,OR(D21="X",D21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),IF(OR(D23="X",D23="x",AND(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))*1),0)</f>
@@ -3060,7 +3138,7 @@
         <f>RANK(U27,$U$26:$U$28)+COUNTIF($U$25:U26,U27)</f>
       </c>
       <c r="I27" s="14" t="str">
-        <f>'data'!$B$19</f>
+        <f>data!$E$19&amp;" "&amp;data!$B$19</f>
       </c>
       <c r="J27" s="14" t="str">
         <f>IF(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),IF(OR(L21="X",L21="x",AND(OR(COUNTA(J21,K21,M21,N21)&gt;0,OR(L21="X",L21="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K21," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N21," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),IF(OR(L23="X",L23="x",AND(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))*1),0)</f>
@@ -3089,7 +3167,7 @@
     </row>
     <row r="28">
       <c r="A28" s="14" t="str">
-        <f>'data'!$B$8</f>
+        <f>data!$E$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="B28" s="14" t="str">
         <f>IF(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),IF(OR(D22="X",D22="x",AND(OR(COUNTA(B22,C22,E22,F22)&gt;0,OR(D22="X",D22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),IF(OR(D23="X",D23="x",AND(OR(COUNTA(B23,C23,E23,F23)&gt;0,OR(D23="X",D23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")))*1),0)</f>
@@ -3110,7 +3188,7 @@
         <f>RANK(U28,$U$26:$U$28)+COUNTIF($U$25:U27,U28)</f>
       </c>
       <c r="I28" s="14" t="str">
-        <f>'data'!$B$20</f>
+        <f>data!$E$20&amp;" "&amp;data!$B$20</f>
       </c>
       <c r="J28" s="14" t="str">
         <f>IF(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),IF(OR(L22="X",L22="x",AND(OR(COUNTA(J22,K22,M22,N22)&gt;0,OR(L22="X",L22="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K22," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N22," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),IF(OR(L23="X",L23="x",AND(OR(COUNTA(J23,K23,M23,N23)&gt;0,OR(L23="X",L23="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K23," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N23," ",""),"0",""),"-","")))*1),0)</f>
@@ -3140,22 +3218,22 @@
     <row r="31">
       <c r="F31" s="13"/>
       <c r="G31" s="13" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="N31" s="13"/>
       <c r="O31" s="13" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32">
       <c r="F32" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G32" s="19" t="str">
         <f>IFERROR(INDEX($A$26:$A$28, MATCH(1, $G$26:$G$28, 0)), "-")</f>
       </c>
       <c r="N32" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O32" s="19" t="str">
         <f>IFERROR(INDEX($I$26:$I$28, MATCH(1, $O$26:$O$28, 0)), "-")</f>
@@ -3163,13 +3241,13 @@
     </row>
     <row r="33">
       <c r="F33" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G33" s="19" t="str">
         <f>IFERROR(INDEX($A$26:$A$28, MATCH(2, $G$26:$G$28, 0)), "-")</f>
       </c>
       <c r="N33" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O33" s="19" t="str">
         <f>IFERROR(INDEX($I$26:$I$28, MATCH(2, $O$26:$O$28, 0)), "-")</f>
@@ -3177,13 +3255,13 @@
     </row>
     <row r="34">
       <c r="F34" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="G34" s="19" t="str">
         <f>IFERROR(INDEX($A$26:$A$28, MATCH(3, $G$26:$G$28, 0)), "-")</f>
       </c>
       <c r="N34" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="O34" s="19" t="str">
         <f>IFERROR(INDEX($I$26:$I$28, MATCH(3, $O$26:$O$28, 0)), "-")</f>
@@ -3211,27 +3289,27 @@
     </row>
     <row r="37">
       <c r="A37" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L37" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O37" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$E$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="B38" s="18"/>
       <c r="C38" s="18"/>
@@ -3239,10 +3317,10 @@
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
       <c r="G38" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$E$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="I38" s="14" t="str">
-        <f>'data'!$B$22</f>
+        <f>data!$E$22&amp;" "&amp;data!$B$22</f>
       </c>
       <c r="J38" s="18"/>
       <c r="K38" s="18"/>
@@ -3250,12 +3328,12 @@
       <c r="M38" s="18"/>
       <c r="N38" s="18"/>
       <c r="O38" s="14" t="str">
-        <f>'data'!$B$21</f>
+        <f>data!$E$21&amp;" "&amp;data!$B$21</f>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="str">
-        <f>'data'!$B$11</f>
+        <f>data!$E$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="B39" s="18"/>
       <c r="C39" s="18"/>
@@ -3263,10 +3341,10 @@
       <c r="E39" s="18"/>
       <c r="F39" s="18"/>
       <c r="G39" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$E$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="I39" s="14" t="str">
-        <f>'data'!$B$23</f>
+        <f>data!$E$23&amp;" "&amp;data!$B$23</f>
       </c>
       <c r="J39" s="18"/>
       <c r="K39" s="18"/>
@@ -3274,12 +3352,12 @@
       <c r="M39" s="18"/>
       <c r="N39" s="18"/>
       <c r="O39" s="14" t="str">
-        <f>'data'!$B$21</f>
+        <f>data!$E$21&amp;" "&amp;data!$B$21</f>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="str">
-        <f>'data'!$B$11</f>
+        <f>data!$E$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
@@ -3287,10 +3365,10 @@
       <c r="E40" s="18"/>
       <c r="F40" s="18"/>
       <c r="G40" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$E$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="I40" s="14" t="str">
-        <f>'data'!$B$23</f>
+        <f>data!$E$23&amp;" "&amp;data!$B$23</f>
       </c>
       <c r="J40" s="18"/>
       <c r="K40" s="18"/>
@@ -3298,56 +3376,56 @@
       <c r="M40" s="18"/>
       <c r="N40" s="18"/>
       <c r="O40" s="14" t="str">
-        <f>'data'!$B$22</f>
+        <f>data!$E$22&amp;" "&amp;data!$B$22</f>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="K42" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="L42" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="M42" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="N42" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="O42" s="13" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="str">
-        <f>'data'!$B$9</f>
+        <f>data!$E$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="B43" s="14" t="str">
         <f>IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x",AND(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),IF(OR(D39="X",D39="x",AND(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))*1),0)</f>
@@ -3368,7 +3446,7 @@
         <f>RANK(U43,$U$43:$U$45)+COUNTIF($U$42:U42,U43)</f>
       </c>
       <c r="I43" s="14" t="str">
-        <f>'data'!$B$21</f>
+        <f>data!$E$21&amp;" "&amp;data!$B$21</f>
       </c>
       <c r="J43" s="14" t="str">
         <f>IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x",AND(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),IF(OR(L39="X",L39="x",AND(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))*1),0)</f>
@@ -3397,7 +3475,7 @@
     </row>
     <row r="44">
       <c r="A44" s="14" t="str">
-        <f>'data'!$B$10</f>
+        <f>data!$E$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="B44" s="14" t="str">
         <f>IF(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),IF(OR(D38="X",D38="x",AND(OR(COUNTA(B38,C38,E38,F38)&gt;0,OR(D38="X",D38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),IF(OR(D40="X",D40="x",AND(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))*1),0)</f>
@@ -3418,7 +3496,7 @@
         <f>RANK(U44,$U$43:$U$45)+COUNTIF($U$42:U43,U44)</f>
       </c>
       <c r="I44" s="14" t="str">
-        <f>'data'!$B$22</f>
+        <f>data!$E$22&amp;" "&amp;data!$B$22</f>
       </c>
       <c r="J44" s="14" t="str">
         <f>IF(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),IF(OR(L38="X",L38="x",AND(OR(COUNTA(J38,K38,M38,N38)&gt;0,OR(L38="X",L38="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K38," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N38," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),IF(OR(L40="X",L40="x",AND(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))*1),0)</f>
@@ -3447,7 +3525,7 @@
     </row>
     <row r="45">
       <c r="A45" s="14" t="str">
-        <f>'data'!$B$11</f>
+        <f>data!$E$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="B45" s="14" t="str">
         <f>IF(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),IF(OR(D39="X",D39="x",AND(OR(COUNTA(B39,C39,E39,F39)&gt;0,OR(D39="X",D39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),IF(OR(D40="X",D40="x",AND(OR(COUNTA(B40,C40,E40,F40)&gt;0,OR(D40="X",D40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")))*1),0)</f>
@@ -3468,7 +3546,7 @@
         <f>RANK(U45,$U$43:$U$45)+COUNTIF($U$42:U44,U45)</f>
       </c>
       <c r="I45" s="14" t="str">
-        <f>'data'!$B$23</f>
+        <f>data!$E$23&amp;" "&amp;data!$B$23</f>
       </c>
       <c r="J45" s="14" t="str">
         <f>IF(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),IF(OR(L39="X",L39="x",AND(OR(COUNTA(J39,K39,M39,N39)&gt;0,OR(L39="X",L39="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K39," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N39," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),IF(OR(L40="X",L40="x",AND(OR(COUNTA(J40,K40,M40,N40)&gt;0,OR(L40="X",L40="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K40," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N40," ",""),"0",""),"-","")))*1),0)</f>
@@ -3498,22 +3576,22 @@
     <row r="48">
       <c r="F48" s="13"/>
       <c r="G48" s="13" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="N48" s="13"/>
       <c r="O48" s="13" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49">
       <c r="F49" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G49" s="19" t="str">
         <f>IFERROR(INDEX($A$43:$A$45, MATCH(1, $G$43:$G$45, 0)), "-")</f>
       </c>
       <c r="N49" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O49" s="19" t="str">
         <f>IFERROR(INDEX($I$43:$I$45, MATCH(1, $O$43:$O$45, 0)), "-")</f>
@@ -3521,13 +3599,13 @@
     </row>
     <row r="50">
       <c r="F50" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G50" s="19" t="str">
         <f>IFERROR(INDEX($A$43:$A$45, MATCH(2, $G$43:$G$45, 0)), "-")</f>
       </c>
       <c r="N50" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O50" s="19" t="str">
         <f>IFERROR(INDEX($I$43:$I$45, MATCH(2, $O$43:$O$45, 0)), "-")</f>
@@ -3535,13 +3613,13 @@
     </row>
     <row r="51">
       <c r="F51" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="G51" s="19" t="str">
         <f>IFERROR(INDEX($A$43:$A$45, MATCH(3, $G$43:$G$45, 0)), "-")</f>
       </c>
       <c r="N51" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="O51" s="19" t="str">
         <f>IFERROR(INDEX($I$43:$I$45, MATCH(3, $O$43:$O$45, 0)), "-")</f>
@@ -3569,27 +3647,27 @@
     </row>
     <row r="54">
       <c r="A54" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G54" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I54" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L54" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O54" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="str">
-        <f>'data'!$B$13</f>
+        <f>data!$E$13&amp;" "&amp;data!$B$13</f>
       </c>
       <c r="B55" s="18"/>
       <c r="C55" s="18"/>
@@ -3597,10 +3675,10 @@
       <c r="E55" s="18"/>
       <c r="F55" s="18"/>
       <c r="G55" s="14" t="str">
-        <f>'data'!$B$12</f>
+        <f>data!$E$12&amp;" "&amp;data!$B$12</f>
       </c>
       <c r="I55" s="14" t="str">
-        <f>'data'!$B$25</f>
+        <f>data!$E$25&amp;" "&amp;data!$B$25</f>
       </c>
       <c r="J55" s="18"/>
       <c r="K55" s="18"/>
@@ -3608,12 +3686,12 @@
       <c r="M55" s="18"/>
       <c r="N55" s="18"/>
       <c r="O55" s="14" t="str">
-        <f>'data'!$B$24</f>
+        <f>data!$E$24&amp;" "&amp;data!$B$24</f>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="str">
-        <f>'data'!$B$14</f>
+        <f>data!$E$14&amp;" "&amp;data!$B$14</f>
       </c>
       <c r="B56" s="18"/>
       <c r="C56" s="18"/>
@@ -3621,10 +3699,10 @@
       <c r="E56" s="18"/>
       <c r="F56" s="18"/>
       <c r="G56" s="14" t="str">
-        <f>'data'!$B$12</f>
+        <f>data!$E$12&amp;" "&amp;data!$B$12</f>
       </c>
       <c r="I56" s="14" t="str">
-        <f>'data'!$B$26</f>
+        <f>data!$E$26&amp;" "&amp;data!$B$26</f>
       </c>
       <c r="J56" s="18"/>
       <c r="K56" s="18"/>
@@ -3632,12 +3710,12 @@
       <c r="M56" s="18"/>
       <c r="N56" s="18"/>
       <c r="O56" s="14" t="str">
-        <f>'data'!$B$24</f>
+        <f>data!$E$24&amp;" "&amp;data!$B$24</f>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="str">
-        <f>'data'!$B$14</f>
+        <f>data!$E$14&amp;" "&amp;data!$B$14</f>
       </c>
       <c r="B57" s="18"/>
       <c r="C57" s="18"/>
@@ -3645,10 +3723,10 @@
       <c r="E57" s="18"/>
       <c r="F57" s="18"/>
       <c r="G57" s="14" t="str">
-        <f>'data'!$B$13</f>
+        <f>data!$E$13&amp;" "&amp;data!$B$13</f>
       </c>
       <c r="I57" s="14" t="str">
-        <f>'data'!$B$26</f>
+        <f>data!$E$26&amp;" "&amp;data!$B$26</f>
       </c>
       <c r="J57" s="18"/>
       <c r="K57" s="18"/>
@@ -3656,56 +3734,56 @@
       <c r="M57" s="18"/>
       <c r="N57" s="18"/>
       <c r="O57" s="14" t="str">
-        <f>'data'!$B$25</f>
+        <f>data!$E$25&amp;" "&amp;data!$B$25</f>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="I59" s="13" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="J59" s="13" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="K59" s="13" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="L59" s="13" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="M59" s="13" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="N59" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="O59" s="13" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="str">
-        <f>'data'!$B$12</f>
+        <f>data!$E$12&amp;" "&amp;data!$B$12</f>
       </c>
       <c r="B60" s="14" t="str">
         <f>IF(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),IF(OR(D55="X",D55="x",AND(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),IF(OR(D56="X",D56="x",AND(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))*1),0)</f>
@@ -3726,7 +3804,7 @@
         <f>RANK(U60,$U$60:$U$62)+COUNTIF($U$59:U59,U60)</f>
       </c>
       <c r="I60" s="14" t="str">
-        <f>'data'!$B$24</f>
+        <f>data!$E$24&amp;" "&amp;data!$B$24</f>
       </c>
       <c r="J60" s="14" t="str">
         <f>IF(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),IF(OR(L55="X",L55="x",AND(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),IF(OR(L56="X",L56="x",AND(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))*1),0)</f>
@@ -3755,7 +3833,7 @@
     </row>
     <row r="61">
       <c r="A61" s="14" t="str">
-        <f>'data'!$B$13</f>
+        <f>data!$E$13&amp;" "&amp;data!$B$13</f>
       </c>
       <c r="B61" s="14" t="str">
         <f>IF(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),IF(OR(D55="X",D55="x",AND(OR(COUNTA(B55,C55,E55,F55)&gt;0,OR(D55="X",D55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),IF(OR(D57="X",D57="x",AND(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))*1),0)</f>
@@ -3776,7 +3854,7 @@
         <f>RANK(U61,$U$60:$U$62)+COUNTIF($U$59:U60,U61)</f>
       </c>
       <c r="I61" s="14" t="str">
-        <f>'data'!$B$25</f>
+        <f>data!$E$25&amp;" "&amp;data!$B$25</f>
       </c>
       <c r="J61" s="14" t="str">
         <f>IF(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),IF(OR(L55="X",L55="x",AND(OR(COUNTA(J55,K55,M55,N55)&gt;0,OR(L55="X",L55="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K55," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N55," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),IF(OR(L57="X",L57="x",AND(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))*1),0)</f>
@@ -3805,7 +3883,7 @@
     </row>
     <row r="62">
       <c r="A62" s="14" t="str">
-        <f>'data'!$B$14</f>
+        <f>data!$E$14&amp;" "&amp;data!$B$14</f>
       </c>
       <c r="B62" s="14" t="str">
         <f>IF(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),IF(OR(D56="X",D56="x",AND(OR(COUNTA(B56,C56,E56,F56)&gt;0,OR(D56="X",D56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),IF(OR(D57="X",D57="x",AND(OR(COUNTA(B57,C57,E57,F57)&gt;0,OR(D57="X",D57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")))*1),0)</f>
@@ -3826,7 +3904,7 @@
         <f>RANK(U62,$U$60:$U$62)+COUNTIF($U$59:U61,U62)</f>
       </c>
       <c r="I62" s="14" t="str">
-        <f>'data'!$B$26</f>
+        <f>data!$E$26&amp;" "&amp;data!$B$26</f>
       </c>
       <c r="J62" s="14" t="str">
         <f>IF(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),IF(OR(L56="X",L56="x",AND(OR(COUNTA(J56,K56,M56,N56)&gt;0,OR(L56="X",L56="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K56," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N56," ",""),"0",""),"-","")))*1),0)+IF(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),IF(OR(L57="X",L57="x",AND(OR(COUNTA(J57,K57,M57,N57)&gt;0,OR(L57="X",L57="x")),(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-","")))=(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-",""))))),0,(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(J57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(K57," ",""),"0",""),"-",""))&gt;LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(M57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(N57," ",""),"0",""),"-","")))*1),0)</f>
@@ -3856,22 +3934,22 @@
     <row r="65">
       <c r="F65" s="13"/>
       <c r="G65" s="13" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="N65" s="13"/>
       <c r="O65" s="13" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
     </row>
     <row r="66">
       <c r="F66" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G66" s="19" t="str">
         <f>IFERROR(INDEX($A$60:$A$62, MATCH(1, $G$60:$G$62, 0)), "-")</f>
       </c>
       <c r="N66" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O66" s="19" t="str">
         <f>IFERROR(INDEX($I$60:$I$62, MATCH(1, $O$60:$O$62, 0)), "-")</f>
@@ -3879,13 +3957,13 @@
     </row>
     <row r="67">
       <c r="F67" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G67" s="19" t="str">
         <f>IFERROR(INDEX($A$60:$A$62, MATCH(2, $G$60:$G$62, 0)), "-")</f>
       </c>
       <c r="N67" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O67" s="19" t="str">
         <f>IFERROR(INDEX($I$60:$I$62, MATCH(2, $O$60:$O$62, 0)), "-")</f>
@@ -3893,13 +3971,13 @@
     </row>
     <row r="68">
       <c r="F68" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="G68" s="19" t="str">
         <f>IFERROR(INDEX($A$60:$A$62, MATCH(3, $G$60:$G$62, 0)), "-")</f>
       </c>
       <c r="N68" t="s">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="O68" s="19" t="str">
         <f>IFERROR(INDEX($I$60:$I$62, MATCH(3, $O$60:$O$62, 0)), "-")</f>
@@ -3951,7 +4029,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -3960,7 +4038,7 @@
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
       <c r="I1" s="13" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
@@ -3971,7 +4049,7 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -3980,7 +4058,7 @@
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
       <c r="I2" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
@@ -3991,22 +4069,22 @@
     </row>
     <row r="3">
       <c r="A3" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4">
@@ -4035,27 +4113,27 @@
     </row>
     <row r="6">
       <c r="F6" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G6" s="19"/>
       <c r="N6" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O6" s="19"/>
     </row>
     <row r="7">
       <c r="F7" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G7" s="19"/>
       <c r="N7" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O7" s="19"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -4064,7 +4142,7 @@
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="I10" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
@@ -4075,22 +4153,22 @@
     </row>
     <row r="11">
       <c r="A11" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O11" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12">
@@ -4119,27 +4197,27 @@
     </row>
     <row r="14">
       <c r="F14" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G14" s="19"/>
       <c r="N14" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O14" s="19"/>
     </row>
     <row r="15">
       <c r="F15" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G15" s="19"/>
       <c r="N15" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O15" s="19"/>
     </row>
     <row r="18">
       <c r="A18" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -4148,7 +4226,7 @@
       <c r="F18" s="13"/>
       <c r="G18" s="13"/>
       <c r="I18" s="13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J18" s="13"/>
       <c r="K18" s="13"/>
@@ -4159,22 +4237,22 @@
     </row>
     <row r="19">
       <c r="A19" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O19" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20">
@@ -4203,27 +4281,27 @@
     </row>
     <row r="22">
       <c r="F22" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G22" s="19"/>
       <c r="N22" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O22" s="19"/>
     </row>
     <row r="23">
       <c r="F23" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G23" s="19"/>
       <c r="N23" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O23" s="19"/>
     </row>
     <row r="26">
       <c r="A26" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
@@ -4232,7 +4310,7 @@
       <c r="F26" s="13"/>
       <c r="G26" s="13"/>
       <c r="I26" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
@@ -4243,22 +4321,22 @@
     </row>
     <row r="27">
       <c r="A27" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O27" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28">
@@ -4287,27 +4365,27 @@
     </row>
     <row r="30">
       <c r="F30" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G30" s="19"/>
       <c r="N30" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O30" s="19"/>
     </row>
     <row r="31">
       <c r="F31" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G31" s="19"/>
       <c r="N31" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O31" s="19"/>
     </row>
     <row r="39">
       <c r="A39" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
@@ -4316,7 +4394,7 @@
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
       <c r="I39" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J39" s="13"/>
       <c r="K39" s="13"/>
@@ -4327,22 +4405,22 @@
     </row>
     <row r="40">
       <c r="A40" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L40" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O40" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41">
@@ -4371,27 +4449,27 @@
     </row>
     <row r="43">
       <c r="F43" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G43" s="19"/>
       <c r="N43" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O43" s="19"/>
     </row>
     <row r="44">
       <c r="F44" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G44" s="19"/>
       <c r="N44" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O44" s="19"/>
     </row>
     <row r="47">
       <c r="A47" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
@@ -4400,7 +4478,7 @@
       <c r="F47" s="13"/>
       <c r="G47" s="13"/>
       <c r="I47" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J47" s="13"/>
       <c r="K47" s="13"/>
@@ -4411,22 +4489,22 @@
     </row>
     <row r="48">
       <c r="A48" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I48" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L48" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O48" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49">
@@ -4455,27 +4533,27 @@
     </row>
     <row r="51">
       <c r="F51" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G51" s="19"/>
       <c r="N51" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O51" s="19"/>
     </row>
     <row r="52">
       <c r="F52" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G52" s="19"/>
       <c r="N52" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O52" s="19"/>
     </row>
     <row r="60">
       <c r="A60" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B60" s="13"/>
       <c r="C60" s="13"/>
@@ -4484,7 +4562,7 @@
       <c r="F60" s="13"/>
       <c r="G60" s="13"/>
       <c r="I60" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J60" s="13"/>
       <c r="K60" s="13"/>
@@ -4495,22 +4573,22 @@
     </row>
     <row r="61">
       <c r="A61" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G61" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="L61" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="O61" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62">
@@ -4539,27 +4617,27 @@
     </row>
     <row r="64">
       <c r="F64" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G64" s="19"/>
       <c r="N64" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="O64" s="19"/>
     </row>
     <row r="65">
       <c r="F65" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G65" s="19"/>
       <c r="N65" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="O65" s="19"/>
     </row>
     <row r="73">
       <c r="A73" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B73" s="13"/>
       <c r="C73" s="13"/>
@@ -4570,13 +4648,13 @@
     </row>
     <row r="74">
       <c r="A74" s="17" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
     </row>
     <row r="75">
@@ -4594,13 +4672,13 @@
     </row>
     <row r="77">
       <c r="F77" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="G77" s="19"/>
     </row>
     <row r="78">
       <c r="F78" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G78" s="19"/>
     </row>
@@ -4670,7 +4748,7 @@
     </row>
     <row r="5">
       <c r="A5" s="25" t="str">
-        <f>"1. " &amp; data!$B$3</f>
+        <f>data!$E$3&amp;" "&amp;data!$B$3</f>
       </c>
       <c r="C5" s="23" t="str">
         <f>CONCATENATE("Pool A-1st ",'Pool Matches'!G15)</f>
@@ -4678,7 +4756,7 @@
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
-        <f>"2. " &amp; data!$B$4</f>
+        <f>data!$E$4&amp;" "&amp;data!$B$4</f>
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="21">
@@ -4687,7 +4765,7 @@
     </row>
     <row r="7">
       <c r="A7" s="27" t="str">
-        <f>"3. " &amp; data!$B$5</f>
+        <f>data!$E$5&amp;" "&amp;data!$B$5</f>
       </c>
       <c r="C7" s="23" t="str">
         <f>CONCATENATE("Pool E-2nd ",'Pool Matches'!O16)</f>
@@ -4716,7 +4794,7 @@
     </row>
     <row r="10">
       <c r="A10" s="25" t="str">
-        <f>"1. " &amp; data!$B$6</f>
+        <f>data!$E$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
@@ -4728,7 +4806,7 @@
     </row>
     <row r="11">
       <c r="A11" s="26" t="str">
-        <f>"2. " &amp; data!$B$7</f>
+        <f>data!$E$7&amp;" "&amp;data!$B$7</f>
       </c>
       <c r="C11" s="23" t="str">
         <f>CONCATENATE("Pool F-2nd ",'Pool Matches'!O33)</f>
@@ -4739,7 +4817,7 @@
     </row>
     <row r="12">
       <c r="A12" s="27" t="str">
-        <f>"3. " &amp; data!$B$8</f>
+        <f>data!$E$8&amp;" "&amp;data!$B$8</f>
       </c>
       <c r="I12" s="21">
         <v>13</v>
@@ -4764,7 +4842,7 @@
     </row>
     <row r="15">
       <c r="A15" s="25" t="str">
-        <f>"1. " &amp; data!$B$9</f>
+        <f>data!$E$9&amp;" "&amp;data!$B$9</f>
       </c>
       <c r="C15" s="23" t="str">
         <f>CONCATENATE("Pool G-2nd ",'Pool Matches'!O50)</f>
@@ -4777,7 +4855,7 @@
     </row>
     <row r="16">
       <c r="A16" s="26" t="str">
-        <f>"2. " &amp; data!$B$10</f>
+        <f>data!$E$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="G16" s="21">
         <v>10</v>
@@ -4787,7 +4865,7 @@
     </row>
     <row r="17">
       <c r="A17" s="27" t="str">
-        <f>"3. " &amp; data!$B$11</f>
+        <f>data!$E$11&amp;" "&amp;data!$B$11</f>
       </c>
       <c r="C17" s="23" t="str">
         <f>CONCATENATE("Pool D-1st ",'Pool Matches'!G66)</f>
@@ -4815,17 +4893,17 @@
     </row>
     <row r="20">
       <c r="A20" s="25" t="str">
-        <f>"1. " &amp; data!$B$12</f>
+        <f>data!$E$12&amp;" "&amp;data!$B$12</f>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="26" t="str">
-        <f>"2. " &amp; data!$B$13</f>
+        <f>data!$E$13&amp;" "&amp;data!$B$13</f>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="27" t="str">
-        <f>"3. " &amp; data!$B$14</f>
+        <f>data!$E$14&amp;" "&amp;data!$B$14</f>
       </c>
     </row>
     <row r="23">
@@ -4875,7 +4953,7 @@
     </row>
     <row r="5">
       <c r="A5" s="25" t="str">
-        <f>"1. " &amp; data!$B$15</f>
+        <f>data!$E$15&amp;" "&amp;data!$B$15</f>
       </c>
       <c r="C5" s="23" t="str">
         <f>CONCATENATE("Pool E-1st ",'Pool Matches'!O15)</f>
@@ -4883,7 +4961,7 @@
     </row>
     <row r="6">
       <c r="A6" s="26" t="str">
-        <f>"2. " &amp; data!$B$16</f>
+        <f>data!$E$16&amp;" "&amp;data!$B$16</f>
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="21">
@@ -4892,7 +4970,7 @@
     </row>
     <row r="7">
       <c r="A7" s="27" t="str">
-        <f>"3. " &amp; data!$B$17</f>
+        <f>data!$E$17&amp;" "&amp;data!$B$17</f>
       </c>
       <c r="C7" s="23" t="str">
         <f>CONCATENATE("Pool A-2nd ",'Pool Matches'!G16)</f>
@@ -4921,7 +4999,7 @@
     </row>
     <row r="10">
       <c r="A10" s="25" t="str">
-        <f>"1. " &amp; data!$B$18</f>
+        <f>data!$E$18&amp;" "&amp;data!$B$18</f>
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
@@ -4933,7 +5011,7 @@
     </row>
     <row r="11">
       <c r="A11" s="26" t="str">
-        <f>"2. " &amp; data!$B$19</f>
+        <f>data!$E$19&amp;" "&amp;data!$B$19</f>
       </c>
       <c r="C11" s="23" t="str">
         <f>CONCATENATE("Pool B-2nd ",'Pool Matches'!G33)</f>
@@ -4944,7 +5022,7 @@
     </row>
     <row r="12">
       <c r="A12" s="27" t="str">
-        <f>"3. " &amp; data!$B$20</f>
+        <f>data!$E$20&amp;" "&amp;data!$B$20</f>
       </c>
       <c r="I12" s="21">
         <v>14</v>
@@ -4969,7 +5047,7 @@
     </row>
     <row r="15">
       <c r="A15" s="25" t="str">
-        <f>"1. " &amp; data!$B$21</f>
+        <f>data!$E$21&amp;" "&amp;data!$B$21</f>
       </c>
       <c r="C15" s="23" t="str">
         <f>CONCATENATE("Pool C-2nd ",'Pool Matches'!G50)</f>
@@ -4982,7 +5060,7 @@
     </row>
     <row r="16">
       <c r="A16" s="26" t="str">
-        <f>"2. " &amp; data!$B$22</f>
+        <f>data!$E$22&amp;" "&amp;data!$B$22</f>
       </c>
       <c r="G16" s="21">
         <v>12</v>
@@ -4992,7 +5070,7 @@
     </row>
     <row r="17">
       <c r="A17" s="27" t="str">
-        <f>"3. " &amp; data!$B$23</f>
+        <f>data!$E$23&amp;" "&amp;data!$B$23</f>
       </c>
       <c r="C17" s="23" t="str">
         <f>CONCATENATE("Pool H-1st ",'Pool Matches'!O66)</f>
@@ -5020,17 +5098,17 @@
     </row>
     <row r="20">
       <c r="A20" s="25" t="str">
-        <f>"1. " &amp; data!$B$24</f>
+        <f>data!$E$24&amp;" "&amp;data!$B$24</f>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="26" t="str">
-        <f>"2. " &amp; data!$B$25</f>
+        <f>data!$E$25&amp;" "&amp;data!$B$25</f>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="27" t="str">
-        <f>"3. " &amp; data!$B$26</f>
+        <f>data!$E$26&amp;" "&amp;data!$B$26</f>
       </c>
     </row>
     <row r="23">

--- a/pools-example-medium-seeded.xlsx
+++ b/pools-example-medium-seeded.xlsx
@@ -25,6 +25,7 @@
     <definedName localSheetId="6" name="_xlnm.Print_Area">'Tree 2'!$A$1:$I$23</definedName>
     <definedName localSheetId="7" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$12</definedName>
     <definedName localSheetId="8" name="_xlnm.Print_Area">'Names to Print B'!$A$1:$B$12</definedName>
+    <definedName localSheetId="9" name="_xlnm.Print_Area">'Tags'!$A$1:$A$48</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$P$85</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -806,13 +807,13 @@
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -1783,7 +1784,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="110"/>
+    <col customWidth="true" max="1" min="1" width="88"/>
   </cols>
   <sheetData>
     <row r="1" ht="409" customHeight="true">

--- a/pools-example-medium-seeded.xlsx
+++ b/pools-example-medium-seeded.xlsx
@@ -810,7 +810,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
@@ -1548,8 +1548,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
@@ -1666,8 +1666,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">

--- a/pools-example-medium-seeded.xlsx
+++ b/pools-example-medium-seeded.xlsx
@@ -813,7 +813,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
-      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
